--- a/outputs/50193.xlsx
+++ b/outputs/50193.xlsx
@@ -2036,275 +2036,275 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="20" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="9" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="9" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="17" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="17" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="21" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="21" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2747,7 +2747,7 @@
         <v/>
       </c>
       <c r="K6" s="25" t="str">
-        <f aca="false">IF(J6="","",SUMPRODUCT((I6=$I$6:$I$1500)*(B6&lt;$B$6:$B$1500))+SUMPRODUCT((I6=$I$6)*(B6=$B$6)))</f>
+        <f aca="false">IF(J6="","",SUMPRODUCT((I6=$I$6:$I$1500)*(B6&lt;$B$6:$B$1500))+COUNTIFS($I$6:I6,I6,$B$6:B6,B6))</f>
         <v/>
       </c>
       <c r="N6" s="12" t="s">
@@ -2795,7 +2795,7 @@
         <v/>
       </c>
       <c r="K7" s="25" t="str">
-        <f aca="false">IF(J7="","",SUMPRODUCT((I7=$I$6:$I$1500)*(B7&lt;$B$6:$B$1500))+SUMPRODUCT((I7=$I$6:$I$7)*(B7=$B$6:$B$7)))</f>
+        <f aca="false">IF(J7="","",SUMPRODUCT((I7=$I$6:$I$1500)*(B7&lt;$B$6:$B$1500))+COUNTIFS($I$6:I7,I7,$B$6:B7,B7))</f>
         <v/>
       </c>
       <c r="N7" s="33" t="s">
@@ -2857,7 +2857,7 @@
         <v/>
       </c>
       <c r="K8" s="25" t="str">
-        <f aca="false">IF(J8="","",SUMPRODUCT((I8=$I$6:$I$1500)*(B8&lt;$B$6:$B$1500))+SUMPRODUCT((I8=$I$6:$I$8)*(B8=$B$6:$B$8)))</f>
+        <f aca="false">IF(J8="","",SUMPRODUCT((I8=$I$6:$I$1500)*(B8&lt;$B$6:$B$1500))+COUNTIFS($I$6:I8,I8,$B$6:B8,B8))</f>
         <v/>
       </c>
       <c r="N8" s="33" t="s">
@@ -2924,7 +2924,7 @@
         <v/>
       </c>
       <c r="K9" s="25" t="str">
-        <f aca="false">IF(J9="","",SUMPRODUCT((I9=$I$6:$I$1500)*(B9&lt;$B$6:$B$1500))+SUMPRODUCT((I9=$I$6:$I$9)*(B9=$B$6:$B$9)))</f>
+        <f aca="false">IF(J9="","",SUMPRODUCT((I9=$I$6:$I$1500)*(B9&lt;$B$6:$B$1500))+COUNTIFS($I$6:I9,I9,$B$6:B9,B9))</f>
         <v/>
       </c>
       <c r="N9" s="33" t="s">
@@ -2991,7 +2991,7 @@
         <v/>
       </c>
       <c r="K10" s="25" t="str">
-        <f aca="false">IF(J10="","",SUMPRODUCT((I10=$I$6:$I$1500)*(B10&lt;$B$6:$B$1500))+SUMPRODUCT((I10=$I$6:$I$10)*(B10=$B$6:$B$10)))</f>
+        <f aca="false">IF(J10="","",SUMPRODUCT((I10=$I$6:$I$1500)*(B10&lt;$B$6:$B$1500))+COUNTIFS($I$6:I10,I10,$B$6:B10,B10))</f>
         <v/>
       </c>
       <c r="N10" s="33" t="s">
@@ -3058,7 +3058,7 @@
         <v/>
       </c>
       <c r="K11" s="25" t="str">
-        <f aca="false">IF(J11="","",SUMPRODUCT((I11=$I$6:$I$1500)*(B11&lt;$B$6:$B$1500))+SUMPRODUCT((I11=$I$6:$I$11)*(B11=$B$6:$B$11)))</f>
+        <f aca="false">IF(J11="","",SUMPRODUCT((I11=$I$6:$I$1500)*(B11&lt;$B$6:$B$1500))+COUNTIFS($I$6:I11,I11,$B$6:B11,B11))</f>
         <v/>
       </c>
       <c r="N11" s="33" t="s">
@@ -3125,7 +3125,7 @@
         <v/>
       </c>
       <c r="K12" s="25" t="str">
-        <f aca="false">IF(J12="","",SUMPRODUCT((I12=$I$6:$I$1500)*(B12&lt;$B$6:$B$1500))+SUMPRODUCT((I12=$I$6:$I$12)*(B12=$B$6:$B$12)))</f>
+        <f aca="false">IF(J12="","",SUMPRODUCT((I12=$I$6:$I$1500)*(B12&lt;$B$6:$B$1500))+COUNTIFS($I$6:I12,I12,$B$6:B12,B12))</f>
         <v/>
       </c>
       <c r="N12" s="33" t="s">
@@ -3192,7 +3192,7 @@
         <v/>
       </c>
       <c r="K13" s="25" t="str">
-        <f aca="false">IF(J13="","",SUMPRODUCT((I13=$I$6:$I$1500)*(B13&lt;$B$6:$B$1500))+SUMPRODUCT((I13=$I$6:$I$13)*(B13=$B$6:$B$13)))</f>
+        <f aca="false">IF(J13="","",SUMPRODUCT((I13=$I$6:$I$1500)*(B13&lt;$B$6:$B$1500))+COUNTIFS($I$6:I13,I13,$B$6:B13,B13))</f>
         <v/>
       </c>
       <c r="N13" s="33" t="s">
@@ -3259,7 +3259,7 @@
         <v/>
       </c>
       <c r="K14" s="25" t="str">
-        <f aca="false">IF(J14="","",SUMPRODUCT((I14=$I$6:$I$1500)*(B14&lt;$B$6:$B$1500))+SUMPRODUCT((I14=$I$6:$I$14)*(B14=$B$6:$B$14)))</f>
+        <f aca="false">IF(J14="","",SUMPRODUCT((I14=$I$6:$I$1500)*(B14&lt;$B$6:$B$1500))+COUNTIFS($I$6:I14,I14,$B$6:B14,B14))</f>
         <v/>
       </c>
       <c r="N14" s="33" t="s">
@@ -3326,7 +3326,7 @@
         <v/>
       </c>
       <c r="K15" s="25" t="str">
-        <f aca="false">IF(J15="","",SUMPRODUCT((I15=$I$6:$I$1500)*(B15&lt;$B$6:$B$1500))+SUMPRODUCT((I15=$I$6:$I$15)*(B15=$B$6:$B$15)))</f>
+        <f aca="false">IF(J15="","",SUMPRODUCT((I15=$I$6:$I$1500)*(B15&lt;$B$6:$B$1500))+COUNTIFS($I$6:I15,I15,$B$6:B15,B15))</f>
         <v/>
       </c>
       <c r="N15" s="33" t="s">
@@ -3393,7 +3393,7 @@
         <v/>
       </c>
       <c r="K16" s="25" t="str">
-        <f aca="false">IF(J16="","",SUMPRODUCT((I16=$I$6:$I$1500)*(B16&lt;$B$6:$B$1500))+SUMPRODUCT((I16=$I$6:$I$16)*(B16=$B$6:$B$16)))</f>
+        <f aca="false">IF(J16="","",SUMPRODUCT((I16=$I$6:$I$1500)*(B16&lt;$B$6:$B$1500))+COUNTIFS($I$6:I16,I16,$B$6:B16,B16))</f>
         <v/>
       </c>
       <c r="N16" s="33" t="s">
@@ -3460,7 +3460,7 @@
         <v/>
       </c>
       <c r="K17" s="25" t="str">
-        <f aca="false">IF(J17="","",SUMPRODUCT((I17=$I$6:$I$1500)*(B17&lt;$B$6:$B$1500))+SUMPRODUCT((I17=$I$6:$I$17)*(B17=$B$6:$B$17)))</f>
+        <f aca="false">IF(J17="","",SUMPRODUCT((I17=$I$6:$I$1500)*(B17&lt;$B$6:$B$1500))+COUNTIFS($I$6:I17,I17,$B$6:B17,B17))</f>
         <v/>
       </c>
       <c r="N17" s="33" t="s">
@@ -3527,7 +3527,7 @@
         <v/>
       </c>
       <c r="K18" s="25" t="str">
-        <f aca="false">IF(J18="","",SUMPRODUCT((I18=$I$6:$I$1500)*(B18&lt;$B$6:$B$1500))+SUMPRODUCT((I18=$I$6:$I$18)*(B18=$B$6:$B$18)))</f>
+        <f aca="false">IF(J18="","",SUMPRODUCT((I18=$I$6:$I$1500)*(B18&lt;$B$6:$B$1500))+COUNTIFS($I$6:I18,I18,$B$6:B18,B18))</f>
         <v/>
       </c>
       <c r="N18" s="33" t="s">
@@ -3594,7 +3594,7 @@
         <v/>
       </c>
       <c r="K19" s="25" t="str">
-        <f aca="false">IF(J19="","",SUMPRODUCT((I19=$I$6:$I$1500)*(B19&lt;$B$6:$B$1500))+SUMPRODUCT((I19=$I$6:$I$19)*(B19=$B$6:$B$19)))</f>
+        <f aca="false">IF(J19="","",SUMPRODUCT((I19=$I$6:$I$1500)*(B19&lt;$B$6:$B$1500))+COUNTIFS($I$6:I19,I19,$B$6:B19,B19))</f>
         <v/>
       </c>
       <c r="N19" s="33" t="s">
@@ -3661,7 +3661,7 @@
         <v/>
       </c>
       <c r="K20" s="25" t="str">
-        <f aca="false">IF(J20="","",SUMPRODUCT((I20=$I$6:$I$1500)*(B20&lt;$B$6:$B$1500))+SUMPRODUCT((I20=$I$6:$I$20)*(B20=$B$6:$B$20)))</f>
+        <f aca="false">IF(J20="","",SUMPRODUCT((I20=$I$6:$I$1500)*(B20&lt;$B$6:$B$1500))+COUNTIFS($I$6:I20,I20,$B$6:B20,B20))</f>
         <v/>
       </c>
       <c r="N20" s="33" t="s">
@@ -3728,7 +3728,7 @@
         <v/>
       </c>
       <c r="K21" s="25" t="str">
-        <f aca="false">IF(J21="","",SUMPRODUCT((I21=$I$6:$I$1500)*(B21&lt;$B$6:$B$1500))+SUMPRODUCT((I21=$I$6:$I$21)*(B21=$B$6:$B$21)))</f>
+        <f aca="false">IF(J21="","",SUMPRODUCT((I21=$I$6:$I$1500)*(B21&lt;$B$6:$B$1500))+COUNTIFS($I$6:I21,I21,$B$6:B21,B21))</f>
         <v/>
       </c>
       <c r="N21" s="33" t="s">
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="K22" s="25" t="str">
-        <f aca="false">IF(J22="","",SUMPRODUCT((I22=$I$6:$I$1500)*(B22&lt;$B$6:$B$1500))+SUMPRODUCT((I22=$I$6:$I$22)*(B22=$B$6:$B$22)))</f>
+        <f aca="false">IF(J22="","",SUMPRODUCT((I22=$I$6:$I$1500)*(B22&lt;$B$6:$B$1500))+COUNTIFS($I$6:I22,I22,$B$6:B22,B22))</f>
         <v/>
       </c>
       <c r="N22" s="33" t="s">
@@ -3862,7 +3862,7 @@
         <v/>
       </c>
       <c r="K23" s="25" t="str">
-        <f aca="false">IF(J23="","",SUMPRODUCT((I23=$I$6:$I$1500)*(B23&lt;$B$6:$B$1500))+SUMPRODUCT((I23=$I$6:$I$23)*(B23=$B$6:$B$23)))</f>
+        <f aca="false">IF(J23="","",SUMPRODUCT((I23=$I$6:$I$1500)*(B23&lt;$B$6:$B$1500))+COUNTIFS($I$6:I23,I23,$B$6:B23,B23))</f>
         <v/>
       </c>
       <c r="N23" s="33" t="s">
@@ -3929,7 +3929,7 @@
         <v/>
       </c>
       <c r="K24" s="25" t="str">
-        <f aca="false">IF(J24="","",SUMPRODUCT((I24=$I$6:$I$1500)*(B24&lt;$B$6:$B$1500))+SUMPRODUCT((I24=$I$6:$I$24)*(B24=$B$6:$B$24)))</f>
+        <f aca="false">IF(J24="","",SUMPRODUCT((I24=$I$6:$I$1500)*(B24&lt;$B$6:$B$1500))+COUNTIFS($I$6:I24,I24,$B$6:B24,B24))</f>
         <v/>
       </c>
       <c r="N24" s="52" t="s">
@@ -3996,7 +3996,7 @@
         <v/>
       </c>
       <c r="K25" s="25" t="str">
-        <f aca="false">IF(J25="","",SUMPRODUCT((I25=$I$6:$I$1500)*(B25&lt;$B$6:$B$1500))+SUMPRODUCT((I25=$I$6:$I$25)*(B25=$B$6:$B$25)))</f>
+        <f aca="false">IF(J25="","",SUMPRODUCT((I25=$I$6:$I$1500)*(B25&lt;$B$6:$B$1500))+COUNTIFS($I$6:I25,I25,$B$6:B25,B25))</f>
         <v/>
       </c>
       <c r="N25" s="33" t="s">
@@ -4063,7 +4063,7 @@
         <v/>
       </c>
       <c r="K26" s="25" t="str">
-        <f aca="false">IF(J26="","",SUMPRODUCT((I26=$I$6:$I$1500)*(B26&lt;$B$6:$B$1500))+SUMPRODUCT((I26=$I$6:$I$26)*(B26=$B$6:$B$26)))</f>
+        <f aca="false">IF(J26="","",SUMPRODUCT((I26=$I$6:$I$1500)*(B26&lt;$B$6:$B$1500))+COUNTIFS($I$6:I26,I26,$B$6:B26,B26))</f>
         <v/>
       </c>
       <c r="N26" s="33" t="s">
@@ -4130,7 +4130,7 @@
         <v/>
       </c>
       <c r="K27" s="25" t="str">
-        <f aca="false">IF(J27="","",SUMPRODUCT((I27=$I$6:$I$1500)*(B27&lt;$B$6:$B$1500))+SUMPRODUCT((I27=$I$6:$I$27)*(B27=$B$6:$B$27)))</f>
+        <f aca="false">IF(J27="","",SUMPRODUCT((I27=$I$6:$I$1500)*(B27&lt;$B$6:$B$1500))+COUNTIFS($I$6:I27,I27,$B$6:B27,B27))</f>
         <v/>
       </c>
       <c r="N27" s="33" t="s">
@@ -4197,7 +4197,7 @@
         <v/>
       </c>
       <c r="K28" s="25" t="str">
-        <f aca="false">IF(J28="","",SUMPRODUCT((I28=$I$6:$I$1500)*(B28&lt;$B$6:$B$1500))+SUMPRODUCT((I28=$I$6:$I$28)*(B28=$B$6:$B$28)))</f>
+        <f aca="false">IF(J28="","",SUMPRODUCT((I28=$I$6:$I$1500)*(B28&lt;$B$6:$B$1500))+COUNTIFS($I$6:I28,I28,$B$6:B28,B28))</f>
         <v/>
       </c>
       <c r="N28" s="33" t="s">
@@ -4247,7 +4247,7 @@
         <v/>
       </c>
       <c r="K29" s="25" t="str">
-        <f aca="false">IF(J29="","",SUMPRODUCT((I29=$I$6:$I$1500)*(B29&lt;$B$6:$B$1500))+SUMPRODUCT((I29=$I$6:$I$29)*(B29=$B$6:$B$29)))</f>
+        <f aca="false">IF(J29="","",SUMPRODUCT((I29=$I$6:$I$1500)*(B29&lt;$B$6:$B$1500))+COUNTIFS($I$6:I29,I29,$B$6:B29,B29))</f>
         <v/>
       </c>
       <c r="N29" s="33" t="s">
@@ -4305,7 +4305,7 @@
         <v/>
       </c>
       <c r="K30" s="25" t="str">
-        <f aca="false">IF(J30="","",SUMPRODUCT((I30=$I$6:$I$1500)*(B30&lt;$B$6:$B$1500))+SUMPRODUCT((I30=$I$6:$I$30)*(B30=$B$6:$B$30)))</f>
+        <f aca="false">IF(J30="","",SUMPRODUCT((I30=$I$6:$I$1500)*(B30&lt;$B$6:$B$1500))+COUNTIFS($I$6:I30,I30,$B$6:B30,B30))</f>
         <v/>
       </c>
       <c r="N30" s="33" t="s">
@@ -4349,7 +4349,7 @@
         <v/>
       </c>
       <c r="K31" s="25" t="str">
-        <f aca="false">IF(J31="","",SUMPRODUCT((I31=$I$6:$I$1500)*(B31&lt;$B$6:$B$1500))+SUMPRODUCT((I31=$I$6:$I$31)*(B31=$B$6:$B$31)))</f>
+        <f aca="false">IF(J31="","",SUMPRODUCT((I31=$I$6:$I$1500)*(B31&lt;$B$6:$B$1500))+COUNTIFS($I$6:I31,I31,$B$6:B31,B31))</f>
         <v/>
       </c>
       <c r="N31" s="33" t="s">
@@ -4393,7 +4393,7 @@
         <v/>
       </c>
       <c r="K32" s="25" t="str">
-        <f aca="false">IF(J32="","",SUMPRODUCT((I32=$I$6:$I$1500)*(B32&lt;$B$6:$B$1500))+SUMPRODUCT((I32=$I$6:$I$32)*(B32=$B$6:$B$32)))</f>
+        <f aca="false">IF(J32="","",SUMPRODUCT((I32=$I$6:$I$1500)*(B32&lt;$B$6:$B$1500))+COUNTIFS($I$6:I32,I32,$B$6:B32,B32))</f>
         <v/>
       </c>
       <c r="N32" s="33" t="s">
@@ -4437,7 +4437,7 @@
         <v/>
       </c>
       <c r="K33" s="25" t="str">
-        <f aca="false">IF(J33="","",SUMPRODUCT((I33=$I$6:$I$1500)*(B33&lt;$B$6:$B$1500))+SUMPRODUCT((I33=$I$6:$I$33)*(B33=$B$6:$B$33)))</f>
+        <f aca="false">IF(J33="","",SUMPRODUCT((I33=$I$6:$I$1500)*(B33&lt;$B$6:$B$1500))+COUNTIFS($I$6:I33,I33,$B$6:B33,B33))</f>
         <v/>
       </c>
       <c r="N33" s="33" t="s">
@@ -4481,7 +4481,7 @@
         <v/>
       </c>
       <c r="K34" s="25" t="str">
-        <f aca="false">IF(J34="","",SUMPRODUCT((I34=$I$6:$I$1500)*(B34&lt;$B$6:$B$1500))+SUMPRODUCT((I34=$I$6:$I$34)*(B34=$B$6:$B$34)))</f>
+        <f aca="false">IF(J34="","",SUMPRODUCT((I34=$I$6:$I$1500)*(B34&lt;$B$6:$B$1500))+COUNTIFS($I$6:I34,I34,$B$6:B34,B34))</f>
         <v/>
       </c>
       <c r="N34" s="33" t="s">
@@ -4525,7 +4525,7 @@
         <v/>
       </c>
       <c r="K35" s="25" t="str">
-        <f aca="false">IF(J35="","",SUMPRODUCT((I35=$I$6:$I$1500)*(B35&lt;$B$6:$B$1500))+SUMPRODUCT((I35=$I$6:$I$35)*(B35=$B$6:$B$35)))</f>
+        <f aca="false">IF(J35="","",SUMPRODUCT((I35=$I$6:$I$1500)*(B35&lt;$B$6:$B$1500))+COUNTIFS($I$6:I35,I35,$B$6:B35,B35))</f>
         <v/>
       </c>
       <c r="N35" s="33" t="s">
@@ -4569,7 +4569,7 @@
         <v/>
       </c>
       <c r="K36" s="25" t="str">
-        <f aca="false">IF(J36="","",SUMPRODUCT((I36=$I$6:$I$1500)*(B36&lt;$B$6:$B$1500))+SUMPRODUCT((I36=$I$6:$I$36)*(B36=$B$6:$B$36)))</f>
+        <f aca="false">IF(J36="","",SUMPRODUCT((I36=$I$6:$I$1500)*(B36&lt;$B$6:$B$1500))+COUNTIFS($I$6:I36,I36,$B$6:B36,B36))</f>
         <v/>
       </c>
       <c r="N36" s="33" t="s">
@@ -4613,7 +4613,7 @@
         <v/>
       </c>
       <c r="K37" s="25" t="str">
-        <f aca="false">IF(J37="","",SUMPRODUCT((I37=$I$6:$I$1500)*(B37&lt;$B$6:$B$1500))+SUMPRODUCT((I37=$I$6:$I$37)*(B37=$B$6:$B$37)))</f>
+        <f aca="false">IF(J37="","",SUMPRODUCT((I37=$I$6:$I$1500)*(B37&lt;$B$6:$B$1500))+COUNTIFS($I$6:I37,I37,$B$6:B37,B37))</f>
         <v/>
       </c>
       <c r="N37" s="33" t="s">
@@ -4657,7 +4657,7 @@
         <v/>
       </c>
       <c r="K38" s="25" t="str">
-        <f aca="false">IF(J38="","",SUMPRODUCT((I38=$I$6:$I$1500)*(B38&lt;$B$6:$B$1500))+SUMPRODUCT((I38=$I$6:$I$38)*(B38=$B$6:$B$38)))</f>
+        <f aca="false">IF(J38="","",SUMPRODUCT((I38=$I$6:$I$1500)*(B38&lt;$B$6:$B$1500))+COUNTIFS($I$6:I38,I38,$B$6:B38,B38))</f>
         <v/>
       </c>
       <c r="N38" s="33" t="s">
@@ -4701,7 +4701,7 @@
         <v/>
       </c>
       <c r="K39" s="25" t="str">
-        <f aca="false">IF(J39="","",SUMPRODUCT((I39=$I$6:$I$1500)*(B39&lt;$B$6:$B$1500))+SUMPRODUCT((I39=$I$6:$I$39)*(B39=$B$6:$B$39)))</f>
+        <f aca="false">IF(J39="","",SUMPRODUCT((I39=$I$6:$I$1500)*(B39&lt;$B$6:$B$1500))+COUNTIFS($I$6:I39,I39,$B$6:B39,B39))</f>
         <v/>
       </c>
       <c r="N39" s="33" t="s">
@@ -4745,7 +4745,7 @@
         <v/>
       </c>
       <c r="K40" s="25" t="str">
-        <f aca="false">IF(J40="","",SUMPRODUCT((I40=$I$6:$I$1500)*(B40&lt;$B$6:$B$1500))+SUMPRODUCT((I40=$I$6:$I$40)*(B40=$B$6:$B$40)))</f>
+        <f aca="false">IF(J40="","",SUMPRODUCT((I40=$I$6:$I$1500)*(B40&lt;$B$6:$B$1500))+COUNTIFS($I$6:I40,I40,$B$6:B40,B40))</f>
         <v/>
       </c>
       <c r="N40" s="33" t="s">
@@ -4789,7 +4789,7 @@
         <v/>
       </c>
       <c r="K41" s="25" t="str">
-        <f aca="false">IF(J41="","",SUMPRODUCT((I41=$I$6:$I$1500)*(B41&lt;$B$6:$B$1500))+SUMPRODUCT((I41=$I$6:$I$41)*(B41=$B$6:$B$41)))</f>
+        <f aca="false">IF(J41="","",SUMPRODUCT((I41=$I$6:$I$1500)*(B41&lt;$B$6:$B$1500))+COUNTIFS($I$6:I41,I41,$B$6:B41,B41))</f>
         <v/>
       </c>
       <c r="N41" s="33" t="s">
@@ -4833,7 +4833,7 @@
         <v/>
       </c>
       <c r="K42" s="25" t="str">
-        <f aca="false">IF(J42="","",SUMPRODUCT((I42=$I$6:$I$1500)*(B42&lt;$B$6:$B$1500))+SUMPRODUCT((I42=$I$6:$I$42)*(B42=$B$6:$B$42)))</f>
+        <f aca="false">IF(J42="","",SUMPRODUCT((I42=$I$6:$I$1500)*(B42&lt;$B$6:$B$1500))+COUNTIFS($I$6:I42,I42,$B$6:B42,B42))</f>
         <v/>
       </c>
       <c r="N42" s="33" t="s">
@@ -4877,7 +4877,7 @@
         <v/>
       </c>
       <c r="K43" s="25" t="str">
-        <f aca="false">IF(J43="","",SUMPRODUCT((I43=$I$6:$I$1500)*(B43&lt;$B$6:$B$1500))+SUMPRODUCT((I43=$I$6:$I$43)*(B43=$B$6:$B$43)))</f>
+        <f aca="false">IF(J43="","",SUMPRODUCT((I43=$I$6:$I$1500)*(B43&lt;$B$6:$B$1500))+COUNTIFS($I$6:I43,I43,$B$6:B43,B43))</f>
         <v/>
       </c>
       <c r="N43" s="33" t="s">
@@ -4921,7 +4921,7 @@
         <v/>
       </c>
       <c r="K44" s="25" t="str">
-        <f aca="false">IF(J44="","",SUMPRODUCT((I44=$I$6:$I$1500)*(B44&lt;$B$6:$B$1500))+SUMPRODUCT((I44=$I$6:$I$44)*(B44=$B$6:$B$44)))</f>
+        <f aca="false">IF(J44="","",SUMPRODUCT((I44=$I$6:$I$1500)*(B44&lt;$B$6:$B$1500))+COUNTIFS($I$6:I44,I44,$B$6:B44,B44))</f>
         <v/>
       </c>
       <c r="N44" s="33" t="s">
@@ -4965,7 +4965,7 @@
         <v/>
       </c>
       <c r="K45" s="25" t="str">
-        <f aca="false">IF(J45="","",SUMPRODUCT((I45=$I$6:$I$1500)*(B45&lt;$B$6:$B$1500))+SUMPRODUCT((I45=$I$6:$I$45)*(B45=$B$6:$B$45)))</f>
+        <f aca="false">IF(J45="","",SUMPRODUCT((I45=$I$6:$I$1500)*(B45&lt;$B$6:$B$1500))+COUNTIFS($I$6:I45,I45,$B$6:B45,B45))</f>
         <v/>
       </c>
       <c r="N45" s="33" t="s">
@@ -5009,7 +5009,7 @@
         <v/>
       </c>
       <c r="K46" s="25" t="str">
-        <f aca="false">IF(J46="","",SUMPRODUCT((I46=$I$6:$I$1500)*(B46&lt;$B$6:$B$1500))+SUMPRODUCT((I46=$I$6:$I$46)*(B46=$B$6:$B$46)))</f>
+        <f aca="false">IF(J46="","",SUMPRODUCT((I46=$I$6:$I$1500)*(B46&lt;$B$6:$B$1500))+COUNTIFS($I$6:I46,I46,$B$6:B46,B46))</f>
         <v/>
       </c>
       <c r="N46" s="33" t="s">
@@ -5053,7 +5053,7 @@
         <v/>
       </c>
       <c r="K47" s="25" t="str">
-        <f aca="false">IF(J47="","",SUMPRODUCT((I47=$I$6:$I$1500)*(B47&lt;$B$6:$B$1500))+SUMPRODUCT((I47=$I$6:$I$47)*(B47=$B$6:$B$47)))</f>
+        <f aca="false">IF(J47="","",SUMPRODUCT((I47=$I$6:$I$1500)*(B47&lt;$B$6:$B$1500))+COUNTIFS($I$6:I47,I47,$B$6:B47,B47))</f>
         <v/>
       </c>
       <c r="N47" s="33" t="s">
@@ -5097,7 +5097,7 @@
         <v/>
       </c>
       <c r="K48" s="25" t="str">
-        <f aca="false">IF(J48="","",SUMPRODUCT((I48=$I$6:$I$1500)*(B48&lt;$B$6:$B$1500))+SUMPRODUCT((I48=$I$6:$I$48)*(B48=$B$6:$B$48)))</f>
+        <f aca="false">IF(J48="","",SUMPRODUCT((I48=$I$6:$I$1500)*(B48&lt;$B$6:$B$1500))+COUNTIFS($I$6:I48,I48,$B$6:B48,B48))</f>
         <v/>
       </c>
       <c r="N48" s="33" t="s">
@@ -5141,7 +5141,7 @@
         <v/>
       </c>
       <c r="K49" s="25" t="str">
-        <f aca="false">IF(J49="","",SUMPRODUCT((I49=$I$6:$I$1500)*(B49&lt;$B$6:$B$1500))+SUMPRODUCT((I49=$I$6:$I$49)*(B49=$B$6:$B$49)))</f>
+        <f aca="false">IF(J49="","",SUMPRODUCT((I49=$I$6:$I$1500)*(B49&lt;$B$6:$B$1500))+COUNTIFS($I$6:I49,I49,$B$6:B49,B49))</f>
         <v/>
       </c>
       <c r="N49" s="33" t="s">
@@ -5185,7 +5185,7 @@
         <v/>
       </c>
       <c r="K50" s="25" t="str">
-        <f aca="false">IF(J50="","",SUMPRODUCT((I50=$I$6:$I$1500)*(B50&lt;$B$6:$B$1500))+SUMPRODUCT((I50=$I$6:$I$50)*(B50=$B$6:$B$50)))</f>
+        <f aca="false">IF(J50="","",SUMPRODUCT((I50=$I$6:$I$1500)*(B50&lt;$B$6:$B$1500))+COUNTIFS($I$6:I50,I50,$B$6:B50,B50))</f>
         <v/>
       </c>
       <c r="N50" s="33" t="s">
@@ -5229,7 +5229,7 @@
         <v/>
       </c>
       <c r="K51" s="25" t="str">
-        <f aca="false">IF(J51="","",SUMPRODUCT((I51=$I$6:$I$1500)*(B51&lt;$B$6:$B$1500))+SUMPRODUCT((I51=$I$6:$I$51)*(B51=$B$6:$B$51)))</f>
+        <f aca="false">IF(J51="","",SUMPRODUCT((I51=$I$6:$I$1500)*(B51&lt;$B$6:$B$1500))+COUNTIFS($I$6:I51,I51,$B$6:B51,B51))</f>
         <v/>
       </c>
       <c r="N51" s="33" t="s">
@@ -5273,7 +5273,7 @@
         <v/>
       </c>
       <c r="K52" s="25" t="str">
-        <f aca="false">IF(J52="","",SUMPRODUCT((I52=$I$6:$I$1500)*(B52&lt;$B$6:$B$1500))+SUMPRODUCT((I52=$I$6:$I$52)*(B52=$B$6:$B$52)))</f>
+        <f aca="false">IF(J52="","",SUMPRODUCT((I52=$I$6:$I$1500)*(B52&lt;$B$6:$B$1500))+COUNTIFS($I$6:I52,I52,$B$6:B52,B52))</f>
         <v/>
       </c>
       <c r="N52" s="33" t="s">
@@ -5317,7 +5317,7 @@
         <v/>
       </c>
       <c r="K53" s="25" t="str">
-        <f aca="false">IF(J53="","",SUMPRODUCT((I53=$I$6:$I$1500)*(B53&lt;$B$6:$B$1500))+SUMPRODUCT((I53=$I$6:$I$53)*(B53=$B$6:$B$53)))</f>
+        <f aca="false">IF(J53="","",SUMPRODUCT((I53=$I$6:$I$1500)*(B53&lt;$B$6:$B$1500))+COUNTIFS($I$6:I53,I53,$B$6:B53,B53))</f>
         <v/>
       </c>
       <c r="N53" s="33" t="s">
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="K54" s="25" t="str">
-        <f aca="false">IF(J54="","",SUMPRODUCT((I54=$I$6:$I$1500)*(B54&lt;$B$6:$B$1500))+SUMPRODUCT((I54=$I$6:$I$54)*(B54=$B$6:$B$54)))</f>
+        <f aca="false">IF(J54="","",SUMPRODUCT((I54=$I$6:$I$1500)*(B54&lt;$B$6:$B$1500))+COUNTIFS($I$6:I54,I54,$B$6:B54,B54))</f>
         <v/>
       </c>
       <c r="N54" s="33" t="s">
@@ -5405,7 +5405,7 @@
         <v/>
       </c>
       <c r="K55" s="25" t="str">
-        <f aca="false">IF(J55="","",SUMPRODUCT((I55=$I$6:$I$1500)*(B55&lt;$B$6:$B$1500))+SUMPRODUCT((I55=$I$6:$I$55)*(B55=$B$6:$B$55)))</f>
+        <f aca="false">IF(J55="","",SUMPRODUCT((I55=$I$6:$I$1500)*(B55&lt;$B$6:$B$1500))+COUNTIFS($I$6:I55,I55,$B$6:B55,B55))</f>
         <v/>
       </c>
       <c r="N55" s="33" t="s">
@@ -5449,7 +5449,7 @@
         <v/>
       </c>
       <c r="K56" s="25" t="str">
-        <f aca="false">IF(J56="","",SUMPRODUCT((I56=$I$6:$I$1500)*(B56&lt;$B$6:$B$1500))+SUMPRODUCT((I56=$I$6:$I$56)*(B56=$B$6:$B$56)))</f>
+        <f aca="false">IF(J56="","",SUMPRODUCT((I56=$I$6:$I$1500)*(B56&lt;$B$6:$B$1500))+COUNTIFS($I$6:I56,I56,$B$6:B56,B56))</f>
         <v/>
       </c>
       <c r="N56" s="33" t="s">
@@ -5493,7 +5493,7 @@
         <v/>
       </c>
       <c r="K57" s="25" t="str">
-        <f aca="false">IF(J57="","",SUMPRODUCT((I57=$I$6:$I$1500)*(B57&lt;$B$6:$B$1500))+SUMPRODUCT((I57=$I$6:$I$57)*(B57=$B$6:$B$57)))</f>
+        <f aca="false">IF(J57="","",SUMPRODUCT((I57=$I$6:$I$1500)*(B57&lt;$B$6:$B$1500))+COUNTIFS($I$6:I57,I57,$B$6:B57,B57))</f>
         <v/>
       </c>
       <c r="N57" s="33" t="s">
@@ -5535,7 +5535,7 @@
         <v/>
       </c>
       <c r="K58" s="25" t="str">
-        <f aca="false">IF(J58="","",SUMPRODUCT((I58=$I$6:$I$1500)*(B58&lt;$B$6:$B$1500))+SUMPRODUCT((I58=$I$6:$I$58)*(B58=$B$6:$B$58)))</f>
+        <f aca="false">IF(J58="","",SUMPRODUCT((I58=$I$6:$I$1500)*(B58&lt;$B$6:$B$1500))+COUNTIFS($I$6:I58,I58,$B$6:B58,B58))</f>
         <v/>
       </c>
       <c r="N58" s="33" t="s">
@@ -5579,7 +5579,7 @@
         <v/>
       </c>
       <c r="K59" s="25" t="str">
-        <f aca="false">IF(J59="","",SUMPRODUCT((I59=$I$6:$I$1500)*(B59&lt;$B$6:$B$1500))+SUMPRODUCT((I59=$I$6:$I$59)*(B59=$B$6:$B$59)))</f>
+        <f aca="false">IF(J59="","",SUMPRODUCT((I59=$I$6:$I$1500)*(B59&lt;$B$6:$B$1500))+COUNTIFS($I$6:I59,I59,$B$6:B59,B59))</f>
         <v/>
       </c>
       <c r="N59" s="33" t="s">
@@ -5623,7 +5623,7 @@
         <v/>
       </c>
       <c r="K60" s="25" t="str">
-        <f aca="false">IF(J60="","",SUMPRODUCT((I60=$I$6:$I$1500)*(B60&lt;$B$6:$B$1500))+SUMPRODUCT((I60=$I$6:$I$60)*(B60=$B$6:$B$60)))</f>
+        <f aca="false">IF(J60="","",SUMPRODUCT((I60=$I$6:$I$1500)*(B60&lt;$B$6:$B$1500))+COUNTIFS($I$6:I60,I60,$B$6:B60,B60))</f>
         <v/>
       </c>
       <c r="N60" s="33" t="s">
@@ -5667,7 +5667,7 @@
         <v/>
       </c>
       <c r="K61" s="25" t="str">
-        <f aca="false">IF(J61="","",SUMPRODUCT((I61=$I$6:$I$1500)*(B61&lt;$B$6:$B$1500))+SUMPRODUCT((I61=$I$6:$I$61)*(B61=$B$6:$B$61)))</f>
+        <f aca="false">IF(J61="","",SUMPRODUCT((I61=$I$6:$I$1500)*(B61&lt;$B$6:$B$1500))+COUNTIFS($I$6:I61,I61,$B$6:B61,B61))</f>
         <v/>
       </c>
       <c r="N61" s="33" t="s">
@@ -5711,7 +5711,7 @@
         <v/>
       </c>
       <c r="K62" s="25" t="str">
-        <f aca="false">IF(J62="","",SUMPRODUCT((I62=$I$6:$I$1500)*(B62&lt;$B$6:$B$1500))+SUMPRODUCT((I62=$I$6:$I$62)*(B62=$B$6:$B$62)))</f>
+        <f aca="false">IF(J62="","",SUMPRODUCT((I62=$I$6:$I$1500)*(B62&lt;$B$6:$B$1500))+COUNTIFS($I$6:I62,I62,$B$6:B62,B62))</f>
         <v/>
       </c>
       <c r="N62" s="52" t="s">
@@ -5755,7 +5755,7 @@
         <v/>
       </c>
       <c r="K63" s="25" t="str">
-        <f aca="false">IF(J63="","",SUMPRODUCT((I63=$I$6:$I$1500)*(B63&lt;$B$6:$B$1500))+SUMPRODUCT((I63=$I$6:$I$63)*(B63=$B$6:$B$63)))</f>
+        <f aca="false">IF(J63="","",SUMPRODUCT((I63=$I$6:$I$1500)*(B63&lt;$B$6:$B$1500))+COUNTIFS($I$6:I63,I63,$B$6:B63,B63))</f>
         <v/>
       </c>
       <c r="N63" s="33" t="s">
@@ -5799,7 +5799,7 @@
         <v/>
       </c>
       <c r="K64" s="25" t="str">
-        <f aca="false">IF(J64="","",SUMPRODUCT((I64=$I$6:$I$1500)*(B64&lt;$B$6:$B$1500))+SUMPRODUCT((I64=$I$6:$I$64)*(B64=$B$6:$B$64)))</f>
+        <f aca="false">IF(J64="","",SUMPRODUCT((I64=$I$6:$I$1500)*(B64&lt;$B$6:$B$1500))+COUNTIFS($I$6:I64,I64,$B$6:B64,B64))</f>
         <v/>
       </c>
       <c r="N64" s="33" t="s">
@@ -5843,7 +5843,7 @@
         <v/>
       </c>
       <c r="K65" s="25" t="str">
-        <f aca="false">IF(J65="","",SUMPRODUCT((I65=$I$6:$I$1500)*(B65&lt;$B$6:$B$1500))+SUMPRODUCT((I65=$I$6:$I$65)*(B65=$B$6:$B$65)))</f>
+        <f aca="false">IF(J65="","",SUMPRODUCT((I65=$I$6:$I$1500)*(B65&lt;$B$6:$B$1500))+COUNTIFS($I$6:I65,I65,$B$6:B65,B65))</f>
         <v/>
       </c>
       <c r="N65" s="33" t="s">
@@ -5887,7 +5887,7 @@
         <v/>
       </c>
       <c r="K66" s="25" t="str">
-        <f aca="false">IF(J66="","",SUMPRODUCT((I66=$I$6:$I$1500)*(B66&lt;$B$6:$B$1500))+SUMPRODUCT((I66=$I$6:$I$66)*(B66=$B$6:$B$66)))</f>
+        <f aca="false">IF(J66="","",SUMPRODUCT((I66=$I$6:$I$1500)*(B66&lt;$B$6:$B$1500))+COUNTIFS($I$6:I66,I66,$B$6:B66,B66))</f>
         <v/>
       </c>
       <c r="N66" s="33" t="s">
@@ -5931,7 +5931,7 @@
         <v/>
       </c>
       <c r="K67" s="25" t="str">
-        <f aca="false">IF(J67="","",SUMPRODUCT((I67=$I$6:$I$1500)*(B67&lt;$B$6:$B$1500))+SUMPRODUCT((I67=$I$6:$I$67)*(B67=$B$6:$B$67)))</f>
+        <f aca="false">IF(J67="","",SUMPRODUCT((I67=$I$6:$I$1500)*(B67&lt;$B$6:$B$1500))+COUNTIFS($I$6:I67,I67,$B$6:B67,B67))</f>
         <v/>
       </c>
       <c r="N67" s="33" t="s">
@@ -5975,7 +5975,7 @@
         <v/>
       </c>
       <c r="K68" s="25" t="str">
-        <f aca="false">IF(J68="","",SUMPRODUCT((I68=$I$6:$I$1500)*(B68&lt;$B$6:$B$1500))+SUMPRODUCT((I68=$I$6:$I$68)*(B68=$B$6:$B$68)))</f>
+        <f aca="false">IF(J68="","",SUMPRODUCT((I68=$I$6:$I$1500)*(B68&lt;$B$6:$B$1500))+COUNTIFS($I$6:I68,I68,$B$6:B68,B68))</f>
         <v/>
       </c>
       <c r="N68" s="33" t="s">
@@ -6019,7 +6019,7 @@
         <v/>
       </c>
       <c r="K69" s="25" t="str">
-        <f aca="false">IF(J69="","",SUMPRODUCT((I69=$I$6:$I$1500)*(B69&lt;$B$6:$B$1500))+SUMPRODUCT((I69=$I$6:$I$69)*(B69=$B$6:$B$69)))</f>
+        <f aca="false">IF(J69="","",SUMPRODUCT((I69=$I$6:$I$1500)*(B69&lt;$B$6:$B$1500))+COUNTIFS($I$6:I69,I69,$B$6:B69,B69))</f>
         <v/>
       </c>
       <c r="N69" s="33" t="s">
@@ -6063,7 +6063,7 @@
         <v/>
       </c>
       <c r="K70" s="25" t="str">
-        <f aca="false">IF(J70="","",SUMPRODUCT((I70=$I$6:$I$1500)*(B70&lt;$B$6:$B$1500))+SUMPRODUCT((I70=$I$6:$I$70)*(B70=$B$6:$B$70)))</f>
+        <f aca="false">IF(J70="","",SUMPRODUCT((I70=$I$6:$I$1500)*(B70&lt;$B$6:$B$1500))+COUNTIFS($I$6:I70,I70,$B$6:B70,B70))</f>
         <v/>
       </c>
       <c r="N70" s="33" t="s">
@@ -6107,7 +6107,7 @@
         <v/>
       </c>
       <c r="K71" s="25" t="str">
-        <f aca="false">IF(J71="","",SUMPRODUCT((I71=$I$6:$I$1500)*(B71&lt;$B$6:$B$1500))+SUMPRODUCT((I71=$I$6:$I$71)*(B71=$B$6:$B$71)))</f>
+        <f aca="false">IF(J71="","",SUMPRODUCT((I71=$I$6:$I$1500)*(B71&lt;$B$6:$B$1500))+COUNTIFS($I$6:I71,I71,$B$6:B71,B71))</f>
         <v/>
       </c>
       <c r="N71" s="33" t="s">
@@ -6151,7 +6151,7 @@
         <v/>
       </c>
       <c r="K72" s="25" t="str">
-        <f aca="false">IF(J72="","",SUMPRODUCT((I72=$I$6:$I$1500)*(B72&lt;$B$6:$B$1500))+SUMPRODUCT((I72=$I$6:$I$72)*(B72=$B$6:$B$72)))</f>
+        <f aca="false">IF(J72="","",SUMPRODUCT((I72=$I$6:$I$1500)*(B72&lt;$B$6:$B$1500))+COUNTIFS($I$6:I72,I72,$B$6:B72,B72))</f>
         <v/>
       </c>
       <c r="N72" s="33" t="s">
@@ -6195,7 +6195,7 @@
         <v/>
       </c>
       <c r="K73" s="25" t="str">
-        <f aca="false">IF(J73="","",SUMPRODUCT((I73=$I$6:$I$1500)*(B73&lt;$B$6:$B$1500))+SUMPRODUCT((I73=$I$6:$I$73)*(B73=$B$6:$B$73)))</f>
+        <f aca="false">IF(J73="","",SUMPRODUCT((I73=$I$6:$I$1500)*(B73&lt;$B$6:$B$1500))+COUNTIFS($I$6:I73,I73,$B$6:B73,B73))</f>
         <v/>
       </c>
       <c r="N73" s="33" t="s">
@@ -6239,7 +6239,7 @@
         <v/>
       </c>
       <c r="K74" s="25" t="str">
-        <f aca="false">IF(J74="","",SUMPRODUCT((I74=$I$6:$I$1500)*(B74&lt;$B$6:$B$1500))+SUMPRODUCT((I74=$I$6:$I$74)*(B74=$B$6:$B$74)))</f>
+        <f aca="false">IF(J74="","",SUMPRODUCT((I74=$I$6:$I$1500)*(B74&lt;$B$6:$B$1500))+COUNTIFS($I$6:I74,I74,$B$6:B74,B74))</f>
         <v/>
       </c>
       <c r="N74" s="33" t="s">
@@ -6283,7 +6283,7 @@
         <v/>
       </c>
       <c r="K75" s="25" t="str">
-        <f aca="false">IF(J75="","",SUMPRODUCT((I75=$I$6:$I$1500)*(B75&lt;$B$6:$B$1500))+SUMPRODUCT((I75=$I$6:$I$75)*(B75=$B$6:$B$75)))</f>
+        <f aca="false">IF(J75="","",SUMPRODUCT((I75=$I$6:$I$1500)*(B75&lt;$B$6:$B$1500))+COUNTIFS($I$6:I75,I75,$B$6:B75,B75))</f>
         <v/>
       </c>
       <c r="N75" s="33" t="s">
@@ -6327,7 +6327,7 @@
         <v/>
       </c>
       <c r="K76" s="25" t="str">
-        <f aca="false">IF(J76="","",SUMPRODUCT((I76=$I$6:$I$1500)*(B76&lt;$B$6:$B$1500))+SUMPRODUCT((I76=$I$6:$I$76)*(B76=$B$6:$B$76)))</f>
+        <f aca="false">IF(J76="","",SUMPRODUCT((I76=$I$6:$I$1500)*(B76&lt;$B$6:$B$1500))+COUNTIFS($I$6:I76,I76,$B$6:B76,B76))</f>
         <v/>
       </c>
       <c r="N76" s="33" t="s">
@@ -6371,7 +6371,7 @@
         <v/>
       </c>
       <c r="K77" s="25" t="str">
-        <f aca="false">IF(J77="","",SUMPRODUCT((I77=$I$6:$I$1500)*(B77&lt;$B$6:$B$1500))+SUMPRODUCT((I77=$I$6:$I$77)*(B77=$B$6:$B$77)))</f>
+        <f aca="false">IF(J77="","",SUMPRODUCT((I77=$I$6:$I$1500)*(B77&lt;$B$6:$B$1500))+COUNTIFS($I$6:I77,I77,$B$6:B77,B77))</f>
         <v/>
       </c>
       <c r="N77" s="33" t="s">
@@ -6415,7 +6415,7 @@
         <v/>
       </c>
       <c r="K78" s="25" t="str">
-        <f aca="false">IF(J78="","",SUMPRODUCT((I78=$I$6:$I$1500)*(B78&lt;$B$6:$B$1500))+SUMPRODUCT((I78=$I$6:$I$78)*(B78=$B$6:$B$78)))</f>
+        <f aca="false">IF(J78="","",SUMPRODUCT((I78=$I$6:$I$1500)*(B78&lt;$B$6:$B$1500))+COUNTIFS($I$6:I78,I78,$B$6:B78,B78))</f>
         <v/>
       </c>
       <c r="N78" s="33" t="s">
@@ -6459,7 +6459,7 @@
         <v/>
       </c>
       <c r="K79" s="25" t="str">
-        <f aca="false">IF(J79="","",SUMPRODUCT((I79=$I$6:$I$1500)*(B79&lt;$B$6:$B$1500))+SUMPRODUCT((I79=$I$6:$I$79)*(B79=$B$6:$B$79)))</f>
+        <f aca="false">IF(J79="","",SUMPRODUCT((I79=$I$6:$I$1500)*(B79&lt;$B$6:$B$1500))+COUNTIFS($I$6:I79,I79,$B$6:B79,B79))</f>
         <v/>
       </c>
       <c r="N79" s="33" t="s">
@@ -6503,7 +6503,7 @@
         <v/>
       </c>
       <c r="K80" s="25" t="str">
-        <f aca="false">IF(J80="","",SUMPRODUCT((I80=$I$6:$I$1500)*(B80&lt;$B$6:$B$1500))+SUMPRODUCT((I80=$I$6:$I$80)*(B80=$B$6:$B$80)))</f>
+        <f aca="false">IF(J80="","",SUMPRODUCT((I80=$I$6:$I$1500)*(B80&lt;$B$6:$B$1500))+COUNTIFS($I$6:I80,I80,$B$6:B80,B80))</f>
         <v/>
       </c>
       <c r="N80" s="33" t="s">
@@ -6547,7 +6547,7 @@
         <v/>
       </c>
       <c r="K81" s="25" t="str">
-        <f aca="false">IF(J81="","",SUMPRODUCT((I81=$I$6:$I$1500)*(B81&lt;$B$6:$B$1500))+SUMPRODUCT((I81=$I$6:$I$81)*(B81=$B$6:$B$81)))</f>
+        <f aca="false">IF(J81="","",SUMPRODUCT((I81=$I$6:$I$1500)*(B81&lt;$B$6:$B$1500))+COUNTIFS($I$6:I81,I81,$B$6:B81,B81))</f>
         <v/>
       </c>
       <c r="N81" s="33" t="s">
@@ -6591,7 +6591,7 @@
         <v/>
       </c>
       <c r="K82" s="25" t="str">
-        <f aca="false">IF(J82="","",SUMPRODUCT((I82=$I$6:$I$1500)*(B82&lt;$B$6:$B$1500))+SUMPRODUCT((I82=$I$6:$I$82)*(B82=$B$6:$B$82)))</f>
+        <f aca="false">IF(J82="","",SUMPRODUCT((I82=$I$6:$I$1500)*(B82&lt;$B$6:$B$1500))+COUNTIFS($I$6:I82,I82,$B$6:B82,B82))</f>
         <v/>
       </c>
       <c r="N82" s="33" t="s">
@@ -6635,7 +6635,7 @@
         <v/>
       </c>
       <c r="K83" s="25" t="str">
-        <f aca="false">IF(J83="","",SUMPRODUCT((I83=$I$6:$I$1500)*(B83&lt;$B$6:$B$1500))+SUMPRODUCT((I83=$I$6:$I$83)*(B83=$B$6:$B$83)))</f>
+        <f aca="false">IF(J83="","",SUMPRODUCT((I83=$I$6:$I$1500)*(B83&lt;$B$6:$B$1500))+COUNTIFS($I$6:I83,I83,$B$6:B83,B83))</f>
         <v/>
       </c>
       <c r="N83" s="33" t="s">
@@ -6679,7 +6679,7 @@
         <v/>
       </c>
       <c r="K84" s="25" t="str">
-        <f aca="false">IF(J84="","",SUMPRODUCT((I84=$I$6:$I$1500)*(B84&lt;$B$6:$B$1500))+SUMPRODUCT((I84=$I$6:$I$84)*(B84=$B$6:$B$84)))</f>
+        <f aca="false">IF(J84="","",SUMPRODUCT((I84=$I$6:$I$1500)*(B84&lt;$B$6:$B$1500))+COUNTIFS($I$6:I84,I84,$B$6:B84,B84))</f>
         <v/>
       </c>
       <c r="N84" s="33" t="s">
@@ -6723,7 +6723,7 @@
         <v/>
       </c>
       <c r="K85" s="25" t="str">
-        <f aca="false">IF(J85="","",SUMPRODUCT((I85=$I$6:$I$1500)*(B85&lt;$B$6:$B$1500))+SUMPRODUCT((I85=$I$6:$I$85)*(B85=$B$6:$B$85)))</f>
+        <f aca="false">IF(J85="","",SUMPRODUCT((I85=$I$6:$I$1500)*(B85&lt;$B$6:$B$1500))+COUNTIFS($I$6:I85,I85,$B$6:B85,B85))</f>
         <v/>
       </c>
       <c r="N85" s="33" t="s">
@@ -6767,7 +6767,7 @@
         <v/>
       </c>
       <c r="K86" s="25" t="str">
-        <f aca="false">IF(J86="","",SUMPRODUCT((I86=$I$6:$I$1500)*(B86&lt;$B$6:$B$1500))+SUMPRODUCT((I86=$I$6:$I$86)*(B86=$B$6:$B$86)))</f>
+        <f aca="false">IF(J86="","",SUMPRODUCT((I86=$I$6:$I$1500)*(B86&lt;$B$6:$B$1500))+COUNTIFS($I$6:I86,I86,$B$6:B86,B86))</f>
         <v/>
       </c>
       <c r="N86" s="33" t="s">
@@ -6811,7 +6811,7 @@
         <v/>
       </c>
       <c r="K87" s="25" t="str">
-        <f aca="false">IF(J87="","",SUMPRODUCT((I87=$I$6:$I$1500)*(B87&lt;$B$6:$B$1500))+SUMPRODUCT((I87=$I$6:$I$87)*(B87=$B$6:$B$87)))</f>
+        <f aca="false">IF(J87="","",SUMPRODUCT((I87=$I$6:$I$1500)*(B87&lt;$B$6:$B$1500))+COUNTIFS($I$6:I87,I87,$B$6:B87,B87))</f>
         <v/>
       </c>
       <c r="N87" s="33" t="s">
@@ -6855,7 +6855,7 @@
         <v/>
       </c>
       <c r="K88" s="25" t="str">
-        <f aca="false">IF(J88="","",SUMPRODUCT((I88=$I$6:$I$1500)*(B88&lt;$B$6:$B$1500))+SUMPRODUCT((I88=$I$6:$I$88)*(B88=$B$6:$B$88)))</f>
+        <f aca="false">IF(J88="","",SUMPRODUCT((I88=$I$6:$I$1500)*(B88&lt;$B$6:$B$1500))+COUNTIFS($I$6:I88,I88,$B$6:B88,B88))</f>
         <v/>
       </c>
       <c r="N88" s="33" t="s">
@@ -6899,7 +6899,7 @@
         <v/>
       </c>
       <c r="K89" s="25" t="str">
-        <f aca="false">IF(J89="","",SUMPRODUCT((I89=$I$6:$I$1500)*(B89&lt;$B$6:$B$1500))+SUMPRODUCT((I89=$I$6:$I$89)*(B89=$B$6:$B$89)))</f>
+        <f aca="false">IF(J89="","",SUMPRODUCT((I89=$I$6:$I$1500)*(B89&lt;$B$6:$B$1500))+COUNTIFS($I$6:I89,I89,$B$6:B89,B89))</f>
         <v/>
       </c>
       <c r="N89" s="33" t="s">
@@ -6943,7 +6943,7 @@
         <v/>
       </c>
       <c r="K90" s="25" t="str">
-        <f aca="false">IF(J90="","",SUMPRODUCT((I90=$I$6:$I$1500)*(B90&lt;$B$6:$B$1500))+SUMPRODUCT((I90=$I$6:$I$90)*(B90=$B$6:$B$90)))</f>
+        <f aca="false">IF(J90="","",SUMPRODUCT((I90=$I$6:$I$1500)*(B90&lt;$B$6:$B$1500))+COUNTIFS($I$6:I90,I90,$B$6:B90,B90))</f>
         <v/>
       </c>
       <c r="N90" s="33" t="s">
@@ -6987,7 +6987,7 @@
         <v/>
       </c>
       <c r="K91" s="25" t="str">
-        <f aca="false">IF(J91="","",SUMPRODUCT((I91=$I$6:$I$1500)*(B91&lt;$B$6:$B$1500))+SUMPRODUCT((I91=$I$6:$I$91)*(B91=$B$6:$B$91)))</f>
+        <f aca="false">IF(J91="","",SUMPRODUCT((I91=$I$6:$I$1500)*(B91&lt;$B$6:$B$1500))+COUNTIFS($I$6:I91,I91,$B$6:B91,B91))</f>
         <v/>
       </c>
       <c r="N91" s="52" t="s">
@@ -7031,7 +7031,7 @@
         <v/>
       </c>
       <c r="K92" s="25" t="str">
-        <f aca="false">IF(J92="","",SUMPRODUCT((I92=$I$6:$I$1500)*(B92&lt;$B$6:$B$1500))+SUMPRODUCT((I92=$I$6:$I$92)*(B92=$B$6:$B$92)))</f>
+        <f aca="false">IF(J92="","",SUMPRODUCT((I92=$I$6:$I$1500)*(B92&lt;$B$6:$B$1500))+COUNTIFS($I$6:I92,I92,$B$6:B92,B92))</f>
         <v/>
       </c>
       <c r="N92" s="33" t="s">
@@ -7075,7 +7075,7 @@
         <v/>
       </c>
       <c r="K93" s="25" t="str">
-        <f aca="false">IF(J93="","",SUMPRODUCT((I93=$I$6:$I$1500)*(B93&lt;$B$6:$B$1500))+SUMPRODUCT((I93=$I$6:$I$93)*(B93=$B$6:$B$93)))</f>
+        <f aca="false">IF(J93="","",SUMPRODUCT((I93=$I$6:$I$1500)*(B93&lt;$B$6:$B$1500))+COUNTIFS($I$6:I93,I93,$B$6:B93,B93))</f>
         <v/>
       </c>
       <c r="N93" s="33" t="s">
@@ -7119,7 +7119,7 @@
         <v/>
       </c>
       <c r="K94" s="25" t="str">
-        <f aca="false">IF(J94="","",SUMPRODUCT((I94=$I$6:$I$1500)*(B94&lt;$B$6:$B$1500))+SUMPRODUCT((I94=$I$6:$I$94)*(B94=$B$6:$B$94)))</f>
+        <f aca="false">IF(J94="","",SUMPRODUCT((I94=$I$6:$I$1500)*(B94&lt;$B$6:$B$1500))+COUNTIFS($I$6:I94,I94,$B$6:B94,B94))</f>
         <v/>
       </c>
       <c r="N94" s="33" t="s">
@@ -7163,7 +7163,7 @@
         <v/>
       </c>
       <c r="K95" s="25" t="str">
-        <f aca="false">IF(J95="","",SUMPRODUCT((I95=$I$6:$I$1500)*(B95&lt;$B$6:$B$1500))+SUMPRODUCT((I95=$I$6:$I$95)*(B95=$B$6:$B$95)))</f>
+        <f aca="false">IF(J95="","",SUMPRODUCT((I95=$I$6:$I$1500)*(B95&lt;$B$6:$B$1500))+COUNTIFS($I$6:I95,I95,$B$6:B95,B95))</f>
         <v/>
       </c>
       <c r="N95" s="33" t="s">
@@ -7207,7 +7207,7 @@
         <v/>
       </c>
       <c r="K96" s="25" t="str">
-        <f aca="false">IF(J96="","",SUMPRODUCT((I96=$I$6:$I$1500)*(B96&lt;$B$6:$B$1500))+SUMPRODUCT((I96=$I$6:$I$96)*(B96=$B$6:$B$96)))</f>
+        <f aca="false">IF(J96="","",SUMPRODUCT((I96=$I$6:$I$1500)*(B96&lt;$B$6:$B$1500))+COUNTIFS($I$6:I96,I96,$B$6:B96,B96))</f>
         <v/>
       </c>
       <c r="N96" s="33" t="s">
@@ -7251,7 +7251,7 @@
         <v/>
       </c>
       <c r="K97" s="25" t="str">
-        <f aca="false">IF(J97="","",SUMPRODUCT((I97=$I$6:$I$1500)*(B97&lt;$B$6:$B$1500))+SUMPRODUCT((I97=$I$6:$I$97)*(B97=$B$6:$B$97)))</f>
+        <f aca="false">IF(J97="","",SUMPRODUCT((I97=$I$6:$I$1500)*(B97&lt;$B$6:$B$1500))+COUNTIFS($I$6:I97,I97,$B$6:B97,B97))</f>
         <v/>
       </c>
       <c r="N97" s="33" t="s">
@@ -7295,7 +7295,7 @@
         <v/>
       </c>
       <c r="K98" s="25" t="str">
-        <f aca="false">IF(J98="","",SUMPRODUCT((I98=$I$6:$I$1500)*(B98&lt;$B$6:$B$1500))+SUMPRODUCT((I98=$I$6:$I$98)*(B98=$B$6:$B$98)))</f>
+        <f aca="false">IF(J98="","",SUMPRODUCT((I98=$I$6:$I$1500)*(B98&lt;$B$6:$B$1500))+COUNTIFS($I$6:I98,I98,$B$6:B98,B98))</f>
         <v/>
       </c>
       <c r="N98" s="33" t="s">
@@ -7339,7 +7339,7 @@
         <v/>
       </c>
       <c r="K99" s="25" t="str">
-        <f aca="false">IF(J99="","",SUMPRODUCT((I99=$I$6:$I$1500)*(B99&lt;$B$6:$B$1500))+SUMPRODUCT((I99=$I$6:$I$99)*(B99=$B$6:$B$99)))</f>
+        <f aca="false">IF(J99="","",SUMPRODUCT((I99=$I$6:$I$1500)*(B99&lt;$B$6:$B$1500))+COUNTIFS($I$6:I99,I99,$B$6:B99,B99))</f>
         <v/>
       </c>
       <c r="N99" s="33" t="s">
@@ -7383,7 +7383,7 @@
         <v/>
       </c>
       <c r="K100" s="25" t="str">
-        <f aca="false">IF(J100="","",SUMPRODUCT((I100=$I$6:$I$1500)*(B100&lt;$B$6:$B$1500))+SUMPRODUCT((I100=$I$6:$I$100)*(B100=$B$6:$B$100)))</f>
+        <f aca="false">IF(J100="","",SUMPRODUCT((I100=$I$6:$I$1500)*(B100&lt;$B$6:$B$1500))+COUNTIFS($I$6:I100,I100,$B$6:B100,B100))</f>
         <v/>
       </c>
       <c r="N100" s="33" t="s">
@@ -7427,7 +7427,7 @@
         <v/>
       </c>
       <c r="K101" s="25" t="str">
-        <f aca="false">IF(J101="","",SUMPRODUCT((I101=$I$6:$I$1500)*(B101&lt;$B$6:$B$1500))+SUMPRODUCT((I101=$I$6:$I$101)*(B101=$B$6:$B$101)))</f>
+        <f aca="false">IF(J101="","",SUMPRODUCT((I101=$I$6:$I$1500)*(B101&lt;$B$6:$B$1500))+COUNTIFS($I$6:I101,I101,$B$6:B101,B101))</f>
         <v/>
       </c>
       <c r="N101" s="33" t="s">
@@ -7471,7 +7471,7 @@
         <v/>
       </c>
       <c r="K102" s="25" t="str">
-        <f aca="false">IF(J102="","",SUMPRODUCT((I102=$I$6:$I$1500)*(B102&lt;$B$6:$B$1500))+SUMPRODUCT((I102=$I$6:$I$102)*(B102=$B$6:$B$102)))</f>
+        <f aca="false">IF(J102="","",SUMPRODUCT((I102=$I$6:$I$1500)*(B102&lt;$B$6:$B$1500))+COUNTIFS($I$6:I102,I102,$B$6:B102,B102))</f>
         <v/>
       </c>
       <c r="N102" s="33" t="s">
@@ -7515,7 +7515,7 @@
         <v/>
       </c>
       <c r="K103" s="25" t="str">
-        <f aca="false">IF(J103="","",SUMPRODUCT((I103=$I$6:$I$1500)*(B103&lt;$B$6:$B$1500))+SUMPRODUCT((I103=$I$6:$I$103)*(B103=$B$6:$B$103)))</f>
+        <f aca="false">IF(J103="","",SUMPRODUCT((I103=$I$6:$I$1500)*(B103&lt;$B$6:$B$1500))+COUNTIFS($I$6:I103,I103,$B$6:B103,B103))</f>
         <v/>
       </c>
       <c r="N103" s="33" t="s">
@@ -7559,7 +7559,7 @@
         <v/>
       </c>
       <c r="K104" s="25" t="str">
-        <f aca="false">IF(J104="","",SUMPRODUCT((I104=$I$6:$I$1500)*(B104&lt;$B$6:$B$1500))+SUMPRODUCT((I104=$I$6:$I$104)*(B104=$B$6:$B$104)))</f>
+        <f aca="false">IF(J104="","",SUMPRODUCT((I104=$I$6:$I$1500)*(B104&lt;$B$6:$B$1500))+COUNTIFS($I$6:I104,I104,$B$6:B104,B104))</f>
         <v/>
       </c>
       <c r="N104" s="33" t="s">
@@ -7603,7 +7603,7 @@
         <v/>
       </c>
       <c r="K105" s="25" t="str">
-        <f aca="false">IF(J105="","",SUMPRODUCT((I105=$I$6:$I$1500)*(B105&lt;$B$6:$B$1500))+SUMPRODUCT((I105=$I$6:$I$105)*(B105=$B$6:$B$105)))</f>
+        <f aca="false">IF(J105="","",SUMPRODUCT((I105=$I$6:$I$1500)*(B105&lt;$B$6:$B$1500))+COUNTIFS($I$6:I105,I105,$B$6:B105,B105))</f>
         <v/>
       </c>
       <c r="N105" s="33" t="s">
@@ -7647,7 +7647,7 @@
         <v/>
       </c>
       <c r="K106" s="25" t="str">
-        <f aca="false">IF(J106="","",SUMPRODUCT((I106=$I$6:$I$1500)*(B106&lt;$B$6:$B$1500))+SUMPRODUCT((I106=$I$6:$I$106)*(B106=$B$6:$B$106)))</f>
+        <f aca="false">IF(J106="","",SUMPRODUCT((I106=$I$6:$I$1500)*(B106&lt;$B$6:$B$1500))+COUNTIFS($I$6:I106,I106,$B$6:B106,B106))</f>
         <v/>
       </c>
       <c r="N106" s="33" t="s">
@@ -7691,7 +7691,7 @@
         <v/>
       </c>
       <c r="K107" s="25" t="str">
-        <f aca="false">IF(J107="","",SUMPRODUCT((I107=$I$6:$I$1500)*(B107&lt;$B$6:$B$1500))+SUMPRODUCT((I107=$I$6:$I$107)*(B107=$B$6:$B$107)))</f>
+        <f aca="false">IF(J107="","",SUMPRODUCT((I107=$I$6:$I$1500)*(B107&lt;$B$6:$B$1500))+COUNTIFS($I$6:I107,I107,$B$6:B107,B107))</f>
         <v/>
       </c>
       <c r="N107" s="33" t="s">
@@ -7735,7 +7735,7 @@
         <v/>
       </c>
       <c r="K108" s="25" t="str">
-        <f aca="false">IF(J108="","",SUMPRODUCT((I108=$I$6:$I$1500)*(B108&lt;$B$6:$B$1500))+SUMPRODUCT((I108=$I$6:$I$108)*(B108=$B$6:$B$108)))</f>
+        <f aca="false">IF(J108="","",SUMPRODUCT((I108=$I$6:$I$1500)*(B108&lt;$B$6:$B$1500))+COUNTIFS($I$6:I108,I108,$B$6:B108,B108))</f>
         <v/>
       </c>
       <c r="N108" s="33" t="s">
@@ -7777,7 +7777,7 @@
         <v/>
       </c>
       <c r="K109" s="25" t="str">
-        <f aca="false">IF(J109="","",SUMPRODUCT((I109=$I$6:$I$1500)*(B109&lt;$B$6:$B$1500))+SUMPRODUCT((I109=$I$6:$I$109)*(B109=$B$6:$B$109)))</f>
+        <f aca="false">IF(J109="","",SUMPRODUCT((I109=$I$6:$I$1500)*(B109&lt;$B$6:$B$1500))+COUNTIFS($I$6:I109,I109,$B$6:B109,B109))</f>
         <v/>
       </c>
       <c r="N109" s="33" t="s">
@@ -7821,7 +7821,7 @@
         <v>187</v>
       </c>
       <c r="K110" s="25" t="n">
-        <f aca="false">IF(J110="","",SUMPRODUCT((I110=$I$6:$I$1500)*(B110&lt;$B$6:$B$1500))+SUMPRODUCT((I110=$I$6:$I$110)*(B110=$B$6:$B$110)))</f>
+        <f aca="false">IF(J110="","",SUMPRODUCT((I110=$I$6:$I$1500)*(B110&lt;$B$6:$B$1500))+COUNTIFS($I$6:I110,I110,$B$6:B110,B110))</f>
         <v>1</v>
       </c>
       <c r="N110" s="33" t="s">
@@ -7865,7 +7865,7 @@
         <v>47</v>
       </c>
       <c r="K111" s="25" t="n">
-        <f aca="false">IF(J111="","",SUMPRODUCT((I111=$I$6:$I$1500)*(B111&lt;$B$6:$B$1500))+SUMPRODUCT((I111=$I$6:$I$111)*(B111=$B$6:$B$111)))</f>
+        <f aca="false">IF(J111="","",SUMPRODUCT((I111=$I$6:$I$1500)*(B111&lt;$B$6:$B$1500))+COUNTIFS($I$6:I111,I111,$B$6:B111,B111))</f>
         <v>2</v>
       </c>
       <c r="N111" s="33" t="s">
@@ -7909,7 +7909,7 @@
         <v>22</v>
       </c>
       <c r="K112" s="25" t="n">
-        <f aca="false">IF(J112="","",SUMPRODUCT((I112=$I$6:$I$1500)*(B112&lt;$B$6:$B$1500))+SUMPRODUCT((I112=$I$6:$I$112)*(B112=$B$6:$B$112)))</f>
+        <f aca="false">IF(J112="","",SUMPRODUCT((I112=$I$6:$I$1500)*(B112&lt;$B$6:$B$1500))+COUNTIFS($I$6:I112,I112,$B$6:B112,B112))</f>
         <v>3</v>
       </c>
       <c r="N112" s="33" t="s">
@@ -7953,7 +7953,7 @@
         <v>12</v>
       </c>
       <c r="K113" s="25" t="n">
-        <f aca="false">IF(J113="","",SUMPRODUCT((I113=$I$6:$I$1500)*(B113&lt;$B$6:$B$1500))+SUMPRODUCT((I113=$I$6:$I$113)*(B113=$B$6:$B$113)))</f>
+        <f aca="false">IF(J113="","",SUMPRODUCT((I113=$I$6:$I$1500)*(B113&lt;$B$6:$B$1500))+COUNTIFS($I$6:I113,I113,$B$6:B113,B113))</f>
         <v>4</v>
       </c>
       <c r="N113" s="33" t="s">
@@ -7997,7 +7997,7 @@
         <v>16</v>
       </c>
       <c r="K114" s="25" t="n">
-        <f aca="false">IF(J114="","",SUMPRODUCT((I114=$I$6:$I$1500)*(B114&lt;$B$6:$B$1500))+SUMPRODUCT((I114=$I$6:$I$114)*(B114=$B$6:$B$114)))</f>
+        <f aca="false">IF(J114="","",SUMPRODUCT((I114=$I$6:$I$1500)*(B114&lt;$B$6:$B$1500))+COUNTIFS($I$6:I114,I114,$B$6:B114,B114))</f>
         <v>5</v>
       </c>
       <c r="N114" s="33" t="s">
@@ -8041,7 +8041,7 @@
         <v>12</v>
       </c>
       <c r="K115" s="25" t="n">
-        <f aca="false">IF(J115="","",SUMPRODUCT((I115=$I$6:$I$1500)*(B115&lt;$B$6:$B$1500))+SUMPRODUCT((I115=$I$6:$I$115)*(B115=$B$6:$B$115)))</f>
+        <f aca="false">IF(J115="","",SUMPRODUCT((I115=$I$6:$I$1500)*(B115&lt;$B$6:$B$1500))+COUNTIFS($I$6:I115,I115,$B$6:B115,B115))</f>
         <v>6</v>
       </c>
       <c r="N115" s="33" t="s">
@@ -8083,7 +8083,7 @@
         <v/>
       </c>
       <c r="K116" s="25" t="str">
-        <f aca="false">IF(J116="","",SUMPRODUCT((I116=$I$6:$I$1500)*(B116&lt;$B$6:$B$1500))+SUMPRODUCT((I116=$I$6:$I$116)*(B116=$B$6:$B$116)))</f>
+        <f aca="false">IF(J116="","",SUMPRODUCT((I116=$I$6:$I$1500)*(B116&lt;$B$6:$B$1500))+COUNTIFS($I$6:I116,I116,$B$6:B116,B116))</f>
         <v/>
       </c>
       <c r="N116" s="33" t="s">
@@ -8127,7 +8127,7 @@
         <v>90</v>
       </c>
       <c r="K117" s="25" t="n">
-        <f aca="false">IF(J117="","",SUMPRODUCT((I117=$I$6:$I$1500)*(B117&lt;$B$6:$B$1500))+SUMPRODUCT((I117=$I$6:$I$117)*(B117=$B$6:$B$117)))</f>
+        <f aca="false">IF(J117="","",SUMPRODUCT((I117=$I$6:$I$1500)*(B117&lt;$B$6:$B$1500))+COUNTIFS($I$6:I117,I117,$B$6:B117,B117))</f>
         <v>1</v>
       </c>
       <c r="L117" s="64"/>
@@ -8172,7 +8172,7 @@
         <v>28</v>
       </c>
       <c r="K118" s="25" t="n">
-        <f aca="false">IF(J118="","",SUMPRODUCT((I118=$I$6:$I$1500)*(B118&lt;$B$6:$B$1500))+SUMPRODUCT((I118=$I$6:$I$118)*(B118=$B$6:$B$118)))</f>
+        <f aca="false">IF(J118="","",SUMPRODUCT((I118=$I$6:$I$1500)*(B118&lt;$B$6:$B$1500))+COUNTIFS($I$6:I118,I118,$B$6:B118,B118))</f>
         <v>2</v>
       </c>
       <c r="N118" s="33" t="s">
@@ -8216,7 +8216,7 @@
         <v>61</v>
       </c>
       <c r="K119" s="25" t="n">
-        <f aca="false">IF(J119="","",SUMPRODUCT((I119=$I$6:$I$1500)*(B119&lt;$B$6:$B$1500))+SUMPRODUCT((I119=$I$6:$I$119)*(B119=$B$6:$B$119)))</f>
+        <f aca="false">IF(J119="","",SUMPRODUCT((I119=$I$6:$I$1500)*(B119&lt;$B$6:$B$1500))+COUNTIFS($I$6:I119,I119,$B$6:B119,B119))</f>
         <v>3</v>
       </c>
       <c r="N119" s="33" t="s">
@@ -8260,7 +8260,7 @@
         <v>23</v>
       </c>
       <c r="K120" s="25" t="n">
-        <f aca="false">IF(J120="","",SUMPRODUCT((I120=$I$6:$I$1500)*(B120&lt;$B$6:$B$1500))+SUMPRODUCT((I120=$I$6:$I$120)*(B120=$B$6:$B$120)))</f>
+        <f aca="false">IF(J120="","",SUMPRODUCT((I120=$I$6:$I$1500)*(B120&lt;$B$6:$B$1500))+COUNTIFS($I$6:I120,I120,$B$6:B120,B120))</f>
         <v>4</v>
       </c>
       <c r="N120" s="52" t="s">
@@ -8304,7 +8304,7 @@
         <v>16</v>
       </c>
       <c r="K121" s="25" t="n">
-        <f aca="false">IF(J121="","",SUMPRODUCT((I121=$I$6:$I$1500)*(B121&lt;$B$6:$B$1500))+SUMPRODUCT((I121=$I$6:$I$121)*(B121=$B$6:$B$121)))</f>
+        <f aca="false">IF(J121="","",SUMPRODUCT((I121=$I$6:$I$1500)*(B121&lt;$B$6:$B$1500))+COUNTIFS($I$6:I121,I121,$B$6:B121,B121))</f>
         <v>5</v>
       </c>
       <c r="N121" s="33" t="s">
@@ -8348,7 +8348,7 @@
         <v>12</v>
       </c>
       <c r="K122" s="25" t="n">
-        <f aca="false">IF(J122="","",SUMPRODUCT((I122=$I$6:$I$1500)*(B122&lt;$B$6:$B$1500))+SUMPRODUCT((I122=$I$6:$I$122)*(B122=$B$6:$B$122)))</f>
+        <f aca="false">IF(J122="","",SUMPRODUCT((I122=$I$6:$I$1500)*(B122&lt;$B$6:$B$1500))+COUNTIFS($I$6:I122,I122,$B$6:B122,B122))</f>
         <v>6</v>
       </c>
       <c r="N122" s="33" t="s">
@@ -8392,7 +8392,7 @@
         <v>22</v>
       </c>
       <c r="K123" s="25" t="n">
-        <f aca="false">IF(J123="","",SUMPRODUCT((I123=$I$6:$I$1500)*(B123&lt;$B$6:$B$1500))+SUMPRODUCT((I123=$I$6:$I$123)*(B123=$B$6:$B$123)))</f>
+        <f aca="false">IF(J123="","",SUMPRODUCT((I123=$I$6:$I$1500)*(B123&lt;$B$6:$B$1500))+COUNTIFS($I$6:I123,I123,$B$6:B123,B123))</f>
         <v>7</v>
       </c>
       <c r="N123" s="33" t="s">
@@ -8436,7 +8436,7 @@
         <v>10</v>
       </c>
       <c r="K124" s="25" t="n">
-        <f aca="false">IF(J124="","",SUMPRODUCT((I124=$I$6:$I$1500)*(B124&lt;$B$6:$B$1500))+SUMPRODUCT((I124=$I$6:$I$124)*(B124=$B$6:$B$124)))</f>
+        <f aca="false">IF(J124="","",SUMPRODUCT((I124=$I$6:$I$1500)*(B124&lt;$B$6:$B$1500))+COUNTIFS($I$6:I124,I124,$B$6:B124,B124))</f>
         <v>8</v>
       </c>
       <c r="N124" s="33" t="s">
@@ -8480,7 +8480,7 @@
         <v>7</v>
       </c>
       <c r="K125" s="25" t="n">
-        <f aca="false">IF(J125="","",SUMPRODUCT((I125=$I$6:$I$1500)*(B125&lt;$B$6:$B$1500))+SUMPRODUCT((I125=$I$6:$I$125)*(B125=$B$6:$B$125)))</f>
+        <f aca="false">IF(J125="","",SUMPRODUCT((I125=$I$6:$I$1500)*(B125&lt;$B$6:$B$1500))+COUNTIFS($I$6:I125,I125,$B$6:B125,B125))</f>
         <v>9</v>
       </c>
       <c r="N125" s="33" t="s">
@@ -8524,7 +8524,7 @@
         <v>14</v>
       </c>
       <c r="K126" s="25" t="n">
-        <f aca="false">IF(J126="","",SUMPRODUCT((I126=$I$6:$I$1500)*(B126&lt;$B$6:$B$1500))+SUMPRODUCT((I126=$I$6:$I$126)*(B126=$B$6:$B$126)))</f>
+        <f aca="false">IF(J126="","",SUMPRODUCT((I126=$I$6:$I$1500)*(B126&lt;$B$6:$B$1500))+COUNTIFS($I$6:I126,I126,$B$6:B126,B126))</f>
         <v>10</v>
       </c>
       <c r="N126" s="33" t="s">
@@ -8568,7 +8568,7 @@
         <v>7</v>
       </c>
       <c r="K127" s="25" t="n">
-        <f aca="false">IF(J127="","",SUMPRODUCT((I127=$I$6:$I$1500)*(B127&lt;$B$6:$B$1500))+SUMPRODUCT((I127=$I$6:$I$127)*(B127=$B$6:$B$127)))</f>
+        <f aca="false">IF(J127="","",SUMPRODUCT((I127=$I$6:$I$1500)*(B127&lt;$B$6:$B$1500))+COUNTIFS($I$6:I127,I127,$B$6:B127,B127))</f>
         <v>11</v>
       </c>
       <c r="N127" s="33" t="s">
@@ -8612,7 +8612,7 @@
         <v>7</v>
       </c>
       <c r="K128" s="25" t="n">
-        <f aca="false">IF(J128="","",SUMPRODUCT((I128=$I$6:$I$1500)*(B128&lt;$B$6:$B$1500))+SUMPRODUCT((I128=$I$6:$I$128)*(B128=$B$6:$B$128)))</f>
+        <f aca="false">IF(J128="","",SUMPRODUCT((I128=$I$6:$I$1500)*(B128&lt;$B$6:$B$1500))+COUNTIFS($I$6:I128,I128,$B$6:B128,B128))</f>
         <v>12</v>
       </c>
       <c r="N128" s="33" t="s">
@@ -8656,7 +8656,7 @@
         <v>4</v>
       </c>
       <c r="K129" s="25" t="n">
-        <f aca="false">IF(J129="","",SUMPRODUCT((I129=$I$6:$I$1500)*(B129&lt;$B$6:$B$1500))+SUMPRODUCT((I129=$I$6:$I$129)*(B129=$B$6:$B$129)))</f>
+        <f aca="false">IF(J129="","",SUMPRODUCT((I129=$I$6:$I$1500)*(B129&lt;$B$6:$B$1500))+COUNTIFS($I$6:I129,I129,$B$6:B129,B129))</f>
         <v>13</v>
       </c>
       <c r="N129" s="33" t="s">
@@ -8700,7 +8700,7 @@
         <v>4</v>
       </c>
       <c r="K130" s="25" t="n">
-        <f aca="false">IF(J130="","",SUMPRODUCT((I130=$I$6:$I$1500)*(B130&lt;$B$6:$B$1500))+SUMPRODUCT((I130=$I$6:$I$130)*(B130=$B$6:$B$130)))</f>
+        <f aca="false">IF(J130="","",SUMPRODUCT((I130=$I$6:$I$1500)*(B130&lt;$B$6:$B$1500))+COUNTIFS($I$6:I130,I130,$B$6:B130,B130))</f>
         <v>14</v>
       </c>
       <c r="N130" s="33" t="s">
@@ -8744,7 +8744,7 @@
         <v>3</v>
       </c>
       <c r="K131" s="25" t="n">
-        <f aca="false">IF(J131="","",SUMPRODUCT((I131=$I$6:$I$1500)*(B131&lt;$B$6:$B$1500))+SUMPRODUCT((I131=$I$6:$I$131)*(B131=$B$6:$B$131)))</f>
+        <f aca="false">IF(J131="","",SUMPRODUCT((I131=$I$6:$I$1500)*(B131&lt;$B$6:$B$1500))+COUNTIFS($I$6:I131,I131,$B$6:B131,B131))</f>
         <v>15</v>
       </c>
       <c r="N131" s="33" t="s">
@@ -8788,7 +8788,7 @@
         <v>7</v>
       </c>
       <c r="K132" s="25" t="n">
-        <f aca="false">IF(J132="","",SUMPRODUCT((I132=$I$6:$I$1500)*(B132&lt;$B$6:$B$1500))+SUMPRODUCT((I132=$I$6:$I$132)*(B132=$B$6:$B$132)))</f>
+        <f aca="false">IF(J132="","",SUMPRODUCT((I132=$I$6:$I$1500)*(B132&lt;$B$6:$B$1500))+COUNTIFS($I$6:I132,I132,$B$6:B132,B132))</f>
         <v>16</v>
       </c>
       <c r="N132" s="33" t="s">
@@ -8832,7 +8832,7 @@
         <v>3</v>
       </c>
       <c r="K133" s="25" t="n">
-        <f aca="false">IF(J133="","",SUMPRODUCT((I133=$I$6:$I$1500)*(B133&lt;$B$6:$B$1500))+SUMPRODUCT((I133=$I$6:$I$133)*(B133=$B$6:$B$133)))</f>
+        <f aca="false">IF(J133="","",SUMPRODUCT((I133=$I$6:$I$1500)*(B133&lt;$B$6:$B$1500))+COUNTIFS($I$6:I133,I133,$B$6:B133,B133))</f>
         <v>17</v>
       </c>
       <c r="N133" s="33" t="s">
@@ -8876,7 +8876,7 @@
         <v>1</v>
       </c>
       <c r="K134" s="25" t="n">
-        <f aca="false">IF(J134="","",SUMPRODUCT((I134=$I$6:$I$1500)*(B134&lt;$B$6:$B$1500))+SUMPRODUCT((I134=$I$6:$I$134)*(B134=$B$6:$B$134)))</f>
+        <f aca="false">IF(J134="","",SUMPRODUCT((I134=$I$6:$I$1500)*(B134&lt;$B$6:$B$1500))+COUNTIFS($I$6:I134,I134,$B$6:B134,B134))</f>
         <v>18</v>
       </c>
       <c r="N134" s="33" t="s">
@@ -8920,7 +8920,7 @@
         <v>1</v>
       </c>
       <c r="K135" s="25" t="n">
-        <f aca="false">IF(J135="","",SUMPRODUCT((I135=$I$6:$I$1500)*(B135&lt;$B$6:$B$1500))+SUMPRODUCT((I135=$I$6:$I$135)*(B135=$B$6:$B$135)))</f>
+        <f aca="false">IF(J135="","",SUMPRODUCT((I135=$I$6:$I$1500)*(B135&lt;$B$6:$B$1500))+COUNTIFS($I$6:I135,I135,$B$6:B135,B135))</f>
         <v>19</v>
       </c>
       <c r="N135" s="33" t="s">
@@ -8962,7 +8962,7 @@
         <v/>
       </c>
       <c r="K136" s="25" t="str">
-        <f aca="false">IF(J136="","",SUMPRODUCT((I136=$I$6:$I$1500)*(B136&lt;$B$6:$B$1500))+SUMPRODUCT((I136=$I$6:$I$136)*(B136=$B$6:$B$136)))</f>
+        <f aca="false">IF(J136="","",SUMPRODUCT((I136=$I$6:$I$1500)*(B136&lt;$B$6:$B$1500))+COUNTIFS($I$6:I136,I136,$B$6:B136,B136))</f>
         <v/>
       </c>
       <c r="N136" s="33" t="s">
@@ -9006,7 +9006,7 @@
         <v>106</v>
       </c>
       <c r="K137" s="25" t="n">
-        <f aca="false">IF(J137="","",SUMPRODUCT((I137=$I$6:$I$1500)*(B137&lt;$B$6:$B$1500))+SUMPRODUCT((I137=$I$6:$I$137)*(B137=$B$6:$B$137)))</f>
+        <f aca="false">IF(J137="","",SUMPRODUCT((I137=$I$6:$I$1500)*(B137&lt;$B$6:$B$1500))+COUNTIFS($I$6:I137,I137,$B$6:B137,B137))</f>
         <v>1</v>
       </c>
       <c r="N137" s="33" t="s">
@@ -9050,7 +9050,7 @@
         <v>45</v>
       </c>
       <c r="K138" s="25" t="n">
-        <f aca="false">IF(J138="","",SUMPRODUCT((I138=$I$6:$I$1500)*(B138&lt;$B$6:$B$1500))+SUMPRODUCT((I138=$I$6:$I$138)*(B138=$B$6:$B$138)))</f>
+        <f aca="false">IF(J138="","",SUMPRODUCT((I138=$I$6:$I$1500)*(B138&lt;$B$6:$B$1500))+COUNTIFS($I$6:I138,I138,$B$6:B138,B138))</f>
         <v>2</v>
       </c>
       <c r="N138" s="33" t="s">
@@ -9094,7 +9094,7 @@
         <v>15</v>
       </c>
       <c r="K139" s="25" t="n">
-        <f aca="false">IF(J139="","",SUMPRODUCT((I139=$I$6:$I$1500)*(B139&lt;$B$6:$B$1500))+SUMPRODUCT((I139=$I$6:$I$139)*(B139=$B$6:$B$139)))</f>
+        <f aca="false">IF(J139="","",SUMPRODUCT((I139=$I$6:$I$1500)*(B139&lt;$B$6:$B$1500))+COUNTIFS($I$6:I139,I139,$B$6:B139,B139))</f>
         <v>6</v>
       </c>
       <c r="N139" s="33" t="s">
@@ -9136,7 +9136,7 @@
         <v/>
       </c>
       <c r="K140" s="25" t="str">
-        <f aca="false">IF(J140="","",SUMPRODUCT((I140=$I$6:$I$1500)*(B140&lt;$B$6:$B$1500))+SUMPRODUCT((I140=$I$6:$I$140)*(B140=$B$6:$B$140)))</f>
+        <f aca="false">IF(J140="","",SUMPRODUCT((I140=$I$6:$I$1500)*(B140&lt;$B$6:$B$1500))+COUNTIFS($I$6:I140,I140,$B$6:B140,B140))</f>
         <v/>
       </c>
       <c r="N140" s="33" t="s">
@@ -9180,7 +9180,7 @@
         <v/>
       </c>
       <c r="K141" s="25" t="str">
-        <f aca="false">IF(J141="","",SUMPRODUCT((I141=$I$6:$I$1500)*(B141&lt;$B$6:$B$1500))+SUMPRODUCT((I141=$I$6:$I$141)*(B141=$B$6:$B$141)))</f>
+        <f aca="false">IF(J141="","",SUMPRODUCT((I141=$I$6:$I$1500)*(B141&lt;$B$6:$B$1500))+COUNTIFS($I$6:I141,I141,$B$6:B141,B141))</f>
         <v/>
       </c>
       <c r="N141" s="33" t="s">
@@ -9224,7 +9224,7 @@
         <v/>
       </c>
       <c r="K142" s="25" t="str">
-        <f aca="false">IF(J142="","",SUMPRODUCT((I142=$I$6:$I$1500)*(B142&lt;$B$6:$B$1500))+SUMPRODUCT((I142=$I$6:$I$142)*(B142=$B$6:$B$142)))</f>
+        <f aca="false">IF(J142="","",SUMPRODUCT((I142=$I$6:$I$1500)*(B142&lt;$B$6:$B$1500))+COUNTIFS($I$6:I142,I142,$B$6:B142,B142))</f>
         <v/>
       </c>
       <c r="N142" s="33" t="s">
@@ -9268,7 +9268,7 @@
         <v/>
       </c>
       <c r="K143" s="25" t="str">
-        <f aca="false">IF(J143="","",SUMPRODUCT((I143=$I$6:$I$1500)*(B143&lt;$B$6:$B$1500))+SUMPRODUCT((I143=$I$6:$I$143)*(B143=$B$6:$B$143)))</f>
+        <f aca="false">IF(J143="","",SUMPRODUCT((I143=$I$6:$I$1500)*(B143&lt;$B$6:$B$1500))+COUNTIFS($I$6:I143,I143,$B$6:B143,B143))</f>
         <v/>
       </c>
       <c r="N143" s="33" t="s">
@@ -9312,7 +9312,7 @@
         <v/>
       </c>
       <c r="K144" s="25" t="str">
-        <f aca="false">IF(J144="","",SUMPRODUCT((I144=$I$6:$I$1500)*(B144&lt;$B$6:$B$1500))+SUMPRODUCT((I144=$I$6:$I$144)*(B144=$B$6:$B$144)))</f>
+        <f aca="false">IF(J144="","",SUMPRODUCT((I144=$I$6:$I$1500)*(B144&lt;$B$6:$B$1500))+COUNTIFS($I$6:I144,I144,$B$6:B144,B144))</f>
         <v/>
       </c>
       <c r="N144" s="33" t="s">
@@ -9356,7 +9356,7 @@
         <v/>
       </c>
       <c r="K145" s="25" t="str">
-        <f aca="false">IF(J145="","",SUMPRODUCT((I145=$I$6:$I$1500)*(B145&lt;$B$6:$B$1500))+SUMPRODUCT((I145=$I$6:$I$145)*(B145=$B$6:$B$145)))</f>
+        <f aca="false">IF(J145="","",SUMPRODUCT((I145=$I$6:$I$1500)*(B145&lt;$B$6:$B$1500))+COUNTIFS($I$6:I145,I145,$B$6:B145,B145))</f>
         <v/>
       </c>
       <c r="N145" s="33" t="s">
@@ -9398,7 +9398,7 @@
         <v/>
       </c>
       <c r="K146" s="25" t="str">
-        <f aca="false">IF(J146="","",SUMPRODUCT((I146=$I$6:$I$1500)*(B146&lt;$B$6:$B$1500))+SUMPRODUCT((I146=$I$6:$I$146)*(B146=$B$6:$B$146)))</f>
+        <f aca="false">IF(J146="","",SUMPRODUCT((I146=$I$6:$I$1500)*(B146&lt;$B$6:$B$1500))+COUNTIFS($I$6:I146,I146,$B$6:B146,B146))</f>
         <v/>
       </c>
       <c r="N146" s="33" t="s">
@@ -9442,7 +9442,7 @@
         <v>65</v>
       </c>
       <c r="K147" s="25" t="n">
-        <f aca="false">IF(J147="","",SUMPRODUCT((I147=$I$6:$I$1500)*(B147&lt;$B$6:$B$1500))+SUMPRODUCT((I147=$I$6:$I$147)*(B147=$B$6:$B$147)))</f>
+        <f aca="false">IF(J147="","",SUMPRODUCT((I147=$I$6:$I$1500)*(B147&lt;$B$6:$B$1500))+COUNTIFS($I$6:I147,I147,$B$6:B147,B147))</f>
         <v>1</v>
       </c>
       <c r="N147" s="33" t="s">
@@ -9486,7 +9486,7 @@
         <v>55</v>
       </c>
       <c r="K148" s="25" t="n">
-        <f aca="false">IF(J148="","",SUMPRODUCT((I148=$I$6:$I$1500)*(B148&lt;$B$6:$B$1500))+SUMPRODUCT((I148=$I$6:$I$148)*(B148=$B$6:$B$148)))</f>
+        <f aca="false">IF(J148="","",SUMPRODUCT((I148=$I$6:$I$1500)*(B148&lt;$B$6:$B$1500))+COUNTIFS($I$6:I148,I148,$B$6:B148,B148))</f>
         <v>2</v>
       </c>
       <c r="N148" s="33" t="s">
@@ -9530,7 +9530,7 @@
         <v>15</v>
       </c>
       <c r="K149" s="25" t="n">
-        <f aca="false">IF(J149="","",SUMPRODUCT((I149=$I$6:$I$1500)*(B149&lt;$B$6:$B$1500))+SUMPRODUCT((I149=$I$6:$I$149)*(B149=$B$6:$B$149)))</f>
+        <f aca="false">IF(J149="","",SUMPRODUCT((I149=$I$6:$I$1500)*(B149&lt;$B$6:$B$1500))+COUNTIFS($I$6:I149,I149,$B$6:B149,B149))</f>
         <v>3</v>
       </c>
       <c r="N149" s="52" t="s">
@@ -9574,7 +9574,7 @@
         <v>14</v>
       </c>
       <c r="K150" s="25" t="n">
-        <f aca="false">IF(J150="","",SUMPRODUCT((I150=$I$6:$I$1500)*(B150&lt;$B$6:$B$1500))+SUMPRODUCT((I150=$I$6:$I$150)*(B150=$B$6:$B$150)))</f>
+        <f aca="false">IF(J150="","",SUMPRODUCT((I150=$I$6:$I$1500)*(B150&lt;$B$6:$B$1500))+COUNTIFS($I$6:I150,I150,$B$6:B150,B150))</f>
         <v>4</v>
       </c>
       <c r="N150" s="33" t="s">
@@ -9618,7 +9618,7 @@
         <v>10</v>
       </c>
       <c r="K151" s="25" t="n">
-        <f aca="false">IF(J151="","",SUMPRODUCT((I151=$I$6:$I$1500)*(B151&lt;$B$6:$B$1500))+SUMPRODUCT((I151=$I$6:$I$151)*(B151=$B$6:$B$151)))</f>
+        <f aca="false">IF(J151="","",SUMPRODUCT((I151=$I$6:$I$1500)*(B151&lt;$B$6:$B$1500))+COUNTIFS($I$6:I151,I151,$B$6:B151,B151))</f>
         <v>5</v>
       </c>
       <c r="N151" s="33" t="s">
@@ -9662,7 +9662,7 @@
         <v>11</v>
       </c>
       <c r="K152" s="25" t="n">
-        <f aca="false">IF(J152="","",SUMPRODUCT((I152=$I$6:$I$1500)*(B152&lt;$B$6:$B$1500))+SUMPRODUCT((I152=$I$6:$I$152)*(B152=$B$6:$B$152)))</f>
+        <f aca="false">IF(J152="","",SUMPRODUCT((I152=$I$6:$I$1500)*(B152&lt;$B$6:$B$1500))+COUNTIFS($I$6:I152,I152,$B$6:B152,B152))</f>
         <v>6</v>
       </c>
       <c r="N152" s="33" t="s">
@@ -9706,7 +9706,7 @@
         <v>9</v>
       </c>
       <c r="K153" s="25" t="n">
-        <f aca="false">IF(J153="","",SUMPRODUCT((I153=$I$6:$I$1500)*(B153&lt;$B$6:$B$1500))+SUMPRODUCT((I153=$I$6:$I$153)*(B153=$B$6:$B$153)))</f>
+        <f aca="false">IF(J153="","",SUMPRODUCT((I153=$I$6:$I$1500)*(B153&lt;$B$6:$B$1500))+COUNTIFS($I$6:I153,I153,$B$6:B153,B153))</f>
         <v>7</v>
       </c>
       <c r="N153" s="33" t="s">
@@ -9750,7 +9750,7 @@
         <v>7</v>
       </c>
       <c r="K154" s="25" t="n">
-        <f aca="false">IF(J154="","",SUMPRODUCT((I154=$I$6:$I$1500)*(B154&lt;$B$6:$B$1500))+SUMPRODUCT((I154=$I$6:$I$154)*(B154=$B$6:$B$154)))</f>
+        <f aca="false">IF(J154="","",SUMPRODUCT((I154=$I$6:$I$1500)*(B154&lt;$B$6:$B$1500))+COUNTIFS($I$6:I154,I154,$B$6:B154,B154))</f>
         <v>8</v>
       </c>
       <c r="N154" s="33" t="s">
@@ -9794,7 +9794,7 @@
         <v>5</v>
       </c>
       <c r="K155" s="25" t="n">
-        <f aca="false">IF(J155="","",SUMPRODUCT((I155=$I$6:$I$1500)*(B155&lt;$B$6:$B$1500))+SUMPRODUCT((I155=$I$6:$I$155)*(B155=$B$6:$B$155)))</f>
+        <f aca="false">IF(J155="","",SUMPRODUCT((I155=$I$6:$I$1500)*(B155&lt;$B$6:$B$1500))+COUNTIFS($I$6:I155,I155,$B$6:B155,B155))</f>
         <v>9</v>
       </c>
       <c r="N155" s="33" t="s">
@@ -9838,7 +9838,7 @@
         <v>3</v>
       </c>
       <c r="K156" s="25" t="n">
-        <f aca="false">IF(J156="","",SUMPRODUCT((I156=$I$6:$I$1500)*(B156&lt;$B$6:$B$1500))+SUMPRODUCT((I156=$I$6:$I$156)*(B156=$B$6:$B$156)))</f>
+        <f aca="false">IF(J156="","",SUMPRODUCT((I156=$I$6:$I$1500)*(B156&lt;$B$6:$B$1500))+COUNTIFS($I$6:I156,I156,$B$6:B156,B156))</f>
         <v>10</v>
       </c>
       <c r="N156" s="33" t="s">
@@ -9882,7 +9882,7 @@
         <v>1</v>
       </c>
       <c r="K157" s="25" t="n">
-        <f aca="false">IF(J157="","",SUMPRODUCT((I157=$I$6:$I$1500)*(B157&lt;$B$6:$B$1500))+SUMPRODUCT((I157=$I$6:$I$157)*(B157=$B$6:$B$157)))</f>
+        <f aca="false">IF(J157="","",SUMPRODUCT((I157=$I$6:$I$1500)*(B157&lt;$B$6:$B$1500))+COUNTIFS($I$6:I157,I157,$B$6:B157,B157))</f>
         <v>11</v>
       </c>
       <c r="N157" s="33" t="s">
@@ -9926,7 +9926,7 @@
         <v>1</v>
       </c>
       <c r="K158" s="25" t="n">
-        <f aca="false">IF(J158="","",SUMPRODUCT((I158=$I$6:$I$1500)*(B158&lt;$B$6:$B$1500))+SUMPRODUCT((I158=$I$6:$I$158)*(B158=$B$6:$B$158)))</f>
+        <f aca="false">IF(J158="","",SUMPRODUCT((I158=$I$6:$I$1500)*(B158&lt;$B$6:$B$1500))+COUNTIFS($I$6:I158,I158,$B$6:B158,B158))</f>
         <v>12</v>
       </c>
       <c r="N158" s="33" t="s">
@@ -9970,7 +9970,7 @@
         <v>1</v>
       </c>
       <c r="K159" s="25" t="n">
-        <f aca="false">IF(J159="","",SUMPRODUCT((I159=$I$6:$I$1500)*(B159&lt;$B$6:$B$1500))+SUMPRODUCT((I159=$I$6:$I$159)*(B159=$B$6:$B$159)))</f>
+        <f aca="false">IF(J159="","",SUMPRODUCT((I159=$I$6:$I$1500)*(B159&lt;$B$6:$B$1500))+COUNTIFS($I$6:I159,I159,$B$6:B159,B159))</f>
         <v>13</v>
       </c>
       <c r="N159" s="33" t="s">
@@ -10012,7 +10012,7 @@
         <v/>
       </c>
       <c r="K160" s="25" t="str">
-        <f aca="false">IF(J160="","",SUMPRODUCT((I160=$I$6:$I$1500)*(B160&lt;$B$6:$B$1500))+SUMPRODUCT((I160=$I$6:$I$160)*(B160=$B$6:$B$160)))</f>
+        <f aca="false">IF(J160="","",SUMPRODUCT((I160=$I$6:$I$1500)*(B160&lt;$B$6:$B$1500))+COUNTIFS($I$6:I160,I160,$B$6:B160,B160))</f>
         <v/>
       </c>
       <c r="N160" s="33" t="s">
@@ -10056,7 +10056,7 @@
         <v>84</v>
       </c>
       <c r="K161" s="25" t="n">
-        <f aca="false">IF(J161="","",SUMPRODUCT((I161=$I$6:$I$1500)*(B161&lt;$B$6:$B$1500))+SUMPRODUCT((I161=$I$6:$I$161)*(B161=$B$6:$B$161)))</f>
+        <f aca="false">IF(J161="","",SUMPRODUCT((I161=$I$6:$I$1500)*(B161&lt;$B$6:$B$1500))+COUNTIFS($I$6:I161,I161,$B$6:B161,B161))</f>
         <v>1</v>
       </c>
       <c r="N161" s="33" t="s">
@@ -10100,7 +10100,7 @@
         <v>41</v>
       </c>
       <c r="K162" s="25" t="n">
-        <f aca="false">IF(J162="","",SUMPRODUCT((I162=$I$6:$I$1500)*(B162&lt;$B$6:$B$1500))+SUMPRODUCT((I162=$I$6:$I$162)*(B162=$B$6:$B$162)))</f>
+        <f aca="false">IF(J162="","",SUMPRODUCT((I162=$I$6:$I$1500)*(B162&lt;$B$6:$B$1500))+COUNTIFS($I$6:I162,I162,$B$6:B162,B162))</f>
         <v>2</v>
       </c>
       <c r="N162" s="33" t="s">
@@ -10144,7 +10144,7 @@
         <v>41</v>
       </c>
       <c r="K163" s="25" t="n">
-        <f aca="false">IF(J163="","",SUMPRODUCT((I163=$I$6:$I$1500)*(B163&lt;$B$6:$B$1500))+SUMPRODUCT((I163=$I$6:$I$163)*(B163=$B$6:$B$163)))</f>
+        <f aca="false">IF(J163="","",SUMPRODUCT((I163=$I$6:$I$1500)*(B163&lt;$B$6:$B$1500))+COUNTIFS($I$6:I163,I163,$B$6:B163,B163))</f>
         <v>3</v>
       </c>
       <c r="N163" s="33" t="s">
@@ -10188,7 +10188,7 @@
         <v/>
       </c>
       <c r="K164" s="25" t="str">
-        <f aca="false">IF(J164="","",SUMPRODUCT((I164=$I$6:$I$1500)*(B164&lt;$B$6:$B$1500))+SUMPRODUCT((I164=$I$6:$I$164)*(B164=$B$6:$B$164)))</f>
+        <f aca="false">IF(J164="","",SUMPRODUCT((I164=$I$6:$I$1500)*(B164&lt;$B$6:$B$1500))+COUNTIFS($I$6:I164,I164,$B$6:B164,B164))</f>
         <v/>
       </c>
       <c r="N164" s="33" t="s">
@@ -10230,7 +10230,7 @@
         <v/>
       </c>
       <c r="K165" s="25" t="str">
-        <f aca="false">IF(J165="","",SUMPRODUCT((I165=$I$6:$I$1500)*(B165&lt;$B$6:$B$1500))+SUMPRODUCT((I165=$I$6:$I$165)*(B165=$B$6:$B$165)))</f>
+        <f aca="false">IF(J165="","",SUMPRODUCT((I165=$I$6:$I$1500)*(B165&lt;$B$6:$B$1500))+COUNTIFS($I$6:I165,I165,$B$6:B165,B165))</f>
         <v/>
       </c>
       <c r="N165" s="33" t="s">
@@ -10274,7 +10274,7 @@
         <v>66</v>
       </c>
       <c r="K166" s="25" t="n">
-        <f aca="false">IF(J166="","",SUMPRODUCT((I166=$I$6:$I$1500)*(B166&lt;$B$6:$B$1500))+SUMPRODUCT((I166=$I$6:$I$166)*(B166=$B$6:$B$166)))</f>
+        <f aca="false">IF(J166="","",SUMPRODUCT((I166=$I$6:$I$1500)*(B166&lt;$B$6:$B$1500))+COUNTIFS($I$6:I166,I166,$B$6:B166,B166))</f>
         <v>1</v>
       </c>
       <c r="N166" s="33" t="s">
@@ -10318,7 +10318,7 @@
         <v>38</v>
       </c>
       <c r="K167" s="25" t="n">
-        <f aca="false">IF(J167="","",SUMPRODUCT((I167=$I$6:$I$1500)*(B167&lt;$B$6:$B$1500))+SUMPRODUCT((I167=$I$6:$I$167)*(B167=$B$6:$B$167)))</f>
+        <f aca="false">IF(J167="","",SUMPRODUCT((I167=$I$6:$I$1500)*(B167&lt;$B$6:$B$1500))+COUNTIFS($I$6:I167,I167,$B$6:B167,B167))</f>
         <v>2</v>
       </c>
       <c r="N167" s="33" t="s">
@@ -10362,7 +10362,7 @@
         <v>28</v>
       </c>
       <c r="K168" s="25" t="n">
-        <f aca="false">IF(J168="","",SUMPRODUCT((I168=$I$6:$I$1500)*(B168&lt;$B$6:$B$1500))+SUMPRODUCT((I168=$I$6:$I$168)*(B168=$B$6:$B$168)))</f>
+        <f aca="false">IF(J168="","",SUMPRODUCT((I168=$I$6:$I$1500)*(B168&lt;$B$6:$B$1500))+COUNTIFS($I$6:I168,I168,$B$6:B168,B168))</f>
         <v>3</v>
       </c>
       <c r="N168" s="33" t="s">
@@ -10406,7 +10406,7 @@
         <v>27</v>
       </c>
       <c r="K169" s="25" t="n">
-        <f aca="false">IF(J169="","",SUMPRODUCT((I169=$I$6:$I$1500)*(B169&lt;$B$6:$B$1500))+SUMPRODUCT((I169=$I$6:$I$169)*(B169=$B$6:$B$169)))</f>
+        <f aca="false">IF(J169="","",SUMPRODUCT((I169=$I$6:$I$1500)*(B169&lt;$B$6:$B$1500))+COUNTIFS($I$6:I169,I169,$B$6:B169,B169))</f>
         <v>4</v>
       </c>
       <c r="N169" s="33" t="s">
@@ -10450,7 +10450,7 @@
         <v>151</v>
       </c>
       <c r="K170" s="25" t="n">
-        <f aca="false">IF(J170="","",SUMPRODUCT((I170=$I$6:$I$1500)*(B170&lt;$B$6:$B$1500))+SUMPRODUCT((I170=$I$6:$I$170)*(B170=$B$6:$B$170)))</f>
+        <f aca="false">IF(J170="","",SUMPRODUCT((I170=$I$6:$I$1500)*(B170&lt;$B$6:$B$1500))+COUNTIFS($I$6:I170,I170,$B$6:B170,B170))</f>
         <v>5</v>
       </c>
       <c r="N170" s="33" t="s">
@@ -10494,7 +10494,7 @@
         <v>19</v>
       </c>
       <c r="K171" s="25" t="n">
-        <f aca="false">IF(J171="","",SUMPRODUCT((I171=$I$6:$I$1500)*(B171&lt;$B$6:$B$1500))+SUMPRODUCT((I171=$I$6:$I$171)*(B171=$B$6:$B$171)))</f>
+        <f aca="false">IF(J171="","",SUMPRODUCT((I171=$I$6:$I$1500)*(B171&lt;$B$6:$B$1500))+COUNTIFS($I$6:I171,I171,$B$6:B171,B171))</f>
         <v>6</v>
       </c>
       <c r="N171" s="33" t="s">
@@ -10538,7 +10538,7 @@
         <v>25</v>
       </c>
       <c r="K172" s="25" t="n">
-        <f aca="false">IF(J172="","",SUMPRODUCT((I172=$I$6:$I$1500)*(B172&lt;$B$6:$B$1500))+SUMPRODUCT((I172=$I$6:$I$172)*(B172=$B$6:$B$172)))</f>
+        <f aca="false">IF(J172="","",SUMPRODUCT((I172=$I$6:$I$1500)*(B172&lt;$B$6:$B$1500))+COUNTIFS($I$6:I172,I172,$B$6:B172,B172))</f>
         <v>7</v>
       </c>
       <c r="N172" s="33" t="s">
@@ -10582,7 +10582,7 @@
         <v>6</v>
       </c>
       <c r="K173" s="25" t="n">
-        <f aca="false">IF(J173="","",SUMPRODUCT((I173=$I$6:$I$1500)*(B173&lt;$B$6:$B$1500))+SUMPRODUCT((I173=$I$6:$I$173)*(B173=$B$6:$B$173)))</f>
+        <f aca="false">IF(J173="","",SUMPRODUCT((I173=$I$6:$I$1500)*(B173&lt;$B$6:$B$1500))+COUNTIFS($I$6:I173,I173,$B$6:B173,B173))</f>
         <v>8</v>
       </c>
       <c r="N173" s="33" t="s">
@@ -10626,7 +10626,7 @@
         <v>4</v>
       </c>
       <c r="K174" s="25" t="n">
-        <f aca="false">IF(J174="","",SUMPRODUCT((I174=$I$6:$I$1500)*(B174&lt;$B$6:$B$1500))+SUMPRODUCT((I174=$I$6:$I$174)*(B174=$B$6:$B$174)))</f>
+        <f aca="false">IF(J174="","",SUMPRODUCT((I174=$I$6:$I$1500)*(B174&lt;$B$6:$B$1500))+COUNTIFS($I$6:I174,I174,$B$6:B174,B174))</f>
         <v>9</v>
       </c>
       <c r="N174" s="33" t="s">
@@ -10670,7 +10670,7 @@
         <v>1</v>
       </c>
       <c r="K175" s="25" t="n">
-        <f aca="false">IF(J175="","",SUMPRODUCT((I175=$I$6:$I$1500)*(B175&lt;$B$6:$B$1500))+SUMPRODUCT((I175=$I$6:$I$175)*(B175=$B$6:$B$175)))</f>
+        <f aca="false">IF(J175="","",SUMPRODUCT((I175=$I$6:$I$1500)*(B175&lt;$B$6:$B$1500))+COUNTIFS($I$6:I175,I175,$B$6:B175,B175))</f>
         <v>10</v>
       </c>
       <c r="N175" s="33" t="s">
@@ -10714,7 +10714,7 @@
         <v>4</v>
       </c>
       <c r="K176" s="25" t="n">
-        <f aca="false">IF(J176="","",SUMPRODUCT((I176=$I$6:$I$1500)*(B176&lt;$B$6:$B$1500))+SUMPRODUCT((I176=$I$6:$I$176)*(B176=$B$6:$B$176)))</f>
+        <f aca="false">IF(J176="","",SUMPRODUCT((I176=$I$6:$I$1500)*(B176&lt;$B$6:$B$1500))+COUNTIFS($I$6:I176,I176,$B$6:B176,B176))</f>
         <v>11</v>
       </c>
       <c r="N176" s="33" t="s">
@@ -10758,7 +10758,7 @@
         <v>4</v>
       </c>
       <c r="K177" s="25" t="n">
-        <f aca="false">IF(J177="","",SUMPRODUCT((I177=$I$6:$I$1500)*(B177&lt;$B$6:$B$1500))+SUMPRODUCT((I177=$I$6:$I$177)*(B177=$B$6:$B$177)))</f>
+        <f aca="false">IF(J177="","",SUMPRODUCT((I177=$I$6:$I$1500)*(B177&lt;$B$6:$B$1500))+COUNTIFS($I$6:I177,I177,$B$6:B177,B177))</f>
         <v>12</v>
       </c>
       <c r="N177" s="33" t="s">
@@ -10802,7 +10802,7 @@
         <v>1</v>
       </c>
       <c r="K178" s="25" t="n">
-        <f aca="false">IF(J178="","",SUMPRODUCT((I178=$I$6:$I$1500)*(B178&lt;$B$6:$B$1500))+SUMPRODUCT((I178=$I$6:$I$178)*(B178=$B$6:$B$178)))</f>
+        <f aca="false">IF(J178="","",SUMPRODUCT((I178=$I$6:$I$1500)*(B178&lt;$B$6:$B$1500))+COUNTIFS($I$6:I178,I178,$B$6:B178,B178))</f>
         <v>13</v>
       </c>
       <c r="N178" s="33" t="s">
@@ -10846,7 +10846,7 @@
         <v>1</v>
       </c>
       <c r="K179" s="25" t="n">
-        <f aca="false">IF(J179="","",SUMPRODUCT((I179=$I$6:$I$1500)*(B179&lt;$B$6:$B$1500))+SUMPRODUCT((I179=$I$6:$I$179)*(B179=$B$6:$B$179)))</f>
+        <f aca="false">IF(J179="","",SUMPRODUCT((I179=$I$6:$I$1500)*(B179&lt;$B$6:$B$1500))+COUNTIFS($I$6:I179,I179,$B$6:B179,B179))</f>
         <v>14</v>
       </c>
       <c r="N179" s="52" t="s">
@@ -10890,7 +10890,7 @@
         <v>1</v>
       </c>
       <c r="K180" s="25" t="n">
-        <f aca="false">IF(J180="","",SUMPRODUCT((I180=$I$6:$I$1500)*(B180&lt;$B$6:$B$1500))+SUMPRODUCT((I180=$I$6:$I$180)*(B180=$B$6:$B$180)))</f>
+        <f aca="false">IF(J180="","",SUMPRODUCT((I180=$I$6:$I$1500)*(B180&lt;$B$6:$B$1500))+COUNTIFS($I$6:I180,I180,$B$6:B180,B180))</f>
         <v>15</v>
       </c>
       <c r="N180" s="33" t="s">
@@ -10934,7 +10934,7 @@
         <v>4</v>
       </c>
       <c r="K181" s="25" t="n">
-        <f aca="false">IF(J181="","",SUMPRODUCT((I181=$I$6:$I$1500)*(B181&lt;$B$6:$B$1500))+SUMPRODUCT((I181=$I$6:$I$181)*(B181=$B$6:$B$181)))</f>
+        <f aca="false">IF(J181="","",SUMPRODUCT((I181=$I$6:$I$1500)*(B181&lt;$B$6:$B$1500))+COUNTIFS($I$6:I181,I181,$B$6:B181,B181))</f>
         <v>16</v>
       </c>
       <c r="N181" s="33" t="s">
@@ -10978,7 +10978,7 @@
         <v/>
       </c>
       <c r="K182" s="25" t="str">
-        <f aca="false">IF(J182="","",SUMPRODUCT((I182=$I$6:$I$1500)*(B182&lt;$B$6:$B$1500))+SUMPRODUCT((I182=$I$6:$I$182)*(B182=$B$6:$B$182)))</f>
+        <f aca="false">IF(J182="","",SUMPRODUCT((I182=$I$6:$I$1500)*(B182&lt;$B$6:$B$1500))+COUNTIFS($I$6:I182,I182,$B$6:B182,B182))</f>
         <v/>
       </c>
       <c r="N182" s="33" t="s">
@@ -11020,7 +11020,7 @@
         <v/>
       </c>
       <c r="K183" s="25" t="str">
-        <f aca="false">IF(J183="","",SUMPRODUCT((I183=$I$6:$I$1500)*(B183&lt;$B$6:$B$1500))+SUMPRODUCT((I183=$I$6:$I$183)*(B183=$B$6:$B$183)))</f>
+        <f aca="false">IF(J183="","",SUMPRODUCT((I183=$I$6:$I$1500)*(B183&lt;$B$6:$B$1500))+COUNTIFS($I$6:I183,I183,$B$6:B183,B183))</f>
         <v/>
       </c>
       <c r="N183" s="33" t="s">
@@ -11064,7 +11064,7 @@
         <v>189</v>
       </c>
       <c r="K184" s="25" t="n">
-        <f aca="false">IF(J184="","",SUMPRODUCT((I184=$I$6:$I$1500)*(B184&lt;$B$6:$B$1500))+SUMPRODUCT((I184=$I$6:$I$184)*(B184=$B$6:$B$184)))</f>
+        <f aca="false">IF(J184="","",SUMPRODUCT((I184=$I$6:$I$1500)*(B184&lt;$B$6:$B$1500))+COUNTIFS($I$6:I184,I184,$B$6:B184,B184))</f>
         <v>1</v>
       </c>
       <c r="N184" s="33" t="s">
@@ -11108,7 +11108,7 @@
         <v>98</v>
       </c>
       <c r="K185" s="25" t="n">
-        <f aca="false">IF(J185="","",SUMPRODUCT((I185=$I$6:$I$1500)*(B185&lt;$B$6:$B$1500))+SUMPRODUCT((I185=$I$6:$I$185)*(B185=$B$6:$B$185)))</f>
+        <f aca="false">IF(J185="","",SUMPRODUCT((I185=$I$6:$I$1500)*(B185&lt;$B$6:$B$1500))+COUNTIFS($I$6:I185,I185,$B$6:B185,B185))</f>
         <v>2</v>
       </c>
       <c r="N185" s="33" t="s">
@@ -11152,7 +11152,7 @@
         <v>52</v>
       </c>
       <c r="K186" s="25" t="n">
-        <f aca="false">IF(J186="","",SUMPRODUCT((I186=$I$6:$I$1500)*(B186&lt;$B$6:$B$1500))+SUMPRODUCT((I186=$I$6:$I$186)*(B186=$B$6:$B$186)))</f>
+        <f aca="false">IF(J186="","",SUMPRODUCT((I186=$I$6:$I$1500)*(B186&lt;$B$6:$B$1500))+COUNTIFS($I$6:I186,I186,$B$6:B186,B186))</f>
         <v>4</v>
       </c>
       <c r="N186" s="33" t="s">
@@ -11196,7 +11196,7 @@
         <v>19</v>
       </c>
       <c r="K187" s="25" t="n">
-        <f aca="false">IF(J187="","",SUMPRODUCT((I187=$I$6:$I$1500)*(B187&lt;$B$6:$B$1500))+SUMPRODUCT((I187=$I$6:$I$187)*(B187=$B$6:$B$187)))</f>
+        <f aca="false">IF(J187="","",SUMPRODUCT((I187=$I$6:$I$1500)*(B187&lt;$B$6:$B$1500))+COUNTIFS($I$6:I187,I187,$B$6:B187,B187))</f>
         <v>6</v>
       </c>
       <c r="N187" s="33" t="s">
@@ -11240,7 +11240,7 @@
         <v>10</v>
       </c>
       <c r="K188" s="25" t="n">
-        <f aca="false">IF(J188="","",SUMPRODUCT((I188=$I$6:$I$1500)*(B188&lt;$B$6:$B$1500))+SUMPRODUCT((I188=$I$6:$I$188)*(B188=$B$6:$B$188)))</f>
+        <f aca="false">IF(J188="","",SUMPRODUCT((I188=$I$6:$I$1500)*(B188&lt;$B$6:$B$1500))+COUNTIFS($I$6:I188,I188,$B$6:B188,B188))</f>
         <v>7</v>
       </c>
       <c r="N188" s="33" t="s">
@@ -11284,7 +11284,7 @@
         <v>9</v>
       </c>
       <c r="K189" s="25" t="n">
-        <f aca="false">IF(J189="","",SUMPRODUCT((I189=$I$6:$I$1500)*(B189&lt;$B$6:$B$1500))+SUMPRODUCT((I189=$I$6:$I$189)*(B189=$B$6:$B$189)))</f>
+        <f aca="false">IF(J189="","",SUMPRODUCT((I189=$I$6:$I$1500)*(B189&lt;$B$6:$B$1500))+COUNTIFS($I$6:I189,I189,$B$6:B189,B189))</f>
         <v>8</v>
       </c>
       <c r="N189" s="33" t="s">
@@ -11328,7 +11328,7 @@
         <v>8</v>
       </c>
       <c r="K190" s="25" t="n">
-        <f aca="false">IF(J190="","",SUMPRODUCT((I190=$I$6:$I$1500)*(B190&lt;$B$6:$B$1500))+SUMPRODUCT((I190=$I$6:$I$190)*(B190=$B$6:$B$190)))</f>
+        <f aca="false">IF(J190="","",SUMPRODUCT((I190=$I$6:$I$1500)*(B190&lt;$B$6:$B$1500))+COUNTIFS($I$6:I190,I190,$B$6:B190,B190))</f>
         <v>9</v>
       </c>
       <c r="N190" s="33" t="s">
@@ -11372,7 +11372,7 @@
         <v>8</v>
       </c>
       <c r="K191" s="25" t="n">
-        <f aca="false">IF(J191="","",SUMPRODUCT((I191=$I$6:$I$1500)*(B191&lt;$B$6:$B$1500))+SUMPRODUCT((I191=$I$6:$I$191)*(B191=$B$6:$B$191)))</f>
+        <f aca="false">IF(J191="","",SUMPRODUCT((I191=$I$6:$I$1500)*(B191&lt;$B$6:$B$1500))+COUNTIFS($I$6:I191,I191,$B$6:B191,B191))</f>
         <v>10</v>
       </c>
       <c r="N191" s="33" t="s">
@@ -11416,7 +11416,7 @@
         <v>7</v>
       </c>
       <c r="K192" s="25" t="n">
-        <f aca="false">IF(J192="","",SUMPRODUCT((I192=$I$6:$I$1500)*(B192&lt;$B$6:$B$1500))+SUMPRODUCT((I192=$I$6:$I$192)*(B192=$B$6:$B$192)))</f>
+        <f aca="false">IF(J192="","",SUMPRODUCT((I192=$I$6:$I$1500)*(B192&lt;$B$6:$B$1500))+COUNTIFS($I$6:I192,I192,$B$6:B192,B192))</f>
         <v>11</v>
       </c>
       <c r="N192" s="33" t="s">
@@ -11460,7 +11460,7 @@
         <v>6</v>
       </c>
       <c r="K193" s="25" t="n">
-        <f aca="false">IF(J193="","",SUMPRODUCT((I193=$I$6:$I$1500)*(B193&lt;$B$6:$B$1500))+SUMPRODUCT((I193=$I$6:$I$193)*(B193=$B$6:$B$193)))</f>
+        <f aca="false">IF(J193="","",SUMPRODUCT((I193=$I$6:$I$1500)*(B193&lt;$B$6:$B$1500))+COUNTIFS($I$6:I193,I193,$B$6:B193,B193))</f>
         <v>13</v>
       </c>
       <c r="N193" s="33" t="s">
@@ -11504,7 +11504,7 @@
         <v>6</v>
       </c>
       <c r="K194" s="25" t="n">
-        <f aca="false">IF(J194="","",SUMPRODUCT((I194=$I$6:$I$1500)*(B194&lt;$B$6:$B$1500))+SUMPRODUCT((I194=$I$6:$I$194)*(B194=$B$6:$B$194)))</f>
+        <f aca="false">IF(J194="","",SUMPRODUCT((I194=$I$6:$I$1500)*(B194&lt;$B$6:$B$1500))+COUNTIFS($I$6:I194,I194,$B$6:B194,B194))</f>
         <v>14</v>
       </c>
       <c r="N194" s="33" t="s">
@@ -11548,7 +11548,7 @@
         <v>5</v>
       </c>
       <c r="K195" s="25" t="n">
-        <f aca="false">IF(J195="","",SUMPRODUCT((I195=$I$6:$I$1500)*(B195&lt;$B$6:$B$1500))+SUMPRODUCT((I195=$I$6:$I$195)*(B195=$B$6:$B$195)))</f>
+        <f aca="false">IF(J195="","",SUMPRODUCT((I195=$I$6:$I$1500)*(B195&lt;$B$6:$B$1500))+COUNTIFS($I$6:I195,I195,$B$6:B195,B195))</f>
         <v>15</v>
       </c>
       <c r="N195" s="33" t="s">
@@ -11592,7 +11592,7 @@
         <v>4</v>
       </c>
       <c r="K196" s="25" t="n">
-        <f aca="false">IF(J196="","",SUMPRODUCT((I196=$I$6:$I$1500)*(B196&lt;$B$6:$B$1500))+SUMPRODUCT((I196=$I$6:$I$196)*(B196=$B$6:$B$196)))</f>
+        <f aca="false">IF(J196="","",SUMPRODUCT((I196=$I$6:$I$1500)*(B196&lt;$B$6:$B$1500))+COUNTIFS($I$6:I196,I196,$B$6:B196,B196))</f>
         <v>16</v>
       </c>
       <c r="N196" s="33" t="s">
@@ -11636,7 +11636,7 @@
         <v>1</v>
       </c>
       <c r="K197" s="25" t="n">
-        <f aca="false">IF(J197="","",SUMPRODUCT((I197=$I$6:$I$1500)*(B197&lt;$B$6:$B$1500))+SUMPRODUCT((I197=$I$6:$I$197)*(B197=$B$6:$B$197)))</f>
+        <f aca="false">IF(J197="","",SUMPRODUCT((I197=$I$6:$I$1500)*(B197&lt;$B$6:$B$1500))+COUNTIFS($I$6:I197,I197,$B$6:B197,B197))</f>
         <v>17</v>
       </c>
       <c r="N197" s="33" t="s">
@@ -11680,7 +11680,7 @@
         <v>1</v>
       </c>
       <c r="K198" s="25" t="n">
-        <f aca="false">IF(J198="","",SUMPRODUCT((I198=$I$6:$I$1500)*(B198&lt;$B$6:$B$1500))+SUMPRODUCT((I198=$I$6:$I$198)*(B198=$B$6:$B$198)))</f>
+        <f aca="false">IF(J198="","",SUMPRODUCT((I198=$I$6:$I$1500)*(B198&lt;$B$6:$B$1500))+COUNTIFS($I$6:I198,I198,$B$6:B198,B198))</f>
         <v>18</v>
       </c>
       <c r="N198" s="33" t="s">
@@ -11724,7 +11724,7 @@
         <v>1</v>
       </c>
       <c r="K199" s="25" t="n">
-        <f aca="false">IF(J199="","",SUMPRODUCT((I199=$I$6:$I$1500)*(B199&lt;$B$6:$B$1500))+SUMPRODUCT((I199=$I$6:$I$199)*(B199=$B$6:$B$199)))</f>
+        <f aca="false">IF(J199="","",SUMPRODUCT((I199=$I$6:$I$1500)*(B199&lt;$B$6:$B$1500))+COUNTIFS($I$6:I199,I199,$B$6:B199,B199))</f>
         <v>19</v>
       </c>
       <c r="N199" s="33" t="s">
@@ -11768,7 +11768,7 @@
         <v>1</v>
       </c>
       <c r="K200" s="25" t="n">
-        <f aca="false">IF(J200="","",SUMPRODUCT((I200=$I$6:$I$1500)*(B200&lt;$B$6:$B$1500))+SUMPRODUCT((I200=$I$6:$I$200)*(B200=$B$6:$B$200)))</f>
+        <f aca="false">IF(J200="","",SUMPRODUCT((I200=$I$6:$I$1500)*(B200&lt;$B$6:$B$1500))+COUNTIFS($I$6:I200,I200,$B$6:B200,B200))</f>
         <v>20</v>
       </c>
       <c r="N200" s="33" t="s">
@@ -11812,7 +11812,7 @@
         <v>0</v>
       </c>
       <c r="K201" s="25" t="n">
-        <f aca="false">IF(J201="","",SUMPRODUCT((I201=$I$6:$I$1500)*(B201&lt;$B$6:$B$1500))+SUMPRODUCT((I201=$I$6:$I$201)*(B201=$B$6:$B$201)))</f>
+        <f aca="false">IF(J201="","",SUMPRODUCT((I201=$I$6:$I$1500)*(B201&lt;$B$6:$B$1500))+COUNTIFS($I$6:I201,I201,$B$6:B201,B201))</f>
         <v>21</v>
       </c>
       <c r="N201" s="33" t="s">
@@ -11856,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="K202" s="25" t="n">
-        <f aca="false">IF(J202="","",SUMPRODUCT((I202=$I$6:$I$1500)*(B202&lt;$B$6:$B$1500))+SUMPRODUCT((I202=$I$6:$I$202)*(B202=$B$6:$B$202)))</f>
+        <f aca="false">IF(J202="","",SUMPRODUCT((I202=$I$6:$I$1500)*(B202&lt;$B$6:$B$1500))+COUNTIFS($I$6:I202,I202,$B$6:B202,B202))</f>
         <v>22</v>
       </c>
       <c r="N202" s="33" t="s">
@@ -11898,7 +11898,7 @@
         <v/>
       </c>
       <c r="K203" s="25" t="str">
-        <f aca="false">IF(J203="","",SUMPRODUCT((I203=$I$6:$I$1500)*(B203&lt;$B$6:$B$1500))+SUMPRODUCT((I203=$I$6:$I$203)*(B203=$B$6:$B$203)))</f>
+        <f aca="false">IF(J203="","",SUMPRODUCT((I203=$I$6:$I$1500)*(B203&lt;$B$6:$B$1500))+COUNTIFS($I$6:I203,I203,$B$6:B203,B203))</f>
         <v/>
       </c>
       <c r="N203" s="33" t="s">
@@ -11942,7 +11942,7 @@
         <v>24</v>
       </c>
       <c r="K204" s="25" t="n">
-        <f aca="false">IF(J204="","",SUMPRODUCT((I204=$I$6:$I$1500)*(B204&lt;$B$6:$B$1500))+SUMPRODUCT((I204=$I$6:$I$204)*(B204=$B$6:$B$204)))</f>
+        <f aca="false">IF(J204="","",SUMPRODUCT((I204=$I$6:$I$1500)*(B204&lt;$B$6:$B$1500))+COUNTIFS($I$6:I204,I204,$B$6:B204,B204))</f>
         <v>7</v>
       </c>
       <c r="N204" s="33" t="s">
@@ -11986,7 +11986,7 @@
         <v>23</v>
       </c>
       <c r="K205" s="25" t="n">
-        <f aca="false">IF(J205="","",SUMPRODUCT((I205=$I$6:$I$1500)*(B205&lt;$B$6:$B$1500))+SUMPRODUCT((I205=$I$6:$I$205)*(B205=$B$6:$B$205)))</f>
+        <f aca="false">IF(J205="","",SUMPRODUCT((I205=$I$6:$I$1500)*(B205&lt;$B$6:$B$1500))+COUNTIFS($I$6:I205,I205,$B$6:B205,B205))</f>
         <v>8</v>
       </c>
       <c r="N205" s="33" t="s">
@@ -12030,7 +12030,7 @@
         <v>24</v>
       </c>
       <c r="K206" s="25" t="n">
-        <f aca="false">IF(J206="","",SUMPRODUCT((I206=$I$6:$I$1500)*(B206&lt;$B$6:$B$1500))+SUMPRODUCT((I206=$I$6:$I$206)*(B206=$B$6:$B$206)))</f>
+        <f aca="false">IF(J206="","",SUMPRODUCT((I206=$I$6:$I$1500)*(B206&lt;$B$6:$B$1500))+COUNTIFS($I$6:I206,I206,$B$6:B206,B206))</f>
         <v>9</v>
       </c>
       <c r="N206" s="33" t="s">
@@ -12074,7 +12074,7 @@
         <v>15</v>
       </c>
       <c r="K207" s="25" t="n">
-        <f aca="false">IF(J207="","",SUMPRODUCT((I207=$I$6:$I$1500)*(B207&lt;$B$6:$B$1500))+SUMPRODUCT((I207=$I$6:$I$207)*(B207=$B$6:$B$207)))</f>
+        <f aca="false">IF(J207="","",SUMPRODUCT((I207=$I$6:$I$1500)*(B207&lt;$B$6:$B$1500))+COUNTIFS($I$6:I207,I207,$B$6:B207,B207))</f>
         <v>10</v>
       </c>
       <c r="N207" s="33" t="s">
@@ -12118,7 +12118,7 @@
         <v>13</v>
       </c>
       <c r="K208" s="25" t="n">
-        <f aca="false">IF(J208="","",SUMPRODUCT((I208=$I$6:$I$1500)*(B208&lt;$B$6:$B$1500))+SUMPRODUCT((I208=$I$6:$I$208)*(B208=$B$6:$B$208)))</f>
+        <f aca="false">IF(J208="","",SUMPRODUCT((I208=$I$6:$I$1500)*(B208&lt;$B$6:$B$1500))+COUNTIFS($I$6:I208,I208,$B$6:B208,B208))</f>
         <v>11</v>
       </c>
       <c r="N208" s="52" t="s">
@@ -12162,7 +12162,7 @@
         <v>8</v>
       </c>
       <c r="K209" s="25" t="n">
-        <f aca="false">IF(J209="","",SUMPRODUCT((I209=$I$6:$I$1500)*(B209&lt;$B$6:$B$1500))+SUMPRODUCT((I209=$I$6:$I$209)*(B209=$B$6:$B$209)))</f>
+        <f aca="false">IF(J209="","",SUMPRODUCT((I209=$I$6:$I$1500)*(B209&lt;$B$6:$B$1500))+COUNTIFS($I$6:I209,I209,$B$6:B209,B209))</f>
         <v>12</v>
       </c>
       <c r="N209" s="33" t="s">
@@ -12206,7 +12206,7 @@
         <v>7</v>
       </c>
       <c r="K210" s="25" t="n">
-        <f aca="false">IF(J210="","",SUMPRODUCT((I210=$I$6:$I$1500)*(B210&lt;$B$6:$B$1500))+SUMPRODUCT((I210=$I$6:$I$210)*(B210=$B$6:$B$210)))</f>
+        <f aca="false">IF(J210="","",SUMPRODUCT((I210=$I$6:$I$1500)*(B210&lt;$B$6:$B$1500))+COUNTIFS($I$6:I210,I210,$B$6:B210,B210))</f>
         <v>13</v>
       </c>
       <c r="N210" s="33" t="s">
@@ -12250,7 +12250,7 @@
         <v>6</v>
       </c>
       <c r="K211" s="25" t="n">
-        <f aca="false">IF(J211="","",SUMPRODUCT((I211=$I$6:$I$1500)*(B211&lt;$B$6:$B$1500))+SUMPRODUCT((I211=$I$6:$I$211)*(B211=$B$6:$B$211)))</f>
+        <f aca="false">IF(J211="","",SUMPRODUCT((I211=$I$6:$I$1500)*(B211&lt;$B$6:$B$1500))+COUNTIFS($I$6:I211,I211,$B$6:B211,B211))</f>
         <v>14</v>
       </c>
       <c r="N211" s="33" t="s">
@@ -12294,7 +12294,7 @@
         <v>3</v>
       </c>
       <c r="K212" s="25" t="n">
-        <f aca="false">IF(J212="","",SUMPRODUCT((I212=$I$6:$I$1500)*(B212&lt;$B$6:$B$1500))+SUMPRODUCT((I212=$I$6:$I$212)*(B212=$B$6:$B$212)))</f>
+        <f aca="false">IF(J212="","",SUMPRODUCT((I212=$I$6:$I$1500)*(B212&lt;$B$6:$B$1500))+COUNTIFS($I$6:I212,I212,$B$6:B212,B212))</f>
         <v>16</v>
       </c>
       <c r="N212" s="33" t="s">
@@ -12338,7 +12338,7 @@
         <v>4</v>
       </c>
       <c r="K213" s="25" t="n">
-        <f aca="false">IF(J213="","",SUMPRODUCT((I213=$I$6:$I$1500)*(B213&lt;$B$6:$B$1500))+SUMPRODUCT((I213=$I$6:$I$213)*(B213=$B$6:$B$213)))</f>
+        <f aca="false">IF(J213="","",SUMPRODUCT((I213=$I$6:$I$1500)*(B213&lt;$B$6:$B$1500))+COUNTIFS($I$6:I213,I213,$B$6:B213,B213))</f>
         <v>17</v>
       </c>
       <c r="N213" s="33" t="s">
@@ -12380,7 +12380,7 @@
         <v/>
       </c>
       <c r="K214" s="25" t="str">
-        <f aca="false">IF(J214="","",SUMPRODUCT((I214=$I$6:$I$1500)*(B214&lt;$B$6:$B$1500))+SUMPRODUCT((I214=$I$6:$I$214)*(B214=$B$6:$B$214)))</f>
+        <f aca="false">IF(J214="","",SUMPRODUCT((I214=$I$6:$I$1500)*(B214&lt;$B$6:$B$1500))+COUNTIFS($I$6:I214,I214,$B$6:B214,B214))</f>
         <v/>
       </c>
       <c r="N214" s="33" t="s">
@@ -12424,7 +12424,7 @@
         <v/>
       </c>
       <c r="K215" s="25" t="str">
-        <f aca="false">IF(J215="","",SUMPRODUCT((I215=$I$6:$I$1500)*(B215&lt;$B$6:$B$1500))+SUMPRODUCT((I215=$I$6:$I$215)*(B215=$B$6:$B$215)))</f>
+        <f aca="false">IF(J215="","",SUMPRODUCT((I215=$I$6:$I$1500)*(B215&lt;$B$6:$B$1500))+COUNTIFS($I$6:I215,I215,$B$6:B215,B215))</f>
         <v/>
       </c>
       <c r="N215" s="33" t="s">
@@ -12468,7 +12468,7 @@
         <v/>
       </c>
       <c r="K216" s="25" t="str">
-        <f aca="false">IF(J216="","",SUMPRODUCT((I216=$I$6:$I$1500)*(B216&lt;$B$6:$B$1500))+SUMPRODUCT((I216=$I$6:$I$216)*(B216=$B$6:$B$216)))</f>
+        <f aca="false">IF(J216="","",SUMPRODUCT((I216=$I$6:$I$1500)*(B216&lt;$B$6:$B$1500))+COUNTIFS($I$6:I216,I216,$B$6:B216,B216))</f>
         <v/>
       </c>
       <c r="N216" s="33" t="s">
@@ -12512,7 +12512,7 @@
         <v/>
       </c>
       <c r="K217" s="25" t="str">
-        <f aca="false">IF(J217="","",SUMPRODUCT((I217=$I$6:$I$1500)*(B217&lt;$B$6:$B$1500))+SUMPRODUCT((I217=$I$6:$I$217)*(B217=$B$6:$B$217)))</f>
+        <f aca="false">IF(J217="","",SUMPRODUCT((I217=$I$6:$I$1500)*(B217&lt;$B$6:$B$1500))+COUNTIFS($I$6:I217,I217,$B$6:B217,B217))</f>
         <v/>
       </c>
       <c r="N217" s="33" t="s">
@@ -12556,7 +12556,7 @@
         <v/>
       </c>
       <c r="K218" s="25" t="str">
-        <f aca="false">IF(J218="","",SUMPRODUCT((I218=$I$6:$I$1500)*(B218&lt;$B$6:$B$1500))+SUMPRODUCT((I218=$I$6:$I$218)*(B218=$B$6:$B$218)))</f>
+        <f aca="false">IF(J218="","",SUMPRODUCT((I218=$I$6:$I$1500)*(B218&lt;$B$6:$B$1500))+COUNTIFS($I$6:I218,I218,$B$6:B218,B218))</f>
         <v/>
       </c>
       <c r="N218" s="33" t="s">
@@ -12600,7 +12600,7 @@
         <v/>
       </c>
       <c r="K219" s="25" t="str">
-        <f aca="false">IF(J219="","",SUMPRODUCT((I219=$I$6:$I$1500)*(B219&lt;$B$6:$B$1500))+SUMPRODUCT((I219=$I$6:$I$219)*(B219=$B$6:$B$219)))</f>
+        <f aca="false">IF(J219="","",SUMPRODUCT((I219=$I$6:$I$1500)*(B219&lt;$B$6:$B$1500))+COUNTIFS($I$6:I219,I219,$B$6:B219,B219))</f>
         <v/>
       </c>
       <c r="N219" s="33" t="s">
@@ -12644,7 +12644,7 @@
         <v/>
       </c>
       <c r="K220" s="25" t="str">
-        <f aca="false">IF(J220="","",SUMPRODUCT((I220=$I$6:$I$1500)*(B220&lt;$B$6:$B$1500))+SUMPRODUCT((I220=$I$6:$I$220)*(B220=$B$6:$B$220)))</f>
+        <f aca="false">IF(J220="","",SUMPRODUCT((I220=$I$6:$I$1500)*(B220&lt;$B$6:$B$1500))+COUNTIFS($I$6:I220,I220,$B$6:B220,B220))</f>
         <v/>
       </c>
       <c r="N220" s="33" t="s">
@@ -12688,7 +12688,7 @@
         <v/>
       </c>
       <c r="K221" s="25" t="str">
-        <f aca="false">IF(J221="","",SUMPRODUCT((I221=$I$6:$I$1500)*(B221&lt;$B$6:$B$1500))+SUMPRODUCT((I221=$I$6:$I$221)*(B221=$B$6:$B$221)))</f>
+        <f aca="false">IF(J221="","",SUMPRODUCT((I221=$I$6:$I$1500)*(B221&lt;$B$6:$B$1500))+COUNTIFS($I$6:I221,I221,$B$6:B221,B221))</f>
         <v/>
       </c>
       <c r="N221" s="33" t="s">
@@ -12732,7 +12732,7 @@
         <v/>
       </c>
       <c r="K222" s="25" t="str">
-        <f aca="false">IF(J222="","",SUMPRODUCT((I222=$I$6:$I$1500)*(B222&lt;$B$6:$B$1500))+SUMPRODUCT((I222=$I$6:$I$222)*(B222=$B$6:$B$222)))</f>
+        <f aca="false">IF(J222="","",SUMPRODUCT((I222=$I$6:$I$1500)*(B222&lt;$B$6:$B$1500))+COUNTIFS($I$6:I222,I222,$B$6:B222,B222))</f>
         <v/>
       </c>
       <c r="N222" s="33" t="s">
@@ -12776,7 +12776,7 @@
         <v/>
       </c>
       <c r="K223" s="25" t="str">
-        <f aca="false">IF(J223="","",SUMPRODUCT((I223=$I$6:$I$1500)*(B223&lt;$B$6:$B$1500))+SUMPRODUCT((I223=$I$6:$I$223)*(B223=$B$6:$B$223)))</f>
+        <f aca="false">IF(J223="","",SUMPRODUCT((I223=$I$6:$I$1500)*(B223&lt;$B$6:$B$1500))+COUNTIFS($I$6:I223,I223,$B$6:B223,B223))</f>
         <v/>
       </c>
       <c r="N223" s="33" t="s">
@@ -12820,7 +12820,7 @@
         <v/>
       </c>
       <c r="K224" s="25" t="str">
-        <f aca="false">IF(J224="","",SUMPRODUCT((I224=$I$6:$I$1500)*(B224&lt;$B$6:$B$1500))+SUMPRODUCT((I224=$I$6:$I$224)*(B224=$B$6:$B$224)))</f>
+        <f aca="false">IF(J224="","",SUMPRODUCT((I224=$I$6:$I$1500)*(B224&lt;$B$6:$B$1500))+COUNTIFS($I$6:I224,I224,$B$6:B224,B224))</f>
         <v/>
       </c>
       <c r="N224" s="33" t="s">
@@ -12864,7 +12864,7 @@
         <v/>
       </c>
       <c r="K225" s="25" t="str">
-        <f aca="false">IF(J225="","",SUMPRODUCT((I225=$I$6:$I$1500)*(B225&lt;$B$6:$B$1500))+SUMPRODUCT((I225=$I$6:$I$225)*(B225=$B$6:$B$225)))</f>
+        <f aca="false">IF(J225="","",SUMPRODUCT((I225=$I$6:$I$1500)*(B225&lt;$B$6:$B$1500))+COUNTIFS($I$6:I225,I225,$B$6:B225,B225))</f>
         <v/>
       </c>
       <c r="N225" s="33" t="s">
@@ -12908,7 +12908,7 @@
         <v/>
       </c>
       <c r="K226" s="25" t="str">
-        <f aca="false">IF(J226="","",SUMPRODUCT((I226=$I$6:$I$1500)*(B226&lt;$B$6:$B$1500))+SUMPRODUCT((I226=$I$6:$I$226)*(B226=$B$6:$B$226)))</f>
+        <f aca="false">IF(J226="","",SUMPRODUCT((I226=$I$6:$I$1500)*(B226&lt;$B$6:$B$1500))+COUNTIFS($I$6:I226,I226,$B$6:B226,B226))</f>
         <v/>
       </c>
       <c r="N226" s="33" t="s">
@@ -12952,7 +12952,7 @@
         <v/>
       </c>
       <c r="K227" s="25" t="str">
-        <f aca="false">IF(J227="","",SUMPRODUCT((I227=$I$6:$I$1500)*(B227&lt;$B$6:$B$1500))+SUMPRODUCT((I227=$I$6:$I$227)*(B227=$B$6:$B$227)))</f>
+        <f aca="false">IF(J227="","",SUMPRODUCT((I227=$I$6:$I$1500)*(B227&lt;$B$6:$B$1500))+COUNTIFS($I$6:I227,I227,$B$6:B227,B227))</f>
         <v/>
       </c>
       <c r="N227" s="33" t="s">
@@ -12996,7 +12996,7 @@
         <v/>
       </c>
       <c r="K228" s="25" t="str">
-        <f aca="false">IF(J228="","",SUMPRODUCT((I228=$I$6:$I$1500)*(B228&lt;$B$6:$B$1500))+SUMPRODUCT((I228=$I$6:$I$228)*(B228=$B$6:$B$228)))</f>
+        <f aca="false">IF(J228="","",SUMPRODUCT((I228=$I$6:$I$1500)*(B228&lt;$B$6:$B$1500))+COUNTIFS($I$6:I228,I228,$B$6:B228,B228))</f>
         <v/>
       </c>
       <c r="N228" s="33" t="s">
@@ -13040,7 +13040,7 @@
         <v/>
       </c>
       <c r="K229" s="25" t="str">
-        <f aca="false">IF(J229="","",SUMPRODUCT((I229=$I$6:$I$1500)*(B229&lt;$B$6:$B$1500))+SUMPRODUCT((I229=$I$6:$I$229)*(B229=$B$6:$B$229)))</f>
+        <f aca="false">IF(J229="","",SUMPRODUCT((I229=$I$6:$I$1500)*(B229&lt;$B$6:$B$1500))+COUNTIFS($I$6:I229,I229,$B$6:B229,B229))</f>
         <v/>
       </c>
       <c r="N229" s="33" t="s">
@@ -13082,7 +13082,7 @@
         <v/>
       </c>
       <c r="K230" s="25" t="str">
-        <f aca="false">IF(J230="","",SUMPRODUCT((I230=$I$6:$I$1500)*(B230&lt;$B$6:$B$1500))+SUMPRODUCT((I230=$I$6:$I$230)*(B230=$B$6:$B$230)))</f>
+        <f aca="false">IF(J230="","",SUMPRODUCT((I230=$I$6:$I$1500)*(B230&lt;$B$6:$B$1500))+COUNTIFS($I$6:I230,I230,$B$6:B230,B230))</f>
         <v/>
       </c>
       <c r="N230" s="33" t="s">
@@ -13126,7 +13126,7 @@
         <v>33</v>
       </c>
       <c r="K231" s="25" t="n">
-        <f aca="false">IF(J231="","",SUMPRODUCT((I231=$I$6:$I$1500)*(B231&lt;$B$6:$B$1500))+SUMPRODUCT((I231=$I$6:$I$231)*(B231=$B$6:$B$231)))</f>
+        <f aca="false">IF(J231="","",SUMPRODUCT((I231=$I$6:$I$1500)*(B231&lt;$B$6:$B$1500))+COUNTIFS($I$6:I231,I231,$B$6:B231,B231))</f>
         <v>1</v>
       </c>
       <c r="N231" s="33" t="s">
@@ -13170,7 +13170,7 @@
         <v>25</v>
       </c>
       <c r="K232" s="25" t="n">
-        <f aca="false">IF(J232="","",SUMPRODUCT((I232=$I$6:$I$1500)*(B232&lt;$B$6:$B$1500))+SUMPRODUCT((I232=$I$6:$I$232)*(B232=$B$6:$B$232)))</f>
+        <f aca="false">IF(J232="","",SUMPRODUCT((I232=$I$6:$I$1500)*(B232&lt;$B$6:$B$1500))+COUNTIFS($I$6:I232,I232,$B$6:B232,B232))</f>
         <v>2</v>
       </c>
       <c r="N232" s="33" t="s">
@@ -13214,7 +13214,7 @@
         <v>44</v>
       </c>
       <c r="K233" s="25" t="n">
-        <f aca="false">IF(J233="","",SUMPRODUCT((I233=$I$6:$I$1500)*(B233&lt;$B$6:$B$1500))+SUMPRODUCT((I233=$I$6:$I$233)*(B233=$B$6:$B$233)))</f>
+        <f aca="false">IF(J233="","",SUMPRODUCT((I233=$I$6:$I$1500)*(B233&lt;$B$6:$B$1500))+COUNTIFS($I$6:I233,I233,$B$6:B233,B233))</f>
         <v>3</v>
       </c>
       <c r="N233" s="33" t="s">
@@ -13258,7 +13258,7 @@
         <v>22</v>
       </c>
       <c r="K234" s="25" t="n">
-        <f aca="false">IF(J234="","",SUMPRODUCT((I234=$I$6:$I$1500)*(B234&lt;$B$6:$B$1500))+SUMPRODUCT((I234=$I$6:$I$234)*(B234=$B$6:$B$234)))</f>
+        <f aca="false">IF(J234="","",SUMPRODUCT((I234=$I$6:$I$1500)*(B234&lt;$B$6:$B$1500))+COUNTIFS($I$6:I234,I234,$B$6:B234,B234))</f>
         <v>4</v>
       </c>
       <c r="N234" s="33" t="s">
@@ -13302,7 +13302,7 @@
         <v>14</v>
       </c>
       <c r="K235" s="25" t="n">
-        <f aca="false">IF(J235="","",SUMPRODUCT((I235=$I$6:$I$1500)*(B235&lt;$B$6:$B$1500))+SUMPRODUCT((I235=$I$6:$I$235)*(B235=$B$6:$B$235)))</f>
+        <f aca="false">IF(J235="","",SUMPRODUCT((I235=$I$6:$I$1500)*(B235&lt;$B$6:$B$1500))+COUNTIFS($I$6:I235,I235,$B$6:B235,B235))</f>
         <v>5</v>
       </c>
       <c r="N235" s="33" t="s">
@@ -13346,7 +13346,7 @@
         <v>15</v>
       </c>
       <c r="K236" s="25" t="n">
-        <f aca="false">IF(J236="","",SUMPRODUCT((I236=$I$6:$I$1500)*(B236&lt;$B$6:$B$1500))+SUMPRODUCT((I236=$I$6:$I$236)*(B236=$B$6:$B$236)))</f>
+        <f aca="false">IF(J236="","",SUMPRODUCT((I236=$I$6:$I$1500)*(B236&lt;$B$6:$B$1500))+COUNTIFS($I$6:I236,I236,$B$6:B236,B236))</f>
         <v>6</v>
       </c>
       <c r="N236" s="33" t="s">
@@ -13390,7 +13390,7 @@
         <v>11</v>
       </c>
       <c r="K237" s="25" t="n">
-        <f aca="false">IF(J237="","",SUMPRODUCT((I237=$I$6:$I$1500)*(B237&lt;$B$6:$B$1500))+SUMPRODUCT((I237=$I$6:$I$237)*(B237=$B$6:$B$237)))</f>
+        <f aca="false">IF(J237="","",SUMPRODUCT((I237=$I$6:$I$1500)*(B237&lt;$B$6:$B$1500))+COUNTIFS($I$6:I237,I237,$B$6:B237,B237))</f>
         <v>7</v>
       </c>
       <c r="N237" s="33" t="s">
@@ -13434,7 +13434,7 @@
         <v>13</v>
       </c>
       <c r="K238" s="25" t="n">
-        <f aca="false">IF(J238="","",SUMPRODUCT((I238=$I$6:$I$1500)*(B238&lt;$B$6:$B$1500))+SUMPRODUCT((I238=$I$6:$I$238)*(B238=$B$6:$B$238)))</f>
+        <f aca="false">IF(J238="","",SUMPRODUCT((I238=$I$6:$I$1500)*(B238&lt;$B$6:$B$1500))+COUNTIFS($I$6:I238,I238,$B$6:B238,B238))</f>
         <v>8</v>
       </c>
       <c r="N238" s="33" t="s">
@@ -13478,7 +13478,7 @@
         <v>6</v>
       </c>
       <c r="K239" s="25" t="n">
-        <f aca="false">IF(J239="","",SUMPRODUCT((I239=$I$6:$I$1500)*(B239&lt;$B$6:$B$1500))+SUMPRODUCT((I239=$I$6:$I$239)*(B239=$B$6:$B$239)))</f>
+        <f aca="false">IF(J239="","",SUMPRODUCT((I239=$I$6:$I$1500)*(B239&lt;$B$6:$B$1500))+COUNTIFS($I$6:I239,I239,$B$6:B239,B239))</f>
         <v>9</v>
       </c>
       <c r="N239" s="33" t="s">
@@ -13522,7 +13522,7 @@
         <v>6</v>
       </c>
       <c r="K240" s="25" t="n">
-        <f aca="false">IF(J240="","",SUMPRODUCT((I240=$I$6:$I$1500)*(B240&lt;$B$6:$B$1500))+SUMPRODUCT((I240=$I$6:$I$240)*(B240=$B$6:$B$240)))</f>
+        <f aca="false">IF(J240="","",SUMPRODUCT((I240=$I$6:$I$1500)*(B240&lt;$B$6:$B$1500))+COUNTIFS($I$6:I240,I240,$B$6:B240,B240))</f>
         <v>10</v>
       </c>
       <c r="N240" s="33" t="s">
@@ -13566,7 +13566,7 @@
         <v>6</v>
       </c>
       <c r="K241" s="25" t="n">
-        <f aca="false">IF(J241="","",SUMPRODUCT((I241=$I$6:$I$1500)*(B241&lt;$B$6:$B$1500))+SUMPRODUCT((I241=$I$6:$I$241)*(B241=$B$6:$B$241)))</f>
+        <f aca="false">IF(J241="","",SUMPRODUCT((I241=$I$6:$I$1500)*(B241&lt;$B$6:$B$1500))+COUNTIFS($I$6:I241,I241,$B$6:B241,B241))</f>
         <v>11</v>
       </c>
       <c r="N241" s="33" t="s">
@@ -13610,7 +13610,7 @@
         <v>6</v>
       </c>
       <c r="K242" s="25" t="n">
-        <f aca="false">IF(J242="","",SUMPRODUCT((I242=$I$6:$I$1500)*(B242&lt;$B$6:$B$1500))+SUMPRODUCT((I242=$I$6:$I$242)*(B242=$B$6:$B$242)))</f>
+        <f aca="false">IF(J242="","",SUMPRODUCT((I242=$I$6:$I$1500)*(B242&lt;$B$6:$B$1500))+COUNTIFS($I$6:I242,I242,$B$6:B242,B242))</f>
         <v>12</v>
       </c>
       <c r="N242" s="52" t="s">
@@ -13654,7 +13654,7 @@
         <v>4</v>
       </c>
       <c r="K243" s="25" t="n">
-        <f aca="false">IF(J243="","",SUMPRODUCT((I243=$I$6:$I$1500)*(B243&lt;$B$6:$B$1500))+SUMPRODUCT((I243=$I$6:$I$243)*(B243=$B$6:$B$243)))</f>
+        <f aca="false">IF(J243="","",SUMPRODUCT((I243=$I$6:$I$1500)*(B243&lt;$B$6:$B$1500))+COUNTIFS($I$6:I243,I243,$B$6:B243,B243))</f>
         <v>13</v>
       </c>
       <c r="N243" s="33" t="s">
@@ -13698,7 +13698,7 @@
         <v>2</v>
       </c>
       <c r="K244" s="25" t="n">
-        <f aca="false">IF(J244="","",SUMPRODUCT((I244=$I$6:$I$1500)*(B244&lt;$B$6:$B$1500))+SUMPRODUCT((I244=$I$6:$I$244)*(B244=$B$6:$B$244)))</f>
+        <f aca="false">IF(J244="","",SUMPRODUCT((I244=$I$6:$I$1500)*(B244&lt;$B$6:$B$1500))+COUNTIFS($I$6:I244,I244,$B$6:B244,B244))</f>
         <v>14</v>
       </c>
       <c r="N244" s="33" t="s">
@@ -13742,7 +13742,7 @@
         <v>2</v>
       </c>
       <c r="K245" s="25" t="n">
-        <f aca="false">IF(J245="","",SUMPRODUCT((I245=$I$6:$I$1500)*(B245&lt;$B$6:$B$1500))+SUMPRODUCT((I245=$I$6:$I$245)*(B245=$B$6:$B$245)))</f>
+        <f aca="false">IF(J245="","",SUMPRODUCT((I245=$I$6:$I$1500)*(B245&lt;$B$6:$B$1500))+COUNTIFS($I$6:I245,I245,$B$6:B245,B245))</f>
         <v>15</v>
       </c>
       <c r="N245" s="33" t="s">
@@ -13786,7 +13786,7 @@
         <v>2</v>
       </c>
       <c r="K246" s="25" t="n">
-        <f aca="false">IF(J246="","",SUMPRODUCT((I246=$I$6:$I$1500)*(B246&lt;$B$6:$B$1500))+SUMPRODUCT((I246=$I$6:$I$246)*(B246=$B$6:$B$246)))</f>
+        <f aca="false">IF(J246="","",SUMPRODUCT((I246=$I$6:$I$1500)*(B246&lt;$B$6:$B$1500))+COUNTIFS($I$6:I246,I246,$B$6:B246,B246))</f>
         <v>16</v>
       </c>
       <c r="N246" s="33" t="s">
@@ -13830,7 +13830,7 @@
         <v>1</v>
       </c>
       <c r="K247" s="25" t="n">
-        <f aca="false">IF(J247="","",SUMPRODUCT((I247=$I$6:$I$1500)*(B247&lt;$B$6:$B$1500))+SUMPRODUCT((I247=$I$6:$I$247)*(B247=$B$6:$B$247)))</f>
+        <f aca="false">IF(J247="","",SUMPRODUCT((I247=$I$6:$I$1500)*(B247&lt;$B$6:$B$1500))+COUNTIFS($I$6:I247,I247,$B$6:B247,B247))</f>
         <v>17</v>
       </c>
       <c r="N247" s="33" t="s">
@@ -13872,7 +13872,7 @@
         <v/>
       </c>
       <c r="K248" s="25" t="str">
-        <f aca="false">IF(J248="","",SUMPRODUCT((I248=$I$6:$I$1500)*(B248&lt;$B$6:$B$1500))+SUMPRODUCT((I248=$I$6:$I$248)*(B248=$B$6:$B$248)))</f>
+        <f aca="false">IF(J248="","",SUMPRODUCT((I248=$I$6:$I$1500)*(B248&lt;$B$6:$B$1500))+COUNTIFS($I$6:I248,I248,$B$6:B248,B248))</f>
         <v/>
       </c>
       <c r="N248" s="33" t="s">
@@ -13916,7 +13916,7 @@
         <v>47</v>
       </c>
       <c r="K249" s="25" t="n">
-        <f aca="false">IF(J249="","",SUMPRODUCT((I249=$I$6:$I$1500)*(B249&lt;$B$6:$B$1500))+SUMPRODUCT((I249=$I$6:$I$249)*(B249=$B$6:$B$249)))</f>
+        <f aca="false">IF(J249="","",SUMPRODUCT((I249=$I$6:$I$1500)*(B249&lt;$B$6:$B$1500))+COUNTIFS($I$6:I249,I249,$B$6:B249,B249))</f>
         <v>4</v>
       </c>
       <c r="N249" s="33" t="s">
@@ -13960,7 +13960,7 @@
         <v>34</v>
       </c>
       <c r="K250" s="25" t="n">
-        <f aca="false">IF(J250="","",SUMPRODUCT((I250=$I$6:$I$1500)*(B250&lt;$B$6:$B$1500))+SUMPRODUCT((I250=$I$6:$I$250)*(B250=$B$6:$B$250)))</f>
+        <f aca="false">IF(J250="","",SUMPRODUCT((I250=$I$6:$I$1500)*(B250&lt;$B$6:$B$1500))+COUNTIFS($I$6:I250,I250,$B$6:B250,B250))</f>
         <v>5</v>
       </c>
       <c r="N250" s="33" t="s">
@@ -14002,7 +14002,7 @@
         <v/>
       </c>
       <c r="K251" s="25" t="str">
-        <f aca="false">IF(J251="","",SUMPRODUCT((I251=$I$6:$I$1500)*(B251&lt;$B$6:$B$1500))+SUMPRODUCT((I251=$I$6:$I$251)*(B251=$B$6:$B$251)))</f>
+        <f aca="false">IF(J251="","",SUMPRODUCT((I251=$I$6:$I$1500)*(B251&lt;$B$6:$B$1500))+COUNTIFS($I$6:I251,I251,$B$6:B251,B251))</f>
         <v/>
       </c>
       <c r="N251" s="33" t="s">
@@ -14046,7 +14046,7 @@
         <v>47</v>
       </c>
       <c r="K252" s="25" t="n">
-        <f aca="false">IF(J252="","",SUMPRODUCT((I252=$I$6:$I$1500)*(B252&lt;$B$6:$B$1500))+SUMPRODUCT((I252=$I$6:$I$252)*(B252=$B$6:$B$252)))</f>
+        <f aca="false">IF(J252="","",SUMPRODUCT((I252=$I$6:$I$1500)*(B252&lt;$B$6:$B$1500))+COUNTIFS($I$6:I252,I252,$B$6:B252,B252))</f>
         <v>1</v>
       </c>
       <c r="N252" s="33" t="s">
@@ -14090,7 +14090,7 @@
         <v>34</v>
       </c>
       <c r="K253" s="25" t="n">
-        <f aca="false">IF(J253="","",SUMPRODUCT((I253=$I$6:$I$1500)*(B253&lt;$B$6:$B$1500))+SUMPRODUCT((I253=$I$6:$I$253)*(B253=$B$6:$B$253)))</f>
+        <f aca="false">IF(J253="","",SUMPRODUCT((I253=$I$6:$I$1500)*(B253&lt;$B$6:$B$1500))+COUNTIFS($I$6:I253,I253,$B$6:B253,B253))</f>
         <v>2</v>
       </c>
       <c r="N253" s="33" t="s">
@@ -14134,7 +14134,7 @@
         <v>30</v>
       </c>
       <c r="K254" s="25" t="n">
-        <f aca="false">IF(J254="","",SUMPRODUCT((I254=$I$6:$I$1500)*(B254&lt;$B$6:$B$1500))+SUMPRODUCT((I254=$I$6:$I$254)*(B254=$B$6:$B$254)))</f>
+        <f aca="false">IF(J254="","",SUMPRODUCT((I254=$I$6:$I$1500)*(B254&lt;$B$6:$B$1500))+COUNTIFS($I$6:I254,I254,$B$6:B254,B254))</f>
         <v>3</v>
       </c>
       <c r="N254" s="33" t="s">
@@ -14178,7 +14178,7 @@
         <v>1</v>
       </c>
       <c r="K255" s="25" t="n">
-        <f aca="false">IF(J255="","",SUMPRODUCT((I255=$I$6:$I$1500)*(B255&lt;$B$6:$B$1500))+SUMPRODUCT((I255=$I$6:$I$255)*(B255=$B$6:$B$255)))</f>
+        <f aca="false">IF(J255="","",SUMPRODUCT((I255=$I$6:$I$1500)*(B255&lt;$B$6:$B$1500))+COUNTIFS($I$6:I255,I255,$B$6:B255,B255))</f>
         <v>4</v>
       </c>
       <c r="N255" s="33" t="s">
@@ -14222,7 +14222,7 @@
         <v>7</v>
       </c>
       <c r="K256" s="25" t="n">
-        <f aca="false">IF(J256="","",SUMPRODUCT((I256=$I$6:$I$1500)*(B256&lt;$B$6:$B$1500))+SUMPRODUCT((I256=$I$6:$I$256)*(B256=$B$6:$B$256)))</f>
+        <f aca="false">IF(J256="","",SUMPRODUCT((I256=$I$6:$I$1500)*(B256&lt;$B$6:$B$1500))+COUNTIFS($I$6:I256,I256,$B$6:B256,B256))</f>
         <v>5</v>
       </c>
       <c r="N256" s="33" t="s">
@@ -14266,7 +14266,7 @@
         <v>8</v>
       </c>
       <c r="K257" s="25" t="n">
-        <f aca="false">IF(J257="","",SUMPRODUCT((I257=$I$6:$I$1500)*(B257&lt;$B$6:$B$1500))+SUMPRODUCT((I257=$I$6:$I$257)*(B257=$B$6:$B$257)))</f>
+        <f aca="false">IF(J257="","",SUMPRODUCT((I257=$I$6:$I$1500)*(B257&lt;$B$6:$B$1500))+COUNTIFS($I$6:I257,I257,$B$6:B257,B257))</f>
         <v>6</v>
       </c>
       <c r="N257" s="33" t="s">
@@ -14310,7 +14310,7 @@
         <v>12</v>
       </c>
       <c r="K258" s="25" t="n">
-        <f aca="false">IF(J258="","",SUMPRODUCT((I258=$I$6:$I$1500)*(B258&lt;$B$6:$B$1500))+SUMPRODUCT((I258=$I$6:$I$258)*(B258=$B$6:$B$258)))</f>
+        <f aca="false">IF(J258="","",SUMPRODUCT((I258=$I$6:$I$1500)*(B258&lt;$B$6:$B$1500))+COUNTIFS($I$6:I258,I258,$B$6:B258,B258))</f>
         <v>7</v>
       </c>
       <c r="N258" s="33" t="s">
@@ -14354,7 +14354,7 @@
         <v>1</v>
       </c>
       <c r="K259" s="25" t="n">
-        <f aca="false">IF(J259="","",SUMPRODUCT((I259=$I$6:$I$1500)*(B259&lt;$B$6:$B$1500))+SUMPRODUCT((I259=$I$6:$I$259)*(B259=$B$6:$B$259)))</f>
+        <f aca="false">IF(J259="","",SUMPRODUCT((I259=$I$6:$I$1500)*(B259&lt;$B$6:$B$1500))+COUNTIFS($I$6:I259,I259,$B$6:B259,B259))</f>
         <v>8</v>
       </c>
       <c r="N259" s="33" t="s">
@@ -14396,7 +14396,7 @@
         <v/>
       </c>
       <c r="K260" s="25" t="str">
-        <f aca="false">IF(J260="","",SUMPRODUCT((I260=$I$6:$I$1500)*(B260&lt;$B$6:$B$1500))+SUMPRODUCT((I260=$I$6:$I$260)*(B260=$B$6:$B$260)))</f>
+        <f aca="false">IF(J260="","",SUMPRODUCT((I260=$I$6:$I$1500)*(B260&lt;$B$6:$B$1500))+COUNTIFS($I$6:I260,I260,$B$6:B260,B260))</f>
         <v/>
       </c>
       <c r="N260" s="33" t="s">
@@ -14440,7 +14440,7 @@
         <v>55</v>
       </c>
       <c r="K261" s="25" t="n">
-        <f aca="false">IF(J261="","",SUMPRODUCT((I261=$I$6:$I$1500)*(B261&lt;$B$6:$B$1500))+SUMPRODUCT((I261=$I$6:$I$261)*(B261=$B$6:$B$261)))</f>
+        <f aca="false">IF(J261="","",SUMPRODUCT((I261=$I$6:$I$1500)*(B261&lt;$B$6:$B$1500))+COUNTIFS($I$6:I261,I261,$B$6:B261,B261))</f>
         <v>3</v>
       </c>
       <c r="N261" s="33" t="s">
@@ -14482,7 +14482,7 @@
         <v/>
       </c>
       <c r="K262" s="25" t="str">
-        <f aca="false">IF(J262="","",SUMPRODUCT((I262=$I$6:$I$1500)*(B262&lt;$B$6:$B$1500))+SUMPRODUCT((I262=$I$6:$I$262)*(B262=$B$6:$B$262)))</f>
+        <f aca="false">IF(J262="","",SUMPRODUCT((I262=$I$6:$I$1500)*(B262&lt;$B$6:$B$1500))+COUNTIFS($I$6:I262,I262,$B$6:B262,B262))</f>
         <v/>
       </c>
       <c r="N262" s="33" t="s">
@@ -14526,7 +14526,7 @@
         <v/>
       </c>
       <c r="K263" s="25" t="str">
-        <f aca="false">IF(J263="","",SUMPRODUCT((I263=$I$6:$I$1500)*(B263&lt;$B$6:$B$1500))+SUMPRODUCT((I263=$I$6:$I$263)*(B263=$B$6:$B$263)))</f>
+        <f aca="false">IF(J263="","",SUMPRODUCT((I263=$I$6:$I$1500)*(B263&lt;$B$6:$B$1500))+COUNTIFS($I$6:I263,I263,$B$6:B263,B263))</f>
         <v/>
       </c>
       <c r="N263" s="33" t="s">
@@ -14570,7 +14570,7 @@
         <v/>
       </c>
       <c r="K264" s="25" t="str">
-        <f aca="false">IF(J264="","",SUMPRODUCT((I264=$I$6:$I$1500)*(B264&lt;$B$6:$B$1500))+SUMPRODUCT((I264=$I$6:$I$264)*(B264=$B$6:$B$264)))</f>
+        <f aca="false">IF(J264="","",SUMPRODUCT((I264=$I$6:$I$1500)*(B264&lt;$B$6:$B$1500))+COUNTIFS($I$6:I264,I264,$B$6:B264,B264))</f>
         <v/>
       </c>
       <c r="N264" s="33" t="s">
@@ -14614,7 +14614,7 @@
         <v/>
       </c>
       <c r="K265" s="25" t="str">
-        <f aca="false">IF(J265="","",SUMPRODUCT((I265=$I$6:$I$1500)*(B265&lt;$B$6:$B$1500))+SUMPRODUCT((I265=$I$6:$I$265)*(B265=$B$6:$B$265)))</f>
+        <f aca="false">IF(J265="","",SUMPRODUCT((I265=$I$6:$I$1500)*(B265&lt;$B$6:$B$1500))+COUNTIFS($I$6:I265,I265,$B$6:B265,B265))</f>
         <v/>
       </c>
       <c r="N265" s="33" t="s">
@@ -14658,7 +14658,7 @@
         <v/>
       </c>
       <c r="K266" s="25" t="str">
-        <f aca="false">IF(J266="","",SUMPRODUCT((I266=$I$6:$I$1500)*(B266&lt;$B$6:$B$1500))+SUMPRODUCT((I266=$I$6:$I$266)*(B266=$B$6:$B$266)))</f>
+        <f aca="false">IF(J266="","",SUMPRODUCT((I266=$I$6:$I$1500)*(B266&lt;$B$6:$B$1500))+COUNTIFS($I$6:I266,I266,$B$6:B266,B266))</f>
         <v/>
       </c>
       <c r="N266" s="33" t="s">
@@ -14702,7 +14702,7 @@
         <v/>
       </c>
       <c r="K267" s="25" t="str">
-        <f aca="false">IF(J267="","",SUMPRODUCT((I267=$I$6:$I$1500)*(B267&lt;$B$6:$B$1500))+SUMPRODUCT((I267=$I$6:$I$267)*(B267=$B$6:$B$267)))</f>
+        <f aca="false">IF(J267="","",SUMPRODUCT((I267=$I$6:$I$1500)*(B267&lt;$B$6:$B$1500))+COUNTIFS($I$6:I267,I267,$B$6:B267,B267))</f>
         <v/>
       </c>
       <c r="N267" s="33" t="s">
@@ -14746,7 +14746,7 @@
         <v/>
       </c>
       <c r="K268" s="25" t="str">
-        <f aca="false">IF(J268="","",SUMPRODUCT((I268=$I$6:$I$1500)*(B268&lt;$B$6:$B$1500))+SUMPRODUCT((I268=$I$6:$I$268)*(B268=$B$6:$B$268)))</f>
+        <f aca="false">IF(J268="","",SUMPRODUCT((I268=$I$6:$I$1500)*(B268&lt;$B$6:$B$1500))+COUNTIFS($I$6:I268,I268,$B$6:B268,B268))</f>
         <v/>
       </c>
       <c r="N268" s="33" t="s">
@@ -14790,7 +14790,7 @@
         <v/>
       </c>
       <c r="K269" s="25" t="str">
-        <f aca="false">IF(J269="","",SUMPRODUCT((I269=$I$6:$I$1500)*(B269&lt;$B$6:$B$1500))+SUMPRODUCT((I269=$I$6:$I$269)*(B269=$B$6:$B$269)))</f>
+        <f aca="false">IF(J269="","",SUMPRODUCT((I269=$I$6:$I$1500)*(B269&lt;$B$6:$B$1500))+COUNTIFS($I$6:I269,I269,$B$6:B269,B269))</f>
         <v/>
       </c>
       <c r="N269" s="33" t="s">
@@ -14834,7 +14834,7 @@
         <v/>
       </c>
       <c r="K270" s="25" t="str">
-        <f aca="false">IF(J270="","",SUMPRODUCT((I270=$I$6:$I$1500)*(B270&lt;$B$6:$B$1500))+SUMPRODUCT((I270=$I$6:$I$270)*(B270=$B$6:$B$270)))</f>
+        <f aca="false">IF(J270="","",SUMPRODUCT((I270=$I$6:$I$1500)*(B270&lt;$B$6:$B$1500))+COUNTIFS($I$6:I270,I270,$B$6:B270,B270))</f>
         <v/>
       </c>
       <c r="N270" s="33" t="s">
@@ -14878,7 +14878,7 @@
         <v/>
       </c>
       <c r="K271" s="25" t="str">
-        <f aca="false">IF(J271="","",SUMPRODUCT((I271=$I$6:$I$1500)*(B271&lt;$B$6:$B$1500))+SUMPRODUCT((I271=$I$6:$I$271)*(B271=$B$6:$B$271)))</f>
+        <f aca="false">IF(J271="","",SUMPRODUCT((I271=$I$6:$I$1500)*(B271&lt;$B$6:$B$1500))+COUNTIFS($I$6:I271,I271,$B$6:B271,B271))</f>
         <v/>
       </c>
       <c r="N271" s="65" t="s">
@@ -14922,7 +14922,7 @@
         <v/>
       </c>
       <c r="K272" s="25" t="str">
-        <f aca="false">IF(J272="","",SUMPRODUCT((I272=$I$6:$I$1500)*(B272&lt;$B$6:$B$1500))+SUMPRODUCT((I272=$I$6:$I$272)*(B272=$B$6:$B$272)))</f>
+        <f aca="false">IF(J272="","",SUMPRODUCT((I272=$I$6:$I$1500)*(B272&lt;$B$6:$B$1500))+COUNTIFS($I$6:I272,I272,$B$6:B272,B272))</f>
         <v/>
       </c>
     </row>
@@ -14960,7 +14960,7 @@
         <v/>
       </c>
       <c r="K273" s="25" t="str">
-        <f aca="false">IF(J273="","",SUMPRODUCT((I273=$I$6:$I$1500)*(B273&lt;$B$6:$B$1500))+SUMPRODUCT((I273=$I$6:$I$273)*(B273=$B$6:$B$273)))</f>
+        <f aca="false">IF(J273="","",SUMPRODUCT((I273=$I$6:$I$1500)*(B273&lt;$B$6:$B$1500))+COUNTIFS($I$6:I273,I273,$B$6:B273,B273))</f>
         <v/>
       </c>
     </row>
@@ -14998,7 +14998,7 @@
         <v/>
       </c>
       <c r="K274" s="25" t="str">
-        <f aca="false">IF(J274="","",SUMPRODUCT((I274=$I$6:$I$1500)*(B274&lt;$B$6:$B$1500))+SUMPRODUCT((I274=$I$6:$I$274)*(B274=$B$6:$B$274)))</f>
+        <f aca="false">IF(J274="","",SUMPRODUCT((I274=$I$6:$I$1500)*(B274&lt;$B$6:$B$1500))+COUNTIFS($I$6:I274,I274,$B$6:B274,B274))</f>
         <v/>
       </c>
     </row>
@@ -15036,7 +15036,7 @@
         <v/>
       </c>
       <c r="K275" s="25" t="str">
-        <f aca="false">IF(J275="","",SUMPRODUCT((I275=$I$6:$I$1500)*(B275&lt;$B$6:$B$1500))+SUMPRODUCT((I275=$I$6:$I$275)*(B275=$B$6:$B$275)))</f>
+        <f aca="false">IF(J275="","",SUMPRODUCT((I275=$I$6:$I$1500)*(B275&lt;$B$6:$B$1500))+COUNTIFS($I$6:I275,I275,$B$6:B275,B275))</f>
         <v/>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
         <v/>
       </c>
       <c r="K276" s="25" t="str">
-        <f aca="false">IF(J276="","",SUMPRODUCT((I276=$I$6:$I$1500)*(B276&lt;$B$6:$B$1500))+SUMPRODUCT((I276=$I$6:$I$276)*(B276=$B$6:$B$276)))</f>
+        <f aca="false">IF(J276="","",SUMPRODUCT((I276=$I$6:$I$1500)*(B276&lt;$B$6:$B$1500))+COUNTIFS($I$6:I276,I276,$B$6:B276,B276))</f>
         <v/>
       </c>
     </row>
@@ -15112,7 +15112,7 @@
         <v/>
       </c>
       <c r="K277" s="25" t="str">
-        <f aca="false">IF(J277="","",SUMPRODUCT((I277=$I$6:$I$1500)*(B277&lt;$B$6:$B$1500))+SUMPRODUCT((I277=$I$6:$I$277)*(B277=$B$6:$B$277)))</f>
+        <f aca="false">IF(J277="","",SUMPRODUCT((I277=$I$6:$I$1500)*(B277&lt;$B$6:$B$1500))+COUNTIFS($I$6:I277,I277,$B$6:B277,B277))</f>
         <v/>
       </c>
     </row>
@@ -15150,7 +15150,7 @@
         <v/>
       </c>
       <c r="K278" s="25" t="str">
-        <f aca="false">IF(J278="","",SUMPRODUCT((I278=$I$6:$I$1500)*(B278&lt;$B$6:$B$1500))+SUMPRODUCT((I278=$I$6:$I$278)*(B278=$B$6:$B$278)))</f>
+        <f aca="false">IF(J278="","",SUMPRODUCT((I278=$I$6:$I$1500)*(B278&lt;$B$6:$B$1500))+COUNTIFS($I$6:I278,I278,$B$6:B278,B278))</f>
         <v/>
       </c>
     </row>
@@ -15188,7 +15188,7 @@
         <v/>
       </c>
       <c r="K279" s="25" t="str">
-        <f aca="false">IF(J279="","",SUMPRODUCT((I279=$I$6:$I$1500)*(B279&lt;$B$6:$B$1500))+SUMPRODUCT((I279=$I$6:$I$279)*(B279=$B$6:$B$279)))</f>
+        <f aca="false">IF(J279="","",SUMPRODUCT((I279=$I$6:$I$1500)*(B279&lt;$B$6:$B$1500))+COUNTIFS($I$6:I279,I279,$B$6:B279,B279))</f>
         <v/>
       </c>
     </row>
@@ -15226,7 +15226,7 @@
         <v/>
       </c>
       <c r="K280" s="25" t="str">
-        <f aca="false">IF(J280="","",SUMPRODUCT((I280=$I$6:$I$1500)*(B280&lt;$B$6:$B$1500))+SUMPRODUCT((I280=$I$6:$I$280)*(B280=$B$6:$B$280)))</f>
+        <f aca="false">IF(J280="","",SUMPRODUCT((I280=$I$6:$I$1500)*(B280&lt;$B$6:$B$1500))+COUNTIFS($I$6:I280,I280,$B$6:B280,B280))</f>
         <v/>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
         <v/>
       </c>
       <c r="K281" s="25" t="str">
-        <f aca="false">IF(J281="","",SUMPRODUCT((I281=$I$6:$I$1500)*(B281&lt;$B$6:$B$1500))+SUMPRODUCT((I281=$I$6:$I$281)*(B281=$B$6:$B$281)))</f>
+        <f aca="false">IF(J281="","",SUMPRODUCT((I281=$I$6:$I$1500)*(B281&lt;$B$6:$B$1500))+COUNTIFS($I$6:I281,I281,$B$6:B281,B281))</f>
         <v/>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
         <v/>
       </c>
       <c r="K282" s="25" t="str">
-        <f aca="false">IF(J282="","",SUMPRODUCT((I282=$I$6:$I$1500)*(B282&lt;$B$6:$B$1500))+SUMPRODUCT((I282=$I$6:$I$282)*(B282=$B$6:$B$282)))</f>
+        <f aca="false">IF(J282="","",SUMPRODUCT((I282=$I$6:$I$1500)*(B282&lt;$B$6:$B$1500))+COUNTIFS($I$6:I282,I282,$B$6:B282,B282))</f>
         <v/>
       </c>
     </row>
@@ -15340,7 +15340,7 @@
         <v/>
       </c>
       <c r="K283" s="25" t="str">
-        <f aca="false">IF(J283="","",SUMPRODUCT((I283=$I$6:$I$1500)*(B283&lt;$B$6:$B$1500))+SUMPRODUCT((I283=$I$6:$I$283)*(B283=$B$6:$B$283)))</f>
+        <f aca="false">IF(J283="","",SUMPRODUCT((I283=$I$6:$I$1500)*(B283&lt;$B$6:$B$1500))+COUNTIFS($I$6:I283,I283,$B$6:B283,B283))</f>
         <v/>
       </c>
     </row>
@@ -15378,7 +15378,7 @@
         <v/>
       </c>
       <c r="K284" s="25" t="str">
-        <f aca="false">IF(J284="","",SUMPRODUCT((I284=$I$6:$I$1500)*(B284&lt;$B$6:$B$1500))+SUMPRODUCT((I284=$I$6:$I$284)*(B284=$B$6:$B$284)))</f>
+        <f aca="false">IF(J284="","",SUMPRODUCT((I284=$I$6:$I$1500)*(B284&lt;$B$6:$B$1500))+COUNTIFS($I$6:I284,I284,$B$6:B284,B284))</f>
         <v/>
       </c>
     </row>
@@ -15416,7 +15416,7 @@
         <v/>
       </c>
       <c r="K285" s="25" t="str">
-        <f aca="false">IF(J285="","",SUMPRODUCT((I285=$I$6:$I$1500)*(B285&lt;$B$6:$B$1500))+SUMPRODUCT((I285=$I$6:$I$285)*(B285=$B$6:$B$285)))</f>
+        <f aca="false">IF(J285="","",SUMPRODUCT((I285=$I$6:$I$1500)*(B285&lt;$B$6:$B$1500))+COUNTIFS($I$6:I285,I285,$B$6:B285,B285))</f>
         <v/>
       </c>
     </row>
@@ -15454,7 +15454,7 @@
         <v/>
       </c>
       <c r="K286" s="25" t="str">
-        <f aca="false">IF(J286="","",SUMPRODUCT((I286=$I$6:$I$1500)*(B286&lt;$B$6:$B$1500))+SUMPRODUCT((I286=$I$6:$I$286)*(B286=$B$6:$B$286)))</f>
+        <f aca="false">IF(J286="","",SUMPRODUCT((I286=$I$6:$I$1500)*(B286&lt;$B$6:$B$1500))+COUNTIFS($I$6:I286,I286,$B$6:B286,B286))</f>
         <v/>
       </c>
     </row>
@@ -15492,7 +15492,7 @@
         <v/>
       </c>
       <c r="K287" s="25" t="str">
-        <f aca="false">IF(J287="","",SUMPRODUCT((I287=$I$6:$I$1500)*(B287&lt;$B$6:$B$1500))+SUMPRODUCT((I287=$I$6:$I$287)*(B287=$B$6:$B$287)))</f>
+        <f aca="false">IF(J287="","",SUMPRODUCT((I287=$I$6:$I$1500)*(B287&lt;$B$6:$B$1500))+COUNTIFS($I$6:I287,I287,$B$6:B287,B287))</f>
         <v/>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
         <v/>
       </c>
       <c r="K288" s="25" t="str">
-        <f aca="false">IF(J288="","",SUMPRODUCT((I288=$I$6:$I$1500)*(B288&lt;$B$6:$B$1500))+SUMPRODUCT((I288=$I$6:$I$288)*(B288=$B$6:$B$288)))</f>
+        <f aca="false">IF(J288="","",SUMPRODUCT((I288=$I$6:$I$1500)*(B288&lt;$B$6:$B$1500))+COUNTIFS($I$6:I288,I288,$B$6:B288,B288))</f>
         <v/>
       </c>
     </row>
@@ -15568,7 +15568,7 @@
         <v/>
       </c>
       <c r="K289" s="25" t="str">
-        <f aca="false">IF(J289="","",SUMPRODUCT((I289=$I$6:$I$1500)*(B289&lt;$B$6:$B$1500))+SUMPRODUCT((I289=$I$6:$I$289)*(B289=$B$6:$B$289)))</f>
+        <f aca="false">IF(J289="","",SUMPRODUCT((I289=$I$6:$I$1500)*(B289&lt;$B$6:$B$1500))+COUNTIFS($I$6:I289,I289,$B$6:B289,B289))</f>
         <v/>
       </c>
     </row>
@@ -15606,7 +15606,7 @@
         <v/>
       </c>
       <c r="K290" s="25" t="str">
-        <f aca="false">IF(J290="","",SUMPRODUCT((I290=$I$6:$I$1500)*(B290&lt;$B$6:$B$1500))+SUMPRODUCT((I290=$I$6:$I$290)*(B290=$B$6:$B$290)))</f>
+        <f aca="false">IF(J290="","",SUMPRODUCT((I290=$I$6:$I$1500)*(B290&lt;$B$6:$B$1500))+COUNTIFS($I$6:I290,I290,$B$6:B290,B290))</f>
         <v/>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
         <v/>
       </c>
       <c r="K291" s="25" t="str">
-        <f aca="false">IF(J291="","",SUMPRODUCT((I291=$I$6:$I$1500)*(B291&lt;$B$6:$B$1500))+SUMPRODUCT((I291=$I$6:$I$291)*(B291=$B$6:$B$291)))</f>
+        <f aca="false">IF(J291="","",SUMPRODUCT((I291=$I$6:$I$1500)*(B291&lt;$B$6:$B$1500))+COUNTIFS($I$6:I291,I291,$B$6:B291,B291))</f>
         <v/>
       </c>
     </row>
@@ -15682,7 +15682,7 @@
         <v/>
       </c>
       <c r="K292" s="25" t="str">
-        <f aca="false">IF(J292="","",SUMPRODUCT((I292=$I$6:$I$1500)*(B292&lt;$B$6:$B$1500))+SUMPRODUCT((I292=$I$6:$I$292)*(B292=$B$6:$B$292)))</f>
+        <f aca="false">IF(J292="","",SUMPRODUCT((I292=$I$6:$I$1500)*(B292&lt;$B$6:$B$1500))+COUNTIFS($I$6:I292,I292,$B$6:B292,B292))</f>
         <v/>
       </c>
     </row>
@@ -15720,7 +15720,7 @@
         <v/>
       </c>
       <c r="K293" s="25" t="str">
-        <f aca="false">IF(J293="","",SUMPRODUCT((I293=$I$6:$I$1500)*(B293&lt;$B$6:$B$1500))+SUMPRODUCT((I293=$I$6:$I$293)*(B293=$B$6:$B$293)))</f>
+        <f aca="false">IF(J293="","",SUMPRODUCT((I293=$I$6:$I$1500)*(B293&lt;$B$6:$B$1500))+COUNTIFS($I$6:I293,I293,$B$6:B293,B293))</f>
         <v/>
       </c>
     </row>
@@ -15758,7 +15758,7 @@
         <v/>
       </c>
       <c r="K294" s="25" t="str">
-        <f aca="false">IF(J294="","",SUMPRODUCT((I294=$I$6:$I$1500)*(B294&lt;$B$6:$B$1500))+SUMPRODUCT((I294=$I$6:$I$294)*(B294=$B$6:$B$294)))</f>
+        <f aca="false">IF(J294="","",SUMPRODUCT((I294=$I$6:$I$1500)*(B294&lt;$B$6:$B$1500))+COUNTIFS($I$6:I294,I294,$B$6:B294,B294))</f>
         <v/>
       </c>
     </row>
@@ -15796,7 +15796,7 @@
         <v/>
       </c>
       <c r="K295" s="25" t="str">
-        <f aca="false">IF(J295="","",SUMPRODUCT((I295=$I$6:$I$1500)*(B295&lt;$B$6:$B$1500))+SUMPRODUCT((I295=$I$6:$I$295)*(B295=$B$6:$B$295)))</f>
+        <f aca="false">IF(J295="","",SUMPRODUCT((I295=$I$6:$I$1500)*(B295&lt;$B$6:$B$1500))+COUNTIFS($I$6:I295,I295,$B$6:B295,B295))</f>
         <v/>
       </c>
     </row>
@@ -15834,7 +15834,7 @@
         <v/>
       </c>
       <c r="K296" s="25" t="str">
-        <f aca="false">IF(J296="","",SUMPRODUCT((I296=$I$6:$I$1500)*(B296&lt;$B$6:$B$1500))+SUMPRODUCT((I296=$I$6:$I$296)*(B296=$B$6:$B$296)))</f>
+        <f aca="false">IF(J296="","",SUMPRODUCT((I296=$I$6:$I$1500)*(B296&lt;$B$6:$B$1500))+COUNTIFS($I$6:I296,I296,$B$6:B296,B296))</f>
         <v/>
       </c>
     </row>
@@ -15872,7 +15872,7 @@
         <v/>
       </c>
       <c r="K297" s="25" t="str">
-        <f aca="false">IF(J297="","",SUMPRODUCT((I297=$I$6:$I$1500)*(B297&lt;$B$6:$B$1500))+SUMPRODUCT((I297=$I$6:$I$297)*(B297=$B$6:$B$297)))</f>
+        <f aca="false">IF(J297="","",SUMPRODUCT((I297=$I$6:$I$1500)*(B297&lt;$B$6:$B$1500))+COUNTIFS($I$6:I297,I297,$B$6:B297,B297))</f>
         <v/>
       </c>
     </row>
@@ -15910,7 +15910,7 @@
         <v/>
       </c>
       <c r="K298" s="25" t="str">
-        <f aca="false">IF(J298="","",SUMPRODUCT((I298=$I$6:$I$1500)*(B298&lt;$B$6:$B$1500))+SUMPRODUCT((I298=$I$6:$I$298)*(B298=$B$6:$B$298)))</f>
+        <f aca="false">IF(J298="","",SUMPRODUCT((I298=$I$6:$I$1500)*(B298&lt;$B$6:$B$1500))+COUNTIFS($I$6:I298,I298,$B$6:B298,B298))</f>
         <v/>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
         <v/>
       </c>
       <c r="K299" s="25" t="str">
-        <f aca="false">IF(J299="","",SUMPRODUCT((I299=$I$6:$I$1500)*(B299&lt;$B$6:$B$1500))+SUMPRODUCT((I299=$I$6:$I$299)*(B299=$B$6:$B$299)))</f>
+        <f aca="false">IF(J299="","",SUMPRODUCT((I299=$I$6:$I$1500)*(B299&lt;$B$6:$B$1500))+COUNTIFS($I$6:I299,I299,$B$6:B299,B299))</f>
         <v/>
       </c>
     </row>
@@ -15986,7 +15986,7 @@
         <v/>
       </c>
       <c r="K300" s="25" t="str">
-        <f aca="false">IF(J300="","",SUMPRODUCT((I300=$I$6:$I$1500)*(B300&lt;$B$6:$B$1500))+SUMPRODUCT((I300=$I$6:$I$300)*(B300=$B$6:$B$300)))</f>
+        <f aca="false">IF(J300="","",SUMPRODUCT((I300=$I$6:$I$1500)*(B300&lt;$B$6:$B$1500))+COUNTIFS($I$6:I300,I300,$B$6:B300,B300))</f>
         <v/>
       </c>
     </row>
@@ -16024,7 +16024,7 @@
         <v/>
       </c>
       <c r="K301" s="25" t="str">
-        <f aca="false">IF(J301="","",SUMPRODUCT((I301=$I$6:$I$1500)*(B301&lt;$B$6:$B$1500))+SUMPRODUCT((I301=$I$6:$I$301)*(B301=$B$6:$B$301)))</f>
+        <f aca="false">IF(J301="","",SUMPRODUCT((I301=$I$6:$I$1500)*(B301&lt;$B$6:$B$1500))+COUNTIFS($I$6:I301,I301,$B$6:B301,B301))</f>
         <v/>
       </c>
     </row>
@@ -16062,7 +16062,7 @@
         <v/>
       </c>
       <c r="K302" s="25" t="str">
-        <f aca="false">IF(J302="","",SUMPRODUCT((I302=$I$6:$I$1500)*(B302&lt;$B$6:$B$1500))+SUMPRODUCT((I302=$I$6:$I$302)*(B302=$B$6:$B$302)))</f>
+        <f aca="false">IF(J302="","",SUMPRODUCT((I302=$I$6:$I$1500)*(B302&lt;$B$6:$B$1500))+COUNTIFS($I$6:I302,I302,$B$6:B302,B302))</f>
         <v/>
       </c>
     </row>
@@ -16100,7 +16100,7 @@
         <v/>
       </c>
       <c r="K303" s="25" t="str">
-        <f aca="false">IF(J303="","",SUMPRODUCT((I303=$I$6:$I$1500)*(B303&lt;$B$6:$B$1500))+SUMPRODUCT((I303=$I$6:$I$303)*(B303=$B$6:$B$303)))</f>
+        <f aca="false">IF(J303="","",SUMPRODUCT((I303=$I$6:$I$1500)*(B303&lt;$B$6:$B$1500))+COUNTIFS($I$6:I303,I303,$B$6:B303,B303))</f>
         <v/>
       </c>
     </row>
@@ -16138,7 +16138,7 @@
         <v/>
       </c>
       <c r="K304" s="25" t="str">
-        <f aca="false">IF(J304="","",SUMPRODUCT((I304=$I$6:$I$1500)*(B304&lt;$B$6:$B$1500))+SUMPRODUCT((I304=$I$6:$I$304)*(B304=$B$6:$B$304)))</f>
+        <f aca="false">IF(J304="","",SUMPRODUCT((I304=$I$6:$I$1500)*(B304&lt;$B$6:$B$1500))+COUNTIFS($I$6:I304,I304,$B$6:B304,B304))</f>
         <v/>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
         <v/>
       </c>
       <c r="K305" s="25" t="str">
-        <f aca="false">IF(J305="","",SUMPRODUCT((I305=$I$6:$I$1500)*(B305&lt;$B$6:$B$1500))+SUMPRODUCT((I305=$I$6:$I$305)*(B305=$B$6:$B$305)))</f>
+        <f aca="false">IF(J305="","",SUMPRODUCT((I305=$I$6:$I$1500)*(B305&lt;$B$6:$B$1500))+COUNTIFS($I$6:I305,I305,$B$6:B305,B305))</f>
         <v/>
       </c>
     </row>
@@ -16214,7 +16214,7 @@
         <v/>
       </c>
       <c r="K306" s="25" t="str">
-        <f aca="false">IF(J306="","",SUMPRODUCT((I306=$I$6:$I$1500)*(B306&lt;$B$6:$B$1500))+SUMPRODUCT((I306=$I$6:$I$306)*(B306=$B$6:$B$306)))</f>
+        <f aca="false">IF(J306="","",SUMPRODUCT((I306=$I$6:$I$1500)*(B306&lt;$B$6:$B$1500))+COUNTIFS($I$6:I306,I306,$B$6:B306,B306))</f>
         <v/>
       </c>
     </row>
@@ -16252,7 +16252,7 @@
         <v/>
       </c>
       <c r="K307" s="25" t="str">
-        <f aca="false">IF(J307="","",SUMPRODUCT((I307=$I$6:$I$1500)*(B307&lt;$B$6:$B$1500))+SUMPRODUCT((I307=$I$6:$I$307)*(B307=$B$6:$B$307)))</f>
+        <f aca="false">IF(J307="","",SUMPRODUCT((I307=$I$6:$I$1500)*(B307&lt;$B$6:$B$1500))+COUNTIFS($I$6:I307,I307,$B$6:B307,B307))</f>
         <v/>
       </c>
     </row>
@@ -16290,7 +16290,7 @@
         <v/>
       </c>
       <c r="K308" s="25" t="str">
-        <f aca="false">IF(J308="","",SUMPRODUCT((I308=$I$6:$I$1500)*(B308&lt;$B$6:$B$1500))+SUMPRODUCT((I308=$I$6:$I$308)*(B308=$B$6:$B$308)))</f>
+        <f aca="false">IF(J308="","",SUMPRODUCT((I308=$I$6:$I$1500)*(B308&lt;$B$6:$B$1500))+COUNTIFS($I$6:I308,I308,$B$6:B308,B308))</f>
         <v/>
       </c>
     </row>
@@ -16328,7 +16328,7 @@
         <v/>
       </c>
       <c r="K309" s="25" t="str">
-        <f aca="false">IF(J309="","",SUMPRODUCT((I309=$I$6:$I$1500)*(B309&lt;$B$6:$B$1500))+SUMPRODUCT((I309=$I$6:$I$309)*(B309=$B$6:$B$309)))</f>
+        <f aca="false">IF(J309="","",SUMPRODUCT((I309=$I$6:$I$1500)*(B309&lt;$B$6:$B$1500))+COUNTIFS($I$6:I309,I309,$B$6:B309,B309))</f>
         <v/>
       </c>
     </row>
@@ -16366,7 +16366,7 @@
         <v/>
       </c>
       <c r="K310" s="25" t="str">
-        <f aca="false">IF(J310="","",SUMPRODUCT((I310=$I$6:$I$1500)*(B310&lt;$B$6:$B$1500))+SUMPRODUCT((I310=$I$6:$I$310)*(B310=$B$6:$B$310)))</f>
+        <f aca="false">IF(J310="","",SUMPRODUCT((I310=$I$6:$I$1500)*(B310&lt;$B$6:$B$1500))+COUNTIFS($I$6:I310,I310,$B$6:B310,B310))</f>
         <v/>
       </c>
     </row>
@@ -16404,7 +16404,7 @@
         <v/>
       </c>
       <c r="K311" s="25" t="str">
-        <f aca="false">IF(J311="","",SUMPRODUCT((I311=$I$6:$I$1500)*(B311&lt;$B$6:$B$1500))+SUMPRODUCT((I311=$I$6:$I$311)*(B311=$B$6:$B$311)))</f>
+        <f aca="false">IF(J311="","",SUMPRODUCT((I311=$I$6:$I$1500)*(B311&lt;$B$6:$B$1500))+COUNTIFS($I$6:I311,I311,$B$6:B311,B311))</f>
         <v/>
       </c>
     </row>
@@ -16442,7 +16442,7 @@
         <v/>
       </c>
       <c r="K312" s="25" t="str">
-        <f aca="false">IF(J312="","",SUMPRODUCT((I312=$I$6:$I$1500)*(B312&lt;$B$6:$B$1500))+SUMPRODUCT((I312=$I$6:$I$312)*(B312=$B$6:$B$312)))</f>
+        <f aca="false">IF(J312="","",SUMPRODUCT((I312=$I$6:$I$1500)*(B312&lt;$B$6:$B$1500))+COUNTIFS($I$6:I312,I312,$B$6:B312,B312))</f>
         <v/>
       </c>
     </row>
@@ -16480,7 +16480,7 @@
         <v/>
       </c>
       <c r="K313" s="25" t="str">
-        <f aca="false">IF(J313="","",SUMPRODUCT((I313=$I$6:$I$1500)*(B313&lt;$B$6:$B$1500))+SUMPRODUCT((I313=$I$6:$I$313)*(B313=$B$6:$B$313)))</f>
+        <f aca="false">IF(J313="","",SUMPRODUCT((I313=$I$6:$I$1500)*(B313&lt;$B$6:$B$1500))+COUNTIFS($I$6:I313,I313,$B$6:B313,B313))</f>
         <v/>
       </c>
     </row>
@@ -16518,7 +16518,7 @@
         <v/>
       </c>
       <c r="K314" s="25" t="str">
-        <f aca="false">IF(J314="","",SUMPRODUCT((I314=$I$6:$I$1500)*(B314&lt;$B$6:$B$1500))+SUMPRODUCT((I314=$I$6:$I$314)*(B314=$B$6:$B$314)))</f>
+        <f aca="false">IF(J314="","",SUMPRODUCT((I314=$I$6:$I$1500)*(B314&lt;$B$6:$B$1500))+COUNTIFS($I$6:I314,I314,$B$6:B314,B314))</f>
         <v/>
       </c>
     </row>
@@ -16556,7 +16556,7 @@
         <v/>
       </c>
       <c r="K315" s="25" t="str">
-        <f aca="false">IF(J315="","",SUMPRODUCT((I315=$I$6:$I$1500)*(B315&lt;$B$6:$B$1500))+SUMPRODUCT((I315=$I$6:$I$315)*(B315=$B$6:$B$315)))</f>
+        <f aca="false">IF(J315="","",SUMPRODUCT((I315=$I$6:$I$1500)*(B315&lt;$B$6:$B$1500))+COUNTIFS($I$6:I315,I315,$B$6:B315,B315))</f>
         <v/>
       </c>
     </row>
@@ -16594,7 +16594,7 @@
         <v/>
       </c>
       <c r="K316" s="25" t="str">
-        <f aca="false">IF(J316="","",SUMPRODUCT((I316=$I$6:$I$1500)*(B316&lt;$B$6:$B$1500))+SUMPRODUCT((I316=$I$6:$I$316)*(B316=$B$6:$B$316)))</f>
+        <f aca="false">IF(J316="","",SUMPRODUCT((I316=$I$6:$I$1500)*(B316&lt;$B$6:$B$1500))+COUNTIFS($I$6:I316,I316,$B$6:B316,B316))</f>
         <v/>
       </c>
     </row>
@@ -16632,7 +16632,7 @@
         <v/>
       </c>
       <c r="K317" s="25" t="str">
-        <f aca="false">IF(J317="","",SUMPRODUCT((I317=$I$6:$I$1500)*(B317&lt;$B$6:$B$1500))+SUMPRODUCT((I317=$I$6:$I$317)*(B317=$B$6:$B$317)))</f>
+        <f aca="false">IF(J317="","",SUMPRODUCT((I317=$I$6:$I$1500)*(B317&lt;$B$6:$B$1500))+COUNTIFS($I$6:I317,I317,$B$6:B317,B317))</f>
         <v/>
       </c>
     </row>
@@ -16670,7 +16670,7 @@
         <v/>
       </c>
       <c r="K318" s="25" t="str">
-        <f aca="false">IF(J318="","",SUMPRODUCT((I318=$I$6:$I$1500)*(B318&lt;$B$6:$B$1500))+SUMPRODUCT((I318=$I$6:$I$318)*(B318=$B$6:$B$318)))</f>
+        <f aca="false">IF(J318="","",SUMPRODUCT((I318=$I$6:$I$1500)*(B318&lt;$B$6:$B$1500))+COUNTIFS($I$6:I318,I318,$B$6:B318,B318))</f>
         <v/>
       </c>
     </row>
@@ -16708,7 +16708,7 @@
         <v/>
       </c>
       <c r="K319" s="25" t="str">
-        <f aca="false">IF(J319="","",SUMPRODUCT((I319=$I$6:$I$1500)*(B319&lt;$B$6:$B$1500))+SUMPRODUCT((I319=$I$6:$I$319)*(B319=$B$6:$B$319)))</f>
+        <f aca="false">IF(J319="","",SUMPRODUCT((I319=$I$6:$I$1500)*(B319&lt;$B$6:$B$1500))+COUNTIFS($I$6:I319,I319,$B$6:B319,B319))</f>
         <v/>
       </c>
     </row>
@@ -16746,7 +16746,7 @@
         <v/>
       </c>
       <c r="K320" s="25" t="str">
-        <f aca="false">IF(J320="","",SUMPRODUCT((I320=$I$6:$I$1500)*(B320&lt;$B$6:$B$1500))+SUMPRODUCT((I320=$I$6:$I$320)*(B320=$B$6:$B$320)))</f>
+        <f aca="false">IF(J320="","",SUMPRODUCT((I320=$I$6:$I$1500)*(B320&lt;$B$6:$B$1500))+COUNTIFS($I$6:I320,I320,$B$6:B320,B320))</f>
         <v/>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
         <v/>
       </c>
       <c r="K321" s="25" t="str">
-        <f aca="false">IF(J321="","",SUMPRODUCT((I321=$I$6:$I$1500)*(B321&lt;$B$6:$B$1500))+SUMPRODUCT((I321=$I$6:$I$321)*(B321=$B$6:$B$321)))</f>
+        <f aca="false">IF(J321="","",SUMPRODUCT((I321=$I$6:$I$1500)*(B321&lt;$B$6:$B$1500))+COUNTIFS($I$6:I321,I321,$B$6:B321,B321))</f>
         <v/>
       </c>
     </row>
@@ -16822,7 +16822,7 @@
         <v/>
       </c>
       <c r="K322" s="25" t="str">
-        <f aca="false">IF(J322="","",SUMPRODUCT((I322=$I$6:$I$1500)*(B322&lt;$B$6:$B$1500))+SUMPRODUCT((I322=$I$6:$I$322)*(B322=$B$6:$B$322)))</f>
+        <f aca="false">IF(J322="","",SUMPRODUCT((I322=$I$6:$I$1500)*(B322&lt;$B$6:$B$1500))+COUNTIFS($I$6:I322,I322,$B$6:B322,B322))</f>
         <v/>
       </c>
     </row>
@@ -16860,7 +16860,7 @@
         <v/>
       </c>
       <c r="K323" s="25" t="str">
-        <f aca="false">IF(J323="","",SUMPRODUCT((I323=$I$6:$I$1500)*(B323&lt;$B$6:$B$1500))+SUMPRODUCT((I323=$I$6:$I$323)*(B323=$B$6:$B$323)))</f>
+        <f aca="false">IF(J323="","",SUMPRODUCT((I323=$I$6:$I$1500)*(B323&lt;$B$6:$B$1500))+COUNTIFS($I$6:I323,I323,$B$6:B323,B323))</f>
         <v/>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
         <v/>
       </c>
       <c r="K324" s="25" t="str">
-        <f aca="false">IF(J324="","",SUMPRODUCT((I324=$I$6:$I$1500)*(B324&lt;$B$6:$B$1500))+SUMPRODUCT((I324=$I$6:$I$324)*(B324=$B$6:$B$324)))</f>
+        <f aca="false">IF(J324="","",SUMPRODUCT((I324=$I$6:$I$1500)*(B324&lt;$B$6:$B$1500))+COUNTIFS($I$6:I324,I324,$B$6:B324,B324))</f>
         <v/>
       </c>
     </row>
@@ -16936,7 +16936,7 @@
         <v/>
       </c>
       <c r="K325" s="25" t="str">
-        <f aca="false">IF(J325="","",SUMPRODUCT((I325=$I$6:$I$1500)*(B325&lt;$B$6:$B$1500))+SUMPRODUCT((I325=$I$6:$I$325)*(B325=$B$6:$B$325)))</f>
+        <f aca="false">IF(J325="","",SUMPRODUCT((I325=$I$6:$I$1500)*(B325&lt;$B$6:$B$1500))+COUNTIFS($I$6:I325,I325,$B$6:B325,B325))</f>
         <v/>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
         <v/>
       </c>
       <c r="K326" s="25" t="str">
-        <f aca="false">IF(J326="","",SUMPRODUCT((I326=$I$6:$I$1500)*(B326&lt;$B$6:$B$1500))+SUMPRODUCT((I326=$I$6:$I$326)*(B326=$B$6:$B$326)))</f>
+        <f aca="false">IF(J326="","",SUMPRODUCT((I326=$I$6:$I$1500)*(B326&lt;$B$6:$B$1500))+COUNTIFS($I$6:I326,I326,$B$6:B326,B326))</f>
         <v/>
       </c>
     </row>
@@ -17012,7 +17012,7 @@
         <v/>
       </c>
       <c r="K327" s="25" t="str">
-        <f aca="false">IF(J327="","",SUMPRODUCT((I327=$I$6:$I$1500)*(B327&lt;$B$6:$B$1500))+SUMPRODUCT((I327=$I$6:$I$327)*(B327=$B$6:$B$327)))</f>
+        <f aca="false">IF(J327="","",SUMPRODUCT((I327=$I$6:$I$1500)*(B327&lt;$B$6:$B$1500))+COUNTIFS($I$6:I327,I327,$B$6:B327,B327))</f>
         <v/>
       </c>
     </row>
@@ -17050,7 +17050,7 @@
         <v/>
       </c>
       <c r="K328" s="25" t="str">
-        <f aca="false">IF(J328="","",SUMPRODUCT((I328=$I$6:$I$1500)*(B328&lt;$B$6:$B$1500))+SUMPRODUCT((I328=$I$6:$I$328)*(B328=$B$6:$B$328)))</f>
+        <f aca="false">IF(J328="","",SUMPRODUCT((I328=$I$6:$I$1500)*(B328&lt;$B$6:$B$1500))+COUNTIFS($I$6:I328,I328,$B$6:B328,B328))</f>
         <v/>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
         <v/>
       </c>
       <c r="K329" s="25" t="str">
-        <f aca="false">IF(J329="","",SUMPRODUCT((I329=$I$6:$I$1500)*(B329&lt;$B$6:$B$1500))+SUMPRODUCT((I329=$I$6:$I$329)*(B329=$B$6:$B$329)))</f>
+        <f aca="false">IF(J329="","",SUMPRODUCT((I329=$I$6:$I$1500)*(B329&lt;$B$6:$B$1500))+COUNTIFS($I$6:I329,I329,$B$6:B329,B329))</f>
         <v/>
       </c>
     </row>
@@ -17126,7 +17126,7 @@
         <v/>
       </c>
       <c r="K330" s="25" t="str">
-        <f aca="false">IF(J330="","",SUMPRODUCT((I330=$I$6:$I$1500)*(B330&lt;$B$6:$B$1500))+SUMPRODUCT((I330=$I$6:$I$330)*(B330=$B$6:$B$330)))</f>
+        <f aca="false">IF(J330="","",SUMPRODUCT((I330=$I$6:$I$1500)*(B330&lt;$B$6:$B$1500))+COUNTIFS($I$6:I330,I330,$B$6:B330,B330))</f>
         <v/>
       </c>
     </row>
@@ -17164,7 +17164,7 @@
         <v/>
       </c>
       <c r="K331" s="25" t="str">
-        <f aca="false">IF(J331="","",SUMPRODUCT((I331=$I$6:$I$1500)*(B331&lt;$B$6:$B$1500))+SUMPRODUCT((I331=$I$6:$I$331)*(B331=$B$6:$B$331)))</f>
+        <f aca="false">IF(J331="","",SUMPRODUCT((I331=$I$6:$I$1500)*(B331&lt;$B$6:$B$1500))+COUNTIFS($I$6:I331,I331,$B$6:B331,B331))</f>
         <v/>
       </c>
     </row>
@@ -17202,7 +17202,7 @@
         <v/>
       </c>
       <c r="K332" s="25" t="str">
-        <f aca="false">IF(J332="","",SUMPRODUCT((I332=$I$6:$I$1500)*(B332&lt;$B$6:$B$1500))+SUMPRODUCT((I332=$I$6:$I$332)*(B332=$B$6:$B$332)))</f>
+        <f aca="false">IF(J332="","",SUMPRODUCT((I332=$I$6:$I$1500)*(B332&lt;$B$6:$B$1500))+COUNTIFS($I$6:I332,I332,$B$6:B332,B332))</f>
         <v/>
       </c>
     </row>
@@ -17240,7 +17240,7 @@
         <v/>
       </c>
       <c r="K333" s="25" t="str">
-        <f aca="false">IF(J333="","",SUMPRODUCT((I333=$I$6:$I$1500)*(B333&lt;$B$6:$B$1500))+SUMPRODUCT((I333=$I$6:$I$333)*(B333=$B$6:$B$333)))</f>
+        <f aca="false">IF(J333="","",SUMPRODUCT((I333=$I$6:$I$1500)*(B333&lt;$B$6:$B$1500))+COUNTIFS($I$6:I333,I333,$B$6:B333,B333))</f>
         <v/>
       </c>
     </row>
@@ -17278,7 +17278,7 @@
         <v/>
       </c>
       <c r="K334" s="25" t="str">
-        <f aca="false">IF(J334="","",SUMPRODUCT((I334=$I$6:$I$1500)*(B334&lt;$B$6:$B$1500))+SUMPRODUCT((I334=$I$6:$I$334)*(B334=$B$6:$B$334)))</f>
+        <f aca="false">IF(J334="","",SUMPRODUCT((I334=$I$6:$I$1500)*(B334&lt;$B$6:$B$1500))+COUNTIFS($I$6:I334,I334,$B$6:B334,B334))</f>
         <v/>
       </c>
     </row>
@@ -17316,7 +17316,7 @@
         <v/>
       </c>
       <c r="K335" s="25" t="str">
-        <f aca="false">IF(J335="","",SUMPRODUCT((I335=$I$6:$I$1500)*(B335&lt;$B$6:$B$1500))+SUMPRODUCT((I335=$I$6:$I$335)*(B335=$B$6:$B$335)))</f>
+        <f aca="false">IF(J335="","",SUMPRODUCT((I335=$I$6:$I$1500)*(B335&lt;$B$6:$B$1500))+COUNTIFS($I$6:I335,I335,$B$6:B335,B335))</f>
         <v/>
       </c>
     </row>
@@ -17354,7 +17354,7 @@
         <v/>
       </c>
       <c r="K336" s="25" t="str">
-        <f aca="false">IF(J336="","",SUMPRODUCT((I336=$I$6:$I$1500)*(B336&lt;$B$6:$B$1500))+SUMPRODUCT((I336=$I$6:$I$336)*(B336=$B$6:$B$336)))</f>
+        <f aca="false">IF(J336="","",SUMPRODUCT((I336=$I$6:$I$1500)*(B336&lt;$B$6:$B$1500))+COUNTIFS($I$6:I336,I336,$B$6:B336,B336))</f>
         <v/>
       </c>
     </row>
@@ -17392,7 +17392,7 @@
         <v/>
       </c>
       <c r="K337" s="25" t="str">
-        <f aca="false">IF(J337="","",SUMPRODUCT((I337=$I$6:$I$1500)*(B337&lt;$B$6:$B$1500))+SUMPRODUCT((I337=$I$6:$I$337)*(B337=$B$6:$B$337)))</f>
+        <f aca="false">IF(J337="","",SUMPRODUCT((I337=$I$6:$I$1500)*(B337&lt;$B$6:$B$1500))+COUNTIFS($I$6:I337,I337,$B$6:B337,B337))</f>
         <v/>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
         <v/>
       </c>
       <c r="K338" s="25" t="str">
-        <f aca="false">IF(J338="","",SUMPRODUCT((I338=$I$6:$I$1500)*(B338&lt;$B$6:$B$1500))+SUMPRODUCT((I338=$I$6:$I$338)*(B338=$B$6:$B$338)))</f>
+        <f aca="false">IF(J338="","",SUMPRODUCT((I338=$I$6:$I$1500)*(B338&lt;$B$6:$B$1500))+COUNTIFS($I$6:I338,I338,$B$6:B338,B338))</f>
         <v/>
       </c>
     </row>
@@ -17468,7 +17468,7 @@
         <v/>
       </c>
       <c r="K339" s="25" t="str">
-        <f aca="false">IF(J339="","",SUMPRODUCT((I339=$I$6:$I$1500)*(B339&lt;$B$6:$B$1500))+SUMPRODUCT((I339=$I$6:$I$339)*(B339=$B$6:$B$339)))</f>
+        <f aca="false">IF(J339="","",SUMPRODUCT((I339=$I$6:$I$1500)*(B339&lt;$B$6:$B$1500))+COUNTIFS($I$6:I339,I339,$B$6:B339,B339))</f>
         <v/>
       </c>
     </row>
@@ -17506,7 +17506,7 @@
         <v/>
       </c>
       <c r="K340" s="25" t="str">
-        <f aca="false">IF(J340="","",SUMPRODUCT((I340=$I$6:$I$1500)*(B340&lt;$B$6:$B$1500))+SUMPRODUCT((I340=$I$6:$I$340)*(B340=$B$6:$B$340)))</f>
+        <f aca="false">IF(J340="","",SUMPRODUCT((I340=$I$6:$I$1500)*(B340&lt;$B$6:$B$1500))+COUNTIFS($I$6:I340,I340,$B$6:B340,B340))</f>
         <v/>
       </c>
     </row>
@@ -17544,7 +17544,7 @@
         <v/>
       </c>
       <c r="K341" s="25" t="str">
-        <f aca="false">IF(J341="","",SUMPRODUCT((I341=$I$6:$I$1500)*(B341&lt;$B$6:$B$1500))+SUMPRODUCT((I341=$I$6:$I$341)*(B341=$B$6:$B$341)))</f>
+        <f aca="false">IF(J341="","",SUMPRODUCT((I341=$I$6:$I$1500)*(B341&lt;$B$6:$B$1500))+COUNTIFS($I$6:I341,I341,$B$6:B341,B341))</f>
         <v/>
       </c>
     </row>
@@ -17582,7 +17582,7 @@
         <v/>
       </c>
       <c r="K342" s="25" t="str">
-        <f aca="false">IF(J342="","",SUMPRODUCT((I342=$I$6:$I$1500)*(B342&lt;$B$6:$B$1500))+SUMPRODUCT((I342=$I$6:$I$342)*(B342=$B$6:$B$342)))</f>
+        <f aca="false">IF(J342="","",SUMPRODUCT((I342=$I$6:$I$1500)*(B342&lt;$B$6:$B$1500))+COUNTIFS($I$6:I342,I342,$B$6:B342,B342))</f>
         <v/>
       </c>
     </row>
@@ -17620,7 +17620,7 @@
         <v/>
       </c>
       <c r="K343" s="25" t="str">
-        <f aca="false">IF(J343="","",SUMPRODUCT((I343=$I$6:$I$1500)*(B343&lt;$B$6:$B$1500))+SUMPRODUCT((I343=$I$6:$I$343)*(B343=$B$6:$B$343)))</f>
+        <f aca="false">IF(J343="","",SUMPRODUCT((I343=$I$6:$I$1500)*(B343&lt;$B$6:$B$1500))+COUNTIFS($I$6:I343,I343,$B$6:B343,B343))</f>
         <v/>
       </c>
     </row>
@@ -17658,7 +17658,7 @@
         <v/>
       </c>
       <c r="K344" s="25" t="str">
-        <f aca="false">IF(J344="","",SUMPRODUCT((I344=$I$6:$I$1500)*(B344&lt;$B$6:$B$1500))+SUMPRODUCT((I344=$I$6:$I$344)*(B344=$B$6:$B$344)))</f>
+        <f aca="false">IF(J344="","",SUMPRODUCT((I344=$I$6:$I$1500)*(B344&lt;$B$6:$B$1500))+COUNTIFS($I$6:I344,I344,$B$6:B344,B344))</f>
         <v/>
       </c>
     </row>
@@ -17696,7 +17696,7 @@
         <v/>
       </c>
       <c r="K345" s="25" t="str">
-        <f aca="false">IF(J345="","",SUMPRODUCT((I345=$I$6:$I$1500)*(B345&lt;$B$6:$B$1500))+SUMPRODUCT((I345=$I$6:$I$345)*(B345=$B$6:$B$345)))</f>
+        <f aca="false">IF(J345="","",SUMPRODUCT((I345=$I$6:$I$1500)*(B345&lt;$B$6:$B$1500))+COUNTIFS($I$6:I345,I345,$B$6:B345,B345))</f>
         <v/>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
         <v>2</v>
       </c>
       <c r="K346" s="25" t="n">
-        <f aca="false">IF(J346="","",SUMPRODUCT((I346=$I$6:$I$1500)*(B346&lt;$B$6:$B$1500))+SUMPRODUCT((I346=$I$6:$I$346)*(B346=$B$6:$B$346)))</f>
+        <f aca="false">IF(J346="","",SUMPRODUCT((I346=$I$6:$I$1500)*(B346&lt;$B$6:$B$1500))+COUNTIFS($I$6:I346,I346,$B$6:B346,B346))</f>
         <v>23</v>
       </c>
     </row>
@@ -17772,7 +17772,7 @@
         <v/>
       </c>
       <c r="K347" s="25" t="str">
-        <f aca="false">IF(J347="","",SUMPRODUCT((I347=$I$6:$I$1500)*(B347&lt;$B$6:$B$1500))+SUMPRODUCT((I347=$I$6:$I$347)*(B347=$B$6:$B$347)))</f>
+        <f aca="false">IF(J347="","",SUMPRODUCT((I347=$I$6:$I$1500)*(B347&lt;$B$6:$B$1500))+COUNTIFS($I$6:I347,I347,$B$6:B347,B347))</f>
         <v/>
       </c>
     </row>
@@ -17810,7 +17810,7 @@
         <v/>
       </c>
       <c r="K348" s="25" t="str">
-        <f aca="false">IF(J348="","",SUMPRODUCT((I348=$I$6:$I$1500)*(B348&lt;$B$6:$B$1500))+SUMPRODUCT((I348=$I$6:$I$348)*(B348=$B$6:$B$348)))</f>
+        <f aca="false">IF(J348="","",SUMPRODUCT((I348=$I$6:$I$1500)*(B348&lt;$B$6:$B$1500))+COUNTIFS($I$6:I348,I348,$B$6:B348,B348))</f>
         <v/>
       </c>
     </row>
@@ -17848,7 +17848,7 @@
         <v/>
       </c>
       <c r="K349" s="25" t="str">
-        <f aca="false">IF(J349="","",SUMPRODUCT((I349=$I$6:$I$1500)*(B349&lt;$B$6:$B$1500))+SUMPRODUCT((I349=$I$6:$I$349)*(B349=$B$6:$B$349)))</f>
+        <f aca="false">IF(J349="","",SUMPRODUCT((I349=$I$6:$I$1500)*(B349&lt;$B$6:$B$1500))+COUNTIFS($I$6:I349,I349,$B$6:B349,B349))</f>
         <v/>
       </c>
     </row>
@@ -17886,7 +17886,7 @@
         <v/>
       </c>
       <c r="K350" s="25" t="str">
-        <f aca="false">IF(J350="","",SUMPRODUCT((I350=$I$6:$I$1500)*(B350&lt;$B$6:$B$1500))+SUMPRODUCT((I350=$I$6:$I$350)*(B350=$B$6:$B$350)))</f>
+        <f aca="false">IF(J350="","",SUMPRODUCT((I350=$I$6:$I$1500)*(B350&lt;$B$6:$B$1500))+COUNTIFS($I$6:I350,I350,$B$6:B350,B350))</f>
         <v/>
       </c>
     </row>
@@ -17924,7 +17924,7 @@
         <v/>
       </c>
       <c r="K351" s="25" t="str">
-        <f aca="false">IF(J351="","",SUMPRODUCT((I351=$I$6:$I$1500)*(B351&lt;$B$6:$B$1500))+SUMPRODUCT((I351=$I$6:$I$351)*(B351=$B$6:$B$351)))</f>
+        <f aca="false">IF(J351="","",SUMPRODUCT((I351=$I$6:$I$1500)*(B351&lt;$B$6:$B$1500))+COUNTIFS($I$6:I351,I351,$B$6:B351,B351))</f>
         <v/>
       </c>
     </row>
@@ -17962,7 +17962,7 @@
         <v/>
       </c>
       <c r="K352" s="25" t="str">
-        <f aca="false">IF(J352="","",SUMPRODUCT((I352=$I$6:$I$1500)*(B352&lt;$B$6:$B$1500))+SUMPRODUCT((I352=$I$6:$I$352)*(B352=$B$6:$B$352)))</f>
+        <f aca="false">IF(J352="","",SUMPRODUCT((I352=$I$6:$I$1500)*(B352&lt;$B$6:$B$1500))+COUNTIFS($I$6:I352,I352,$B$6:B352,B352))</f>
         <v/>
       </c>
     </row>
@@ -18000,7 +18000,7 @@
         <v/>
       </c>
       <c r="K353" s="25" t="str">
-        <f aca="false">IF(J353="","",SUMPRODUCT((I353=$I$6:$I$1500)*(B353&lt;$B$6:$B$1500))+SUMPRODUCT((I353=$I$6:$I$353)*(B353=$B$6:$B$353)))</f>
+        <f aca="false">IF(J353="","",SUMPRODUCT((I353=$I$6:$I$1500)*(B353&lt;$B$6:$B$1500))+COUNTIFS($I$6:I353,I353,$B$6:B353,B353))</f>
         <v/>
       </c>
     </row>
@@ -18038,7 +18038,7 @@
         <v/>
       </c>
       <c r="K354" s="25" t="str">
-        <f aca="false">IF(J354="","",SUMPRODUCT((I354=$I$6:$I$1500)*(B354&lt;$B$6:$B$1500))+SUMPRODUCT((I354=$I$6:$I$354)*(B354=$B$6:$B$354)))</f>
+        <f aca="false">IF(J354="","",SUMPRODUCT((I354=$I$6:$I$1500)*(B354&lt;$B$6:$B$1500))+COUNTIFS($I$6:I354,I354,$B$6:B354,B354))</f>
         <v/>
       </c>
     </row>
@@ -18076,7 +18076,7 @@
         <v/>
       </c>
       <c r="K355" s="25" t="str">
-        <f aca="false">IF(J355="","",SUMPRODUCT((I355=$I$6:$I$1500)*(B355&lt;$B$6:$B$1500))+SUMPRODUCT((I355=$I$6:$I$355)*(B355=$B$6:$B$355)))</f>
+        <f aca="false">IF(J355="","",SUMPRODUCT((I355=$I$6:$I$1500)*(B355&lt;$B$6:$B$1500))+COUNTIFS($I$6:I355,I355,$B$6:B355,B355))</f>
         <v/>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
         <v/>
       </c>
       <c r="K356" s="25" t="str">
-        <f aca="false">IF(J356="","",SUMPRODUCT((I356=$I$6:$I$1500)*(B356&lt;$B$6:$B$1500))+SUMPRODUCT((I356=$I$6:$I$356)*(B356=$B$6:$B$356)))</f>
+        <f aca="false">IF(J356="","",SUMPRODUCT((I356=$I$6:$I$1500)*(B356&lt;$B$6:$B$1500))+COUNTIFS($I$6:I356,I356,$B$6:B356,B356))</f>
         <v/>
       </c>
     </row>
@@ -18152,7 +18152,7 @@
         <v/>
       </c>
       <c r="K357" s="25" t="str">
-        <f aca="false">IF(J357="","",SUMPRODUCT((I357=$I$6:$I$1500)*(B357&lt;$B$6:$B$1500))+SUMPRODUCT((I357=$I$6:$I$357)*(B357=$B$6:$B$357)))</f>
+        <f aca="false">IF(J357="","",SUMPRODUCT((I357=$I$6:$I$1500)*(B357&lt;$B$6:$B$1500))+COUNTIFS($I$6:I357,I357,$B$6:B357,B357))</f>
         <v/>
       </c>
     </row>
@@ -18190,7 +18190,7 @@
         <v/>
       </c>
       <c r="K358" s="25" t="str">
-        <f aca="false">IF(J358="","",SUMPRODUCT((I358=$I$6:$I$1500)*(B358&lt;$B$6:$B$1500))+SUMPRODUCT((I358=$I$6:$I$358)*(B358=$B$6:$B$358)))</f>
+        <f aca="false">IF(J358="","",SUMPRODUCT((I358=$I$6:$I$1500)*(B358&lt;$B$6:$B$1500))+COUNTIFS($I$6:I358,I358,$B$6:B358,B358))</f>
         <v/>
       </c>
     </row>
@@ -18228,7 +18228,7 @@
         <v/>
       </c>
       <c r="K359" s="25" t="str">
-        <f aca="false">IF(J359="","",SUMPRODUCT((I359=$I$6:$I$1500)*(B359&lt;$B$6:$B$1500))+SUMPRODUCT((I359=$I$6:$I$359)*(B359=$B$6:$B$359)))</f>
+        <f aca="false">IF(J359="","",SUMPRODUCT((I359=$I$6:$I$1500)*(B359&lt;$B$6:$B$1500))+COUNTIFS($I$6:I359,I359,$B$6:B359,B359))</f>
         <v/>
       </c>
     </row>
@@ -18266,7 +18266,7 @@
         <v/>
       </c>
       <c r="K360" s="25" t="str">
-        <f aca="false">IF(J360="","",SUMPRODUCT((I360=$I$6:$I$1500)*(B360&lt;$B$6:$B$1500))+SUMPRODUCT((I360=$I$6:$I$360)*(B360=$B$6:$B$360)))</f>
+        <f aca="false">IF(J360="","",SUMPRODUCT((I360=$I$6:$I$1500)*(B360&lt;$B$6:$B$1500))+COUNTIFS($I$6:I360,I360,$B$6:B360,B360))</f>
         <v/>
       </c>
     </row>
@@ -18304,7 +18304,7 @@
         <v/>
       </c>
       <c r="K361" s="25" t="str">
-        <f aca="false">IF(J361="","",SUMPRODUCT((I361=$I$6:$I$1500)*(B361&lt;$B$6:$B$1500))+SUMPRODUCT((I361=$I$6:$I$361)*(B361=$B$6:$B$361)))</f>
+        <f aca="false">IF(J361="","",SUMPRODUCT((I361=$I$6:$I$1500)*(B361&lt;$B$6:$B$1500))+COUNTIFS($I$6:I361,I361,$B$6:B361,B361))</f>
         <v/>
       </c>
     </row>
@@ -18342,7 +18342,7 @@
         <v/>
       </c>
       <c r="K362" s="25" t="str">
-        <f aca="false">IF(J362="","",SUMPRODUCT((I362=$I$6:$I$1500)*(B362&lt;$B$6:$B$1500))+SUMPRODUCT((I362=$I$6:$I$362)*(B362=$B$6:$B$362)))</f>
+        <f aca="false">IF(J362="","",SUMPRODUCT((I362=$I$6:$I$1500)*(B362&lt;$B$6:$B$1500))+COUNTIFS($I$6:I362,I362,$B$6:B362,B362))</f>
         <v/>
       </c>
     </row>
@@ -18380,7 +18380,7 @@
         <v/>
       </c>
       <c r="K363" s="25" t="str">
-        <f aca="false">IF(J363="","",SUMPRODUCT((I363=$I$6:$I$1500)*(B363&lt;$B$6:$B$1500))+SUMPRODUCT((I363=$I$6:$I$363)*(B363=$B$6:$B$363)))</f>
+        <f aca="false">IF(J363="","",SUMPRODUCT((I363=$I$6:$I$1500)*(B363&lt;$B$6:$B$1500))+COUNTIFS($I$6:I363,I363,$B$6:B363,B363))</f>
         <v/>
       </c>
     </row>
@@ -18418,7 +18418,7 @@
         <v/>
       </c>
       <c r="K364" s="25" t="str">
-        <f aca="false">IF(J364="","",SUMPRODUCT((I364=$I$6:$I$1500)*(B364&lt;$B$6:$B$1500))+SUMPRODUCT((I364=$I$6:$I$364)*(B364=$B$6:$B$364)))</f>
+        <f aca="false">IF(J364="","",SUMPRODUCT((I364=$I$6:$I$1500)*(B364&lt;$B$6:$B$1500))+COUNTIFS($I$6:I364,I364,$B$6:B364,B364))</f>
         <v/>
       </c>
     </row>
@@ -18456,7 +18456,7 @@
         <v/>
       </c>
       <c r="K365" s="25" t="str">
-        <f aca="false">IF(J365="","",SUMPRODUCT((I365=$I$6:$I$1500)*(B365&lt;$B$6:$B$1500))+SUMPRODUCT((I365=$I$6:$I$365)*(B365=$B$6:$B$365)))</f>
+        <f aca="false">IF(J365="","",SUMPRODUCT((I365=$I$6:$I$1500)*(B365&lt;$B$6:$B$1500))+COUNTIFS($I$6:I365,I365,$B$6:B365,B365))</f>
         <v/>
       </c>
     </row>
@@ -18494,7 +18494,7 @@
         <v/>
       </c>
       <c r="K366" s="25" t="str">
-        <f aca="false">IF(J366="","",SUMPRODUCT((I366=$I$6:$I$1500)*(B366&lt;$B$6:$B$1500))+SUMPRODUCT((I366=$I$6:$I$366)*(B366=$B$6:$B$366)))</f>
+        <f aca="false">IF(J366="","",SUMPRODUCT((I366=$I$6:$I$1500)*(B366&lt;$B$6:$B$1500))+COUNTIFS($I$6:I366,I366,$B$6:B366,B366))</f>
         <v/>
       </c>
     </row>
@@ -18532,7 +18532,7 @@
         <v/>
       </c>
       <c r="K367" s="25" t="str">
-        <f aca="false">IF(J367="","",SUMPRODUCT((I367=$I$6:$I$1500)*(B367&lt;$B$6:$B$1500))+SUMPRODUCT((I367=$I$6:$I$367)*(B367=$B$6:$B$367)))</f>
+        <f aca="false">IF(J367="","",SUMPRODUCT((I367=$I$6:$I$1500)*(B367&lt;$B$6:$B$1500))+COUNTIFS($I$6:I367,I367,$B$6:B367,B367))</f>
         <v/>
       </c>
     </row>
@@ -18570,7 +18570,7 @@
         <v/>
       </c>
       <c r="K368" s="25" t="str">
-        <f aca="false">IF(J368="","",SUMPRODUCT((I368=$I$6:$I$1500)*(B368&lt;$B$6:$B$1500))+SUMPRODUCT((I368=$I$6:$I$368)*(B368=$B$6:$B$368)))</f>
+        <f aca="false">IF(J368="","",SUMPRODUCT((I368=$I$6:$I$1500)*(B368&lt;$B$6:$B$1500))+COUNTIFS($I$6:I368,I368,$B$6:B368,B368))</f>
         <v/>
       </c>
     </row>
@@ -18608,7 +18608,7 @@
         <v/>
       </c>
       <c r="K369" s="25" t="str">
-        <f aca="false">IF(J369="","",SUMPRODUCT((I369=$I$6:$I$1500)*(B369&lt;$B$6:$B$1500))+SUMPRODUCT((I369=$I$6:$I$369)*(B369=$B$6:$B$369)))</f>
+        <f aca="false">IF(J369="","",SUMPRODUCT((I369=$I$6:$I$1500)*(B369&lt;$B$6:$B$1500))+COUNTIFS($I$6:I369,I369,$B$6:B369,B369))</f>
         <v/>
       </c>
     </row>
@@ -18646,7 +18646,7 @@
         <v/>
       </c>
       <c r="K370" s="25" t="str">
-        <f aca="false">IF(J370="","",SUMPRODUCT((I370=$I$6:$I$1500)*(B370&lt;$B$6:$B$1500))+SUMPRODUCT((I370=$I$6:$I$370)*(B370=$B$6:$B$370)))</f>
+        <f aca="false">IF(J370="","",SUMPRODUCT((I370=$I$6:$I$1500)*(B370&lt;$B$6:$B$1500))+COUNTIFS($I$6:I370,I370,$B$6:B370,B370))</f>
         <v/>
       </c>
     </row>
@@ -18684,7 +18684,7 @@
         <v/>
       </c>
       <c r="K371" s="25" t="str">
-        <f aca="false">IF(J371="","",SUMPRODUCT((I371=$I$6:$I$1500)*(B371&lt;$B$6:$B$1500))+SUMPRODUCT((I371=$I$6:$I$371)*(B371=$B$6:$B$371)))</f>
+        <f aca="false">IF(J371="","",SUMPRODUCT((I371=$I$6:$I$1500)*(B371&lt;$B$6:$B$1500))+COUNTIFS($I$6:I371,I371,$B$6:B371,B371))</f>
         <v/>
       </c>
     </row>
@@ -18722,7 +18722,7 @@
         <v/>
       </c>
       <c r="K372" s="25" t="str">
-        <f aca="false">IF(J372="","",SUMPRODUCT((I372=$I$6:$I$1500)*(B372&lt;$B$6:$B$1500))+SUMPRODUCT((I372=$I$6:$I$372)*(B372=$B$6:$B$372)))</f>
+        <f aca="false">IF(J372="","",SUMPRODUCT((I372=$I$6:$I$1500)*(B372&lt;$B$6:$B$1500))+COUNTIFS($I$6:I372,I372,$B$6:B372,B372))</f>
         <v/>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
         <v/>
       </c>
       <c r="K373" s="25" t="str">
-        <f aca="false">IF(J373="","",SUMPRODUCT((I373=$I$6:$I$1500)*(B373&lt;$B$6:$B$1500))+SUMPRODUCT((I373=$I$6:$I$373)*(B373=$B$6:$B$373)))</f>
+        <f aca="false">IF(J373="","",SUMPRODUCT((I373=$I$6:$I$1500)*(B373&lt;$B$6:$B$1500))+COUNTIFS($I$6:I373,I373,$B$6:B373,B373))</f>
         <v/>
       </c>
     </row>
@@ -18798,7 +18798,7 @@
         <v/>
       </c>
       <c r="K374" s="25" t="str">
-        <f aca="false">IF(J374="","",SUMPRODUCT((I374=$I$6:$I$1500)*(B374&lt;$B$6:$B$1500))+SUMPRODUCT((I374=$I$6:$I$374)*(B374=$B$6:$B$374)))</f>
+        <f aca="false">IF(J374="","",SUMPRODUCT((I374=$I$6:$I$1500)*(B374&lt;$B$6:$B$1500))+COUNTIFS($I$6:I374,I374,$B$6:B374,B374))</f>
         <v/>
       </c>
     </row>
@@ -18836,7 +18836,7 @@
         <v/>
       </c>
       <c r="K375" s="25" t="str">
-        <f aca="false">IF(J375="","",SUMPRODUCT((I375=$I$6:$I$1500)*(B375&lt;$B$6:$B$1500))+SUMPRODUCT((I375=$I$6:$I$375)*(B375=$B$6:$B$375)))</f>
+        <f aca="false">IF(J375="","",SUMPRODUCT((I375=$I$6:$I$1500)*(B375&lt;$B$6:$B$1500))+COUNTIFS($I$6:I375,I375,$B$6:B375,B375))</f>
         <v/>
       </c>
     </row>
@@ -18874,7 +18874,7 @@
         <v/>
       </c>
       <c r="K376" s="25" t="str">
-        <f aca="false">IF(J376="","",SUMPRODUCT((I376=$I$6:$I$1500)*(B376&lt;$B$6:$B$1500))+SUMPRODUCT((I376=$I$6:$I$376)*(B376=$B$6:$B$376)))</f>
+        <f aca="false">IF(J376="","",SUMPRODUCT((I376=$I$6:$I$1500)*(B376&lt;$B$6:$B$1500))+COUNTIFS($I$6:I376,I376,$B$6:B376,B376))</f>
         <v/>
       </c>
     </row>
@@ -18912,7 +18912,7 @@
         <v/>
       </c>
       <c r="K377" s="25" t="str">
-        <f aca="false">IF(J377="","",SUMPRODUCT((I377=$I$6:$I$1500)*(B377&lt;$B$6:$B$1500))+SUMPRODUCT((I377=$I$6:$I$377)*(B377=$B$6:$B$377)))</f>
+        <f aca="false">IF(J377="","",SUMPRODUCT((I377=$I$6:$I$1500)*(B377&lt;$B$6:$B$1500))+COUNTIFS($I$6:I377,I377,$B$6:B377,B377))</f>
         <v/>
       </c>
     </row>
@@ -18950,7 +18950,7 @@
         <v/>
       </c>
       <c r="K378" s="25" t="str">
-        <f aca="false">IF(J378="","",SUMPRODUCT((I378=$I$6:$I$1500)*(B378&lt;$B$6:$B$1500))+SUMPRODUCT((I378=$I$6:$I$378)*(B378=$B$6:$B$378)))</f>
+        <f aca="false">IF(J378="","",SUMPRODUCT((I378=$I$6:$I$1500)*(B378&lt;$B$6:$B$1500))+COUNTIFS($I$6:I378,I378,$B$6:B378,B378))</f>
         <v/>
       </c>
     </row>
@@ -18988,7 +18988,7 @@
         <v/>
       </c>
       <c r="K379" s="25" t="str">
-        <f aca="false">IF(J379="","",SUMPRODUCT((I379=$I$6:$I$1500)*(B379&lt;$B$6:$B$1500))+SUMPRODUCT((I379=$I$6:$I$379)*(B379=$B$6:$B$379)))</f>
+        <f aca="false">IF(J379="","",SUMPRODUCT((I379=$I$6:$I$1500)*(B379&lt;$B$6:$B$1500))+COUNTIFS($I$6:I379,I379,$B$6:B379,B379))</f>
         <v/>
       </c>
     </row>
@@ -19026,7 +19026,7 @@
         <v/>
       </c>
       <c r="K380" s="25" t="str">
-        <f aca="false">IF(J380="","",SUMPRODUCT((I380=$I$6:$I$1500)*(B380&lt;$B$6:$B$1500))+SUMPRODUCT((I380=$I$6:$I$380)*(B380=$B$6:$B$380)))</f>
+        <f aca="false">IF(J380="","",SUMPRODUCT((I380=$I$6:$I$1500)*(B380&lt;$B$6:$B$1500))+COUNTIFS($I$6:I380,I380,$B$6:B380,B380))</f>
         <v/>
       </c>
     </row>
@@ -19064,7 +19064,7 @@
         <v/>
       </c>
       <c r="K381" s="25" t="str">
-        <f aca="false">IF(J381="","",SUMPRODUCT((I381=$I$6:$I$1500)*(B381&lt;$B$6:$B$1500))+SUMPRODUCT((I381=$I$6:$I$381)*(B381=$B$6:$B$381)))</f>
+        <f aca="false">IF(J381="","",SUMPRODUCT((I381=$I$6:$I$1500)*(B381&lt;$B$6:$B$1500))+COUNTIFS($I$6:I381,I381,$B$6:B381,B381))</f>
         <v/>
       </c>
     </row>
@@ -19102,7 +19102,7 @@
         <v/>
       </c>
       <c r="K382" s="25" t="str">
-        <f aca="false">IF(J382="","",SUMPRODUCT((I382=$I$6:$I$1500)*(B382&lt;$B$6:$B$1500))+SUMPRODUCT((I382=$I$6:$I$382)*(B382=$B$6:$B$382)))</f>
+        <f aca="false">IF(J382="","",SUMPRODUCT((I382=$I$6:$I$1500)*(B382&lt;$B$6:$B$1500))+COUNTIFS($I$6:I382,I382,$B$6:B382,B382))</f>
         <v/>
       </c>
     </row>
@@ -19140,7 +19140,7 @@
         <v/>
       </c>
       <c r="K383" s="25" t="str">
-        <f aca="false">IF(J383="","",SUMPRODUCT((I383=$I$6:$I$1500)*(B383&lt;$B$6:$B$1500))+SUMPRODUCT((I383=$I$6:$I$383)*(B383=$B$6:$B$383)))</f>
+        <f aca="false">IF(J383="","",SUMPRODUCT((I383=$I$6:$I$1500)*(B383&lt;$B$6:$B$1500))+COUNTIFS($I$6:I383,I383,$B$6:B383,B383))</f>
         <v/>
       </c>
     </row>
@@ -19178,7 +19178,7 @@
         <v/>
       </c>
       <c r="K384" s="25" t="str">
-        <f aca="false">IF(J384="","",SUMPRODUCT((I384=$I$6:$I$1500)*(B384&lt;$B$6:$B$1500))+SUMPRODUCT((I384=$I$6:$I$384)*(B384=$B$6:$B$384)))</f>
+        <f aca="false">IF(J384="","",SUMPRODUCT((I384=$I$6:$I$1500)*(B384&lt;$B$6:$B$1500))+COUNTIFS($I$6:I384,I384,$B$6:B384,B384))</f>
         <v/>
       </c>
     </row>
@@ -19216,7 +19216,7 @@
         <v/>
       </c>
       <c r="K385" s="25" t="str">
-        <f aca="false">IF(J385="","",SUMPRODUCT((I385=$I$6:$I$1500)*(B385&lt;$B$6:$B$1500))+SUMPRODUCT((I385=$I$6:$I$385)*(B385=$B$6:$B$385)))</f>
+        <f aca="false">IF(J385="","",SUMPRODUCT((I385=$I$6:$I$1500)*(B385&lt;$B$6:$B$1500))+COUNTIFS($I$6:I385,I385,$B$6:B385,B385))</f>
         <v/>
       </c>
     </row>
@@ -19254,7 +19254,7 @@
         <v/>
       </c>
       <c r="K386" s="25" t="str">
-        <f aca="false">IF(J386="","",SUMPRODUCT((I386=$I$6:$I$1500)*(B386&lt;$B$6:$B$1500))+SUMPRODUCT((I386=$I$6:$I$386)*(B386=$B$6:$B$386)))</f>
+        <f aca="false">IF(J386="","",SUMPRODUCT((I386=$I$6:$I$1500)*(B386&lt;$B$6:$B$1500))+COUNTIFS($I$6:I386,I386,$B$6:B386,B386))</f>
         <v/>
       </c>
     </row>
@@ -19292,7 +19292,7 @@
         <v/>
       </c>
       <c r="K387" s="25" t="str">
-        <f aca="false">IF(J387="","",SUMPRODUCT((I387=$I$6:$I$1500)*(B387&lt;$B$6:$B$1500))+SUMPRODUCT((I387=$I$6:$I$387)*(B387=$B$6:$B$387)))</f>
+        <f aca="false">IF(J387="","",SUMPRODUCT((I387=$I$6:$I$1500)*(B387&lt;$B$6:$B$1500))+COUNTIFS($I$6:I387,I387,$B$6:B387,B387))</f>
         <v/>
       </c>
     </row>
@@ -19330,7 +19330,7 @@
         <v/>
       </c>
       <c r="K388" s="25" t="str">
-        <f aca="false">IF(J388="","",SUMPRODUCT((I388=$I$6:$I$1500)*(B388&lt;$B$6:$B$1500))+SUMPRODUCT((I388=$I$6:$I$388)*(B388=$B$6:$B$388)))</f>
+        <f aca="false">IF(J388="","",SUMPRODUCT((I388=$I$6:$I$1500)*(B388&lt;$B$6:$B$1500))+COUNTIFS($I$6:I388,I388,$B$6:B388,B388))</f>
         <v/>
       </c>
     </row>
@@ -19368,7 +19368,7 @@
         <v/>
       </c>
       <c r="K389" s="25" t="str">
-        <f aca="false">IF(J389="","",SUMPRODUCT((I389=$I$6:$I$1500)*(B389&lt;$B$6:$B$1500))+SUMPRODUCT((I389=$I$6:$I$389)*(B389=$B$6:$B$389)))</f>
+        <f aca="false">IF(J389="","",SUMPRODUCT((I389=$I$6:$I$1500)*(B389&lt;$B$6:$B$1500))+COUNTIFS($I$6:I389,I389,$B$6:B389,B389))</f>
         <v/>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
         <v/>
       </c>
       <c r="K390" s="25" t="str">
-        <f aca="false">IF(J390="","",SUMPRODUCT((I390=$I$6:$I$1500)*(B390&lt;$B$6:$B$1500))+SUMPRODUCT((I390=$I$6:$I$390)*(B390=$B$6:$B$390)))</f>
+        <f aca="false">IF(J390="","",SUMPRODUCT((I390=$I$6:$I$1500)*(B390&lt;$B$6:$B$1500))+COUNTIFS($I$6:I390,I390,$B$6:B390,B390))</f>
         <v/>
       </c>
     </row>
@@ -19444,7 +19444,7 @@
         <v/>
       </c>
       <c r="K391" s="25" t="str">
-        <f aca="false">IF(J391="","",SUMPRODUCT((I391=$I$6:$I$1500)*(B391&lt;$B$6:$B$1500))+SUMPRODUCT((I391=$I$6:$I$391)*(B391=$B$6:$B$391)))</f>
+        <f aca="false">IF(J391="","",SUMPRODUCT((I391=$I$6:$I$1500)*(B391&lt;$B$6:$B$1500))+COUNTIFS($I$6:I391,I391,$B$6:B391,B391))</f>
         <v/>
       </c>
     </row>
@@ -19482,7 +19482,7 @@
         <v/>
       </c>
       <c r="K392" s="25" t="str">
-        <f aca="false">IF(J392="","",SUMPRODUCT((I392=$I$6:$I$1500)*(B392&lt;$B$6:$B$1500))+SUMPRODUCT((I392=$I$6:$I$392)*(B392=$B$6:$B$392)))</f>
+        <f aca="false">IF(J392="","",SUMPRODUCT((I392=$I$6:$I$1500)*(B392&lt;$B$6:$B$1500))+COUNTIFS($I$6:I392,I392,$B$6:B392,B392))</f>
         <v/>
       </c>
     </row>
@@ -19520,7 +19520,7 @@
         <v/>
       </c>
       <c r="K393" s="25" t="str">
-        <f aca="false">IF(J393="","",SUMPRODUCT((I393=$I$6:$I$1500)*(B393&lt;$B$6:$B$1500))+SUMPRODUCT((I393=$I$6:$I$393)*(B393=$B$6:$B$393)))</f>
+        <f aca="false">IF(J393="","",SUMPRODUCT((I393=$I$6:$I$1500)*(B393&lt;$B$6:$B$1500))+COUNTIFS($I$6:I393,I393,$B$6:B393,B393))</f>
         <v/>
       </c>
     </row>
@@ -19558,7 +19558,7 @@
         <v/>
       </c>
       <c r="K394" s="25" t="str">
-        <f aca="false">IF(J394="","",SUMPRODUCT((I394=$I$6:$I$1500)*(B394&lt;$B$6:$B$1500))+SUMPRODUCT((I394=$I$6:$I$394)*(B394=$B$6:$B$394)))</f>
+        <f aca="false">IF(J394="","",SUMPRODUCT((I394=$I$6:$I$1500)*(B394&lt;$B$6:$B$1500))+COUNTIFS($I$6:I394,I394,$B$6:B394,B394))</f>
         <v/>
       </c>
     </row>
@@ -19596,7 +19596,7 @@
         <v/>
       </c>
       <c r="K395" s="25" t="str">
-        <f aca="false">IF(J395="","",SUMPRODUCT((I395=$I$6:$I$1500)*(B395&lt;$B$6:$B$1500))+SUMPRODUCT((I395=$I$6:$I$395)*(B395=$B$6:$B$395)))</f>
+        <f aca="false">IF(J395="","",SUMPRODUCT((I395=$I$6:$I$1500)*(B395&lt;$B$6:$B$1500))+COUNTIFS($I$6:I395,I395,$B$6:B395,B395))</f>
         <v/>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
         <v/>
       </c>
       <c r="K396" s="25" t="str">
-        <f aca="false">IF(J396="","",SUMPRODUCT((I396=$I$6:$I$1500)*(B396&lt;$B$6:$B$1500))+SUMPRODUCT((I396=$I$6:$I$396)*(B396=$B$6:$B$396)))</f>
+        <f aca="false">IF(J396="","",SUMPRODUCT((I396=$I$6:$I$1500)*(B396&lt;$B$6:$B$1500))+COUNTIFS($I$6:I396,I396,$B$6:B396,B396))</f>
         <v/>
       </c>
     </row>
@@ -19672,7 +19672,7 @@
         <v/>
       </c>
       <c r="K397" s="25" t="str">
-        <f aca="false">IF(J397="","",SUMPRODUCT((I397=$I$6:$I$1500)*(B397&lt;$B$6:$B$1500))+SUMPRODUCT((I397=$I$6:$I$397)*(B397=$B$6:$B$397)))</f>
+        <f aca="false">IF(J397="","",SUMPRODUCT((I397=$I$6:$I$1500)*(B397&lt;$B$6:$B$1500))+COUNTIFS($I$6:I397,I397,$B$6:B397,B397))</f>
         <v/>
       </c>
     </row>
@@ -19710,7 +19710,7 @@
         <v/>
       </c>
       <c r="K398" s="25" t="str">
-        <f aca="false">IF(J398="","",SUMPRODUCT((I398=$I$6:$I$1500)*(B398&lt;$B$6:$B$1500))+SUMPRODUCT((I398=$I$6:$I$398)*(B398=$B$6:$B$398)))</f>
+        <f aca="false">IF(J398="","",SUMPRODUCT((I398=$I$6:$I$1500)*(B398&lt;$B$6:$B$1500))+COUNTIFS($I$6:I398,I398,$B$6:B398,B398))</f>
         <v/>
       </c>
     </row>
@@ -19748,7 +19748,7 @@
         <v/>
       </c>
       <c r="K399" s="25" t="str">
-        <f aca="false">IF(J399="","",SUMPRODUCT((I399=$I$6:$I$1500)*(B399&lt;$B$6:$B$1500))+SUMPRODUCT((I399=$I$6:$I$399)*(B399=$B$6:$B$399)))</f>
+        <f aca="false">IF(J399="","",SUMPRODUCT((I399=$I$6:$I$1500)*(B399&lt;$B$6:$B$1500))+COUNTIFS($I$6:I399,I399,$B$6:B399,B399))</f>
         <v/>
       </c>
     </row>
@@ -19786,7 +19786,7 @@
         <v/>
       </c>
       <c r="K400" s="25" t="str">
-        <f aca="false">IF(J400="","",SUMPRODUCT((I400=$I$6:$I$1500)*(B400&lt;$B$6:$B$1500))+SUMPRODUCT((I400=$I$6:$I$400)*(B400=$B$6:$B$400)))</f>
+        <f aca="false">IF(J400="","",SUMPRODUCT((I400=$I$6:$I$1500)*(B400&lt;$B$6:$B$1500))+COUNTIFS($I$6:I400,I400,$B$6:B400,B400))</f>
         <v/>
       </c>
     </row>
@@ -19824,7 +19824,7 @@
         <v/>
       </c>
       <c r="K401" s="25" t="str">
-        <f aca="false">IF(J401="","",SUMPRODUCT((I401=$I$6:$I$1500)*(B401&lt;$B$6:$B$1500))+SUMPRODUCT((I401=$I$6:$I$401)*(B401=$B$6:$B$401)))</f>
+        <f aca="false">IF(J401="","",SUMPRODUCT((I401=$I$6:$I$1500)*(B401&lt;$B$6:$B$1500))+COUNTIFS($I$6:I401,I401,$B$6:B401,B401))</f>
         <v/>
       </c>
     </row>
@@ -19862,7 +19862,7 @@
         <v/>
       </c>
       <c r="K402" s="25" t="str">
-        <f aca="false">IF(J402="","",SUMPRODUCT((I402=$I$6:$I$1500)*(B402&lt;$B$6:$B$1500))+SUMPRODUCT((I402=$I$6:$I$402)*(B402=$B$6:$B$402)))</f>
+        <f aca="false">IF(J402="","",SUMPRODUCT((I402=$I$6:$I$1500)*(B402&lt;$B$6:$B$1500))+COUNTIFS($I$6:I402,I402,$B$6:B402,B402))</f>
         <v/>
       </c>
     </row>
@@ -19900,7 +19900,7 @@
         <v/>
       </c>
       <c r="K403" s="25" t="str">
-        <f aca="false">IF(J403="","",SUMPRODUCT((I403=$I$6:$I$1500)*(B403&lt;$B$6:$B$1500))+SUMPRODUCT((I403=$I$6:$I$403)*(B403=$B$6:$B$403)))</f>
+        <f aca="false">IF(J403="","",SUMPRODUCT((I403=$I$6:$I$1500)*(B403&lt;$B$6:$B$1500))+COUNTIFS($I$6:I403,I403,$B$6:B403,B403))</f>
         <v/>
       </c>
     </row>
@@ -19938,7 +19938,7 @@
         <v/>
       </c>
       <c r="K404" s="25" t="str">
-        <f aca="false">IF(J404="","",SUMPRODUCT((I404=$I$6:$I$1500)*(B404&lt;$B$6:$B$1500))+SUMPRODUCT((I404=$I$6:$I$404)*(B404=$B$6:$B$404)))</f>
+        <f aca="false">IF(J404="","",SUMPRODUCT((I404=$I$6:$I$1500)*(B404&lt;$B$6:$B$1500))+COUNTIFS($I$6:I404,I404,$B$6:B404,B404))</f>
         <v/>
       </c>
     </row>
@@ -19976,7 +19976,7 @@
         <v/>
       </c>
       <c r="K405" s="25" t="str">
-        <f aca="false">IF(J405="","",SUMPRODUCT((I405=$I$6:$I$1500)*(B405&lt;$B$6:$B$1500))+SUMPRODUCT((I405=$I$6:$I$405)*(B405=$B$6:$B$405)))</f>
+        <f aca="false">IF(J405="","",SUMPRODUCT((I405=$I$6:$I$1500)*(B405&lt;$B$6:$B$1500))+COUNTIFS($I$6:I405,I405,$B$6:B405,B405))</f>
         <v/>
       </c>
     </row>
@@ -20014,7 +20014,7 @@
         <v/>
       </c>
       <c r="K406" s="25" t="str">
-        <f aca="false">IF(J406="","",SUMPRODUCT((I406=$I$6:$I$1500)*(B406&lt;$B$6:$B$1500))+SUMPRODUCT((I406=$I$6:$I$406)*(B406=$B$6:$B$406)))</f>
+        <f aca="false">IF(J406="","",SUMPRODUCT((I406=$I$6:$I$1500)*(B406&lt;$B$6:$B$1500))+COUNTIFS($I$6:I406,I406,$B$6:B406,B406))</f>
         <v/>
       </c>
     </row>
@@ -20052,7 +20052,7 @@
         <v/>
       </c>
       <c r="K407" s="25" t="str">
-        <f aca="false">IF(J407="","",SUMPRODUCT((I407=$I$6:$I$1500)*(B407&lt;$B$6:$B$1500))+SUMPRODUCT((I407=$I$6:$I$407)*(B407=$B$6:$B$407)))</f>
+        <f aca="false">IF(J407="","",SUMPRODUCT((I407=$I$6:$I$1500)*(B407&lt;$B$6:$B$1500))+COUNTIFS($I$6:I407,I407,$B$6:B407,B407))</f>
         <v/>
       </c>
     </row>
@@ -20090,7 +20090,7 @@
         <v/>
       </c>
       <c r="K408" s="25" t="str">
-        <f aca="false">IF(J408="","",SUMPRODUCT((I408=$I$6:$I$1500)*(B408&lt;$B$6:$B$1500))+SUMPRODUCT((I408=$I$6:$I$408)*(B408=$B$6:$B$408)))</f>
+        <f aca="false">IF(J408="","",SUMPRODUCT((I408=$I$6:$I$1500)*(B408&lt;$B$6:$B$1500))+COUNTIFS($I$6:I408,I408,$B$6:B408,B408))</f>
         <v/>
       </c>
     </row>
@@ -20128,7 +20128,7 @@
         <v/>
       </c>
       <c r="K409" s="25" t="str">
-        <f aca="false">IF(J409="","",SUMPRODUCT((I409=$I$6:$I$1500)*(B409&lt;$B$6:$B$1500))+SUMPRODUCT((I409=$I$6:$I$409)*(B409=$B$6:$B$409)))</f>
+        <f aca="false">IF(J409="","",SUMPRODUCT((I409=$I$6:$I$1500)*(B409&lt;$B$6:$B$1500))+COUNTIFS($I$6:I409,I409,$B$6:B409,B409))</f>
         <v/>
       </c>
     </row>
@@ -20166,7 +20166,7 @@
         <v/>
       </c>
       <c r="K410" s="25" t="str">
-        <f aca="false">IF(J410="","",SUMPRODUCT((I410=$I$6:$I$1500)*(B410&lt;$B$6:$B$1500))+SUMPRODUCT((I410=$I$6:$I$410)*(B410=$B$6:$B$410)))</f>
+        <f aca="false">IF(J410="","",SUMPRODUCT((I410=$I$6:$I$1500)*(B410&lt;$B$6:$B$1500))+COUNTIFS($I$6:I410,I410,$B$6:B410,B410))</f>
         <v/>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
         <v/>
       </c>
       <c r="K411" s="25" t="str">
-        <f aca="false">IF(J411="","",SUMPRODUCT((I411=$I$6:$I$1500)*(B411&lt;$B$6:$B$1500))+SUMPRODUCT((I411=$I$6:$I$411)*(B411=$B$6:$B$411)))</f>
+        <f aca="false">IF(J411="","",SUMPRODUCT((I411=$I$6:$I$1500)*(B411&lt;$B$6:$B$1500))+COUNTIFS($I$6:I411,I411,$B$6:B411,B411))</f>
         <v/>
       </c>
     </row>
@@ -20242,7 +20242,7 @@
         <v/>
       </c>
       <c r="K412" s="25" t="str">
-        <f aca="false">IF(J412="","",SUMPRODUCT((I412=$I$6:$I$1500)*(B412&lt;$B$6:$B$1500))+SUMPRODUCT((I412=$I$6:$I$412)*(B412=$B$6:$B$412)))</f>
+        <f aca="false">IF(J412="","",SUMPRODUCT((I412=$I$6:$I$1500)*(B412&lt;$B$6:$B$1500))+COUNTIFS($I$6:I412,I412,$B$6:B412,B412))</f>
         <v/>
       </c>
     </row>
@@ -20280,7 +20280,7 @@
         <v/>
       </c>
       <c r="K413" s="25" t="str">
-        <f aca="false">IF(J413="","",SUMPRODUCT((I413=$I$6:$I$1500)*(B413&lt;$B$6:$B$1500))+SUMPRODUCT((I413=$I$6:$I$413)*(B413=$B$6:$B$413)))</f>
+        <f aca="false">IF(J413="","",SUMPRODUCT((I413=$I$6:$I$1500)*(B413&lt;$B$6:$B$1500))+COUNTIFS($I$6:I413,I413,$B$6:B413,B413))</f>
         <v/>
       </c>
     </row>
@@ -20318,7 +20318,7 @@
         <v/>
       </c>
       <c r="K414" s="25" t="str">
-        <f aca="false">IF(J414="","",SUMPRODUCT((I414=$I$6:$I$1500)*(B414&lt;$B$6:$B$1500))+SUMPRODUCT((I414=$I$6:$I$414)*(B414=$B$6:$B$414)))</f>
+        <f aca="false">IF(J414="","",SUMPRODUCT((I414=$I$6:$I$1500)*(B414&lt;$B$6:$B$1500))+COUNTIFS($I$6:I414,I414,$B$6:B414,B414))</f>
         <v/>
       </c>
     </row>
@@ -20356,7 +20356,7 @@
         <v/>
       </c>
       <c r="K415" s="25" t="str">
-        <f aca="false">IF(J415="","",SUMPRODUCT((I415=$I$6:$I$1500)*(B415&lt;$B$6:$B$1500))+SUMPRODUCT((I415=$I$6:$I$415)*(B415=$B$6:$B$415)))</f>
+        <f aca="false">IF(J415="","",SUMPRODUCT((I415=$I$6:$I$1500)*(B415&lt;$B$6:$B$1500))+COUNTIFS($I$6:I415,I415,$B$6:B415,B415))</f>
         <v/>
       </c>
     </row>
@@ -20394,7 +20394,7 @@
         <v/>
       </c>
       <c r="K416" s="25" t="str">
-        <f aca="false">IF(J416="","",SUMPRODUCT((I416=$I$6:$I$1500)*(B416&lt;$B$6:$B$1500))+SUMPRODUCT((I416=$I$6:$I$416)*(B416=$B$6:$B$416)))</f>
+        <f aca="false">IF(J416="","",SUMPRODUCT((I416=$I$6:$I$1500)*(B416&lt;$B$6:$B$1500))+COUNTIFS($I$6:I416,I416,$B$6:B416,B416))</f>
         <v/>
       </c>
     </row>
@@ -20432,7 +20432,7 @@
         <v/>
       </c>
       <c r="K417" s="25" t="str">
-        <f aca="false">IF(J417="","",SUMPRODUCT((I417=$I$6:$I$1500)*(B417&lt;$B$6:$B$1500))+SUMPRODUCT((I417=$I$6:$I$417)*(B417=$B$6:$B$417)))</f>
+        <f aca="false">IF(J417="","",SUMPRODUCT((I417=$I$6:$I$1500)*(B417&lt;$B$6:$B$1500))+COUNTIFS($I$6:I417,I417,$B$6:B417,B417))</f>
         <v/>
       </c>
     </row>
@@ -20470,7 +20470,7 @@
         <v/>
       </c>
       <c r="K418" s="25" t="str">
-        <f aca="false">IF(J418="","",SUMPRODUCT((I418=$I$6:$I$1500)*(B418&lt;$B$6:$B$1500))+SUMPRODUCT((I418=$I$6:$I$418)*(B418=$B$6:$B$418)))</f>
+        <f aca="false">IF(J418="","",SUMPRODUCT((I418=$I$6:$I$1500)*(B418&lt;$B$6:$B$1500))+COUNTIFS($I$6:I418,I418,$B$6:B418,B418))</f>
         <v/>
       </c>
     </row>
@@ -20508,7 +20508,7 @@
         <v/>
       </c>
       <c r="K419" s="25" t="str">
-        <f aca="false">IF(J419="","",SUMPRODUCT((I419=$I$6:$I$1500)*(B419&lt;$B$6:$B$1500))+SUMPRODUCT((I419=$I$6:$I$419)*(B419=$B$6:$B$419)))</f>
+        <f aca="false">IF(J419="","",SUMPRODUCT((I419=$I$6:$I$1500)*(B419&lt;$B$6:$B$1500))+COUNTIFS($I$6:I419,I419,$B$6:B419,B419))</f>
         <v/>
       </c>
     </row>
@@ -20546,7 +20546,7 @@
         <v/>
       </c>
       <c r="K420" s="25" t="str">
-        <f aca="false">IF(J420="","",SUMPRODUCT((I420=$I$6:$I$1500)*(B420&lt;$B$6:$B$1500))+SUMPRODUCT((I420=$I$6:$I$420)*(B420=$B$6:$B$420)))</f>
+        <f aca="false">IF(J420="","",SUMPRODUCT((I420=$I$6:$I$1500)*(B420&lt;$B$6:$B$1500))+COUNTIFS($I$6:I420,I420,$B$6:B420,B420))</f>
         <v/>
       </c>
     </row>
@@ -20584,7 +20584,7 @@
         <v/>
       </c>
       <c r="K421" s="25" t="str">
-        <f aca="false">IF(J421="","",SUMPRODUCT((I421=$I$6:$I$1500)*(B421&lt;$B$6:$B$1500))+SUMPRODUCT((I421=$I$6:$I$421)*(B421=$B$6:$B$421)))</f>
+        <f aca="false">IF(J421="","",SUMPRODUCT((I421=$I$6:$I$1500)*(B421&lt;$B$6:$B$1500))+COUNTIFS($I$6:I421,I421,$B$6:B421,B421))</f>
         <v/>
       </c>
     </row>
@@ -20622,7 +20622,7 @@
         <v/>
       </c>
       <c r="K422" s="25" t="str">
-        <f aca="false">IF(J422="","",SUMPRODUCT((I422=$I$6:$I$1500)*(B422&lt;$B$6:$B$1500))+SUMPRODUCT((I422=$I$6:$I$422)*(B422=$B$6:$B$422)))</f>
+        <f aca="false">IF(J422="","",SUMPRODUCT((I422=$I$6:$I$1500)*(B422&lt;$B$6:$B$1500))+COUNTIFS($I$6:I422,I422,$B$6:B422,B422))</f>
         <v/>
       </c>
     </row>
@@ -20660,7 +20660,7 @@
         <v/>
       </c>
       <c r="K423" s="25" t="str">
-        <f aca="false">IF(J423="","",SUMPRODUCT((I423=$I$6:$I$1500)*(B423&lt;$B$6:$B$1500))+SUMPRODUCT((I423=$I$6:$I$423)*(B423=$B$6:$B$423)))</f>
+        <f aca="false">IF(J423="","",SUMPRODUCT((I423=$I$6:$I$1500)*(B423&lt;$B$6:$B$1500))+COUNTIFS($I$6:I423,I423,$B$6:B423,B423))</f>
         <v/>
       </c>
     </row>
@@ -20698,7 +20698,7 @@
         <v/>
       </c>
       <c r="K424" s="25" t="str">
-        <f aca="false">IF(J424="","",SUMPRODUCT((I424=$I$6:$I$1500)*(B424&lt;$B$6:$B$1500))+SUMPRODUCT((I424=$I$6:$I$424)*(B424=$B$6:$B$424)))</f>
+        <f aca="false">IF(J424="","",SUMPRODUCT((I424=$I$6:$I$1500)*(B424&lt;$B$6:$B$1500))+COUNTIFS($I$6:I424,I424,$B$6:B424,B424))</f>
         <v/>
       </c>
     </row>
@@ -20736,7 +20736,7 @@
         <v/>
       </c>
       <c r="K425" s="25" t="str">
-        <f aca="false">IF(J425="","",SUMPRODUCT((I425=$I$6:$I$1500)*(B425&lt;$B$6:$B$1500))+SUMPRODUCT((I425=$I$6:$I$425)*(B425=$B$6:$B$425)))</f>
+        <f aca="false">IF(J425="","",SUMPRODUCT((I425=$I$6:$I$1500)*(B425&lt;$B$6:$B$1500))+COUNTIFS($I$6:I425,I425,$B$6:B425,B425))</f>
         <v/>
       </c>
     </row>
@@ -20774,7 +20774,7 @@
         <v/>
       </c>
       <c r="K426" s="25" t="str">
-        <f aca="false">IF(J426="","",SUMPRODUCT((I426=$I$6:$I$1500)*(B426&lt;$B$6:$B$1500))+SUMPRODUCT((I426=$I$6:$I$426)*(B426=$B$6:$B$426)))</f>
+        <f aca="false">IF(J426="","",SUMPRODUCT((I426=$I$6:$I$1500)*(B426&lt;$B$6:$B$1500))+COUNTIFS($I$6:I426,I426,$B$6:B426,B426))</f>
         <v/>
       </c>
     </row>
@@ -20812,7 +20812,7 @@
         <v/>
       </c>
       <c r="K427" s="25" t="str">
-        <f aca="false">IF(J427="","",SUMPRODUCT((I427=$I$6:$I$1500)*(B427&lt;$B$6:$B$1500))+SUMPRODUCT((I427=$I$6:$I$427)*(B427=$B$6:$B$427)))</f>
+        <f aca="false">IF(J427="","",SUMPRODUCT((I427=$I$6:$I$1500)*(B427&lt;$B$6:$B$1500))+COUNTIFS($I$6:I427,I427,$B$6:B427,B427))</f>
         <v/>
       </c>
     </row>
@@ -20850,7 +20850,7 @@
         <v/>
       </c>
       <c r="K428" s="25" t="str">
-        <f aca="false">IF(J428="","",SUMPRODUCT((I428=$I$6:$I$1500)*(B428&lt;$B$6:$B$1500))+SUMPRODUCT((I428=$I$6:$I$428)*(B428=$B$6:$B$428)))</f>
+        <f aca="false">IF(J428="","",SUMPRODUCT((I428=$I$6:$I$1500)*(B428&lt;$B$6:$B$1500))+COUNTIFS($I$6:I428,I428,$B$6:B428,B428))</f>
         <v/>
       </c>
     </row>
@@ -20888,7 +20888,7 @@
         <v/>
       </c>
       <c r="K429" s="25" t="str">
-        <f aca="false">IF(J429="","",SUMPRODUCT((I429=$I$6:$I$1500)*(B429&lt;$B$6:$B$1500))+SUMPRODUCT((I429=$I$6:$I$429)*(B429=$B$6:$B$429)))</f>
+        <f aca="false">IF(J429="","",SUMPRODUCT((I429=$I$6:$I$1500)*(B429&lt;$B$6:$B$1500))+COUNTIFS($I$6:I429,I429,$B$6:B429,B429))</f>
         <v/>
       </c>
     </row>
@@ -20926,7 +20926,7 @@
         <v/>
       </c>
       <c r="K430" s="25" t="str">
-        <f aca="false">IF(J430="","",SUMPRODUCT((I430=$I$6:$I$1500)*(B430&lt;$B$6:$B$1500))+SUMPRODUCT((I430=$I$6:$I$430)*(B430=$B$6:$B$430)))</f>
+        <f aca="false">IF(J430="","",SUMPRODUCT((I430=$I$6:$I$1500)*(B430&lt;$B$6:$B$1500))+COUNTIFS($I$6:I430,I430,$B$6:B430,B430))</f>
         <v/>
       </c>
     </row>
@@ -20964,7 +20964,7 @@
         <v/>
       </c>
       <c r="K431" s="25" t="str">
-        <f aca="false">IF(J431="","",SUMPRODUCT((I431=$I$6:$I$1500)*(B431&lt;$B$6:$B$1500))+SUMPRODUCT((I431=$I$6:$I$431)*(B431=$B$6:$B$431)))</f>
+        <f aca="false">IF(J431="","",SUMPRODUCT((I431=$I$6:$I$1500)*(B431&lt;$B$6:$B$1500))+COUNTIFS($I$6:I431,I431,$B$6:B431,B431))</f>
         <v/>
       </c>
     </row>
@@ -21002,7 +21002,7 @@
         <v/>
       </c>
       <c r="K432" s="25" t="str">
-        <f aca="false">IF(J432="","",SUMPRODUCT((I432=$I$6:$I$1500)*(B432&lt;$B$6:$B$1500))+SUMPRODUCT((I432=$I$6:$I$432)*(B432=$B$6:$B$432)))</f>
+        <f aca="false">IF(J432="","",SUMPRODUCT((I432=$I$6:$I$1500)*(B432&lt;$B$6:$B$1500))+COUNTIFS($I$6:I432,I432,$B$6:B432,B432))</f>
         <v/>
       </c>
     </row>
@@ -21040,7 +21040,7 @@
         <v/>
       </c>
       <c r="K433" s="25" t="str">
-        <f aca="false">IF(J433="","",SUMPRODUCT((I433=$I$6:$I$1500)*(B433&lt;$B$6:$B$1500))+SUMPRODUCT((I433=$I$6:$I$433)*(B433=$B$6:$B$433)))</f>
+        <f aca="false">IF(J433="","",SUMPRODUCT((I433=$I$6:$I$1500)*(B433&lt;$B$6:$B$1500))+COUNTIFS($I$6:I433,I433,$B$6:B433,B433))</f>
         <v/>
       </c>
     </row>
@@ -21078,7 +21078,7 @@
         <v/>
       </c>
       <c r="K434" s="25" t="str">
-        <f aca="false">IF(J434="","",SUMPRODUCT((I434=$I$6:$I$1500)*(B434&lt;$B$6:$B$1500))+SUMPRODUCT((I434=$I$6:$I$434)*(B434=$B$6:$B$434)))</f>
+        <f aca="false">IF(J434="","",SUMPRODUCT((I434=$I$6:$I$1500)*(B434&lt;$B$6:$B$1500))+COUNTIFS($I$6:I434,I434,$B$6:B434,B434))</f>
         <v/>
       </c>
     </row>
@@ -21116,7 +21116,7 @@
         <v/>
       </c>
       <c r="K435" s="25" t="str">
-        <f aca="false">IF(J435="","",SUMPRODUCT((I435=$I$6:$I$1500)*(B435&lt;$B$6:$B$1500))+SUMPRODUCT((I435=$I$6:$I$435)*(B435=$B$6:$B$435)))</f>
+        <f aca="false">IF(J435="","",SUMPRODUCT((I435=$I$6:$I$1500)*(B435&lt;$B$6:$B$1500))+COUNTIFS($I$6:I435,I435,$B$6:B435,B435))</f>
         <v/>
       </c>
     </row>
@@ -21154,7 +21154,7 @@
         <v/>
       </c>
       <c r="K436" s="25" t="str">
-        <f aca="false">IF(J436="","",SUMPRODUCT((I436=$I$6:$I$1500)*(B436&lt;$B$6:$B$1500))+SUMPRODUCT((I436=$I$6:$I$436)*(B436=$B$6:$B$436)))</f>
+        <f aca="false">IF(J436="","",SUMPRODUCT((I436=$I$6:$I$1500)*(B436&lt;$B$6:$B$1500))+COUNTIFS($I$6:I436,I436,$B$6:B436,B436))</f>
         <v/>
       </c>
     </row>
@@ -21192,7 +21192,7 @@
         <v/>
       </c>
       <c r="K437" s="25" t="str">
-        <f aca="false">IF(J437="","",SUMPRODUCT((I437=$I$6:$I$1500)*(B437&lt;$B$6:$B$1500))+SUMPRODUCT((I437=$I$6:$I$437)*(B437=$B$6:$B$437)))</f>
+        <f aca="false">IF(J437="","",SUMPRODUCT((I437=$I$6:$I$1500)*(B437&lt;$B$6:$B$1500))+COUNTIFS($I$6:I437,I437,$B$6:B437,B437))</f>
         <v/>
       </c>
     </row>
@@ -21230,7 +21230,7 @@
         <v/>
       </c>
       <c r="K438" s="25" t="str">
-        <f aca="false">IF(J438="","",SUMPRODUCT((I438=$I$6:$I$1500)*(B438&lt;$B$6:$B$1500))+SUMPRODUCT((I438=$I$6:$I$438)*(B438=$B$6:$B$438)))</f>
+        <f aca="false">IF(J438="","",SUMPRODUCT((I438=$I$6:$I$1500)*(B438&lt;$B$6:$B$1500))+COUNTIFS($I$6:I438,I438,$B$6:B438,B438))</f>
         <v/>
       </c>
     </row>
@@ -21268,7 +21268,7 @@
         <v/>
       </c>
       <c r="K439" s="25" t="str">
-        <f aca="false">IF(J439="","",SUMPRODUCT((I439=$I$6:$I$1500)*(B439&lt;$B$6:$B$1500))+SUMPRODUCT((I439=$I$6:$I$439)*(B439=$B$6:$B$439)))</f>
+        <f aca="false">IF(J439="","",SUMPRODUCT((I439=$I$6:$I$1500)*(B439&lt;$B$6:$B$1500))+COUNTIFS($I$6:I439,I439,$B$6:B439,B439))</f>
         <v/>
       </c>
     </row>
@@ -21306,7 +21306,7 @@
         <v/>
       </c>
       <c r="K440" s="25" t="str">
-        <f aca="false">IF(J440="","",SUMPRODUCT((I440=$I$6:$I$1500)*(B440&lt;$B$6:$B$1500))+SUMPRODUCT((I440=$I$6:$I$440)*(B440=$B$6:$B$440)))</f>
+        <f aca="false">IF(J440="","",SUMPRODUCT((I440=$I$6:$I$1500)*(B440&lt;$B$6:$B$1500))+COUNTIFS($I$6:I440,I440,$B$6:B440,B440))</f>
         <v/>
       </c>
     </row>
@@ -21344,7 +21344,7 @@
         <v/>
       </c>
       <c r="K441" s="25" t="str">
-        <f aca="false">IF(J441="","",SUMPRODUCT((I441=$I$6:$I$1500)*(B441&lt;$B$6:$B$1500))+SUMPRODUCT((I441=$I$6:$I$441)*(B441=$B$6:$B$441)))</f>
+        <f aca="false">IF(J441="","",SUMPRODUCT((I441=$I$6:$I$1500)*(B441&lt;$B$6:$B$1500))+COUNTIFS($I$6:I441,I441,$B$6:B441,B441))</f>
         <v/>
       </c>
     </row>
@@ -21382,7 +21382,7 @@
         <v/>
       </c>
       <c r="K442" s="25" t="str">
-        <f aca="false">IF(J442="","",SUMPRODUCT((I442=$I$6:$I$1500)*(B442&lt;$B$6:$B$1500))+SUMPRODUCT((I442=$I$6:$I$442)*(B442=$B$6:$B$442)))</f>
+        <f aca="false">IF(J442="","",SUMPRODUCT((I442=$I$6:$I$1500)*(B442&lt;$B$6:$B$1500))+COUNTIFS($I$6:I442,I442,$B$6:B442,B442))</f>
         <v/>
       </c>
     </row>
@@ -21420,7 +21420,7 @@
         <v/>
       </c>
       <c r="K443" s="25" t="str">
-        <f aca="false">IF(J443="","",SUMPRODUCT((I443=$I$6:$I$1500)*(B443&lt;$B$6:$B$1500))+SUMPRODUCT((I443=$I$6:$I$443)*(B443=$B$6:$B$443)))</f>
+        <f aca="false">IF(J443="","",SUMPRODUCT((I443=$I$6:$I$1500)*(B443&lt;$B$6:$B$1500))+COUNTIFS($I$6:I443,I443,$B$6:B443,B443))</f>
         <v/>
       </c>
     </row>
@@ -21458,7 +21458,7 @@
         <v/>
       </c>
       <c r="K444" s="25" t="str">
-        <f aca="false">IF(J444="","",SUMPRODUCT((I444=$I$6:$I$1500)*(B444&lt;$B$6:$B$1500))+SUMPRODUCT((I444=$I$6:$I$444)*(B444=$B$6:$B$444)))</f>
+        <f aca="false">IF(J444="","",SUMPRODUCT((I444=$I$6:$I$1500)*(B444&lt;$B$6:$B$1500))+COUNTIFS($I$6:I444,I444,$B$6:B444,B444))</f>
         <v/>
       </c>
     </row>
@@ -21496,7 +21496,7 @@
         <v/>
       </c>
       <c r="K445" s="25" t="str">
-        <f aca="false">IF(J445="","",SUMPRODUCT((I445=$I$6:$I$1500)*(B445&lt;$B$6:$B$1500))+SUMPRODUCT((I445=$I$6:$I$445)*(B445=$B$6:$B$445)))</f>
+        <f aca="false">IF(J445="","",SUMPRODUCT((I445=$I$6:$I$1500)*(B445&lt;$B$6:$B$1500))+COUNTIFS($I$6:I445,I445,$B$6:B445,B445))</f>
         <v/>
       </c>
     </row>
@@ -21534,7 +21534,7 @@
         <v/>
       </c>
       <c r="K446" s="25" t="str">
-        <f aca="false">IF(J446="","",SUMPRODUCT((I446=$I$6:$I$1500)*(B446&lt;$B$6:$B$1500))+SUMPRODUCT((I446=$I$6:$I$446)*(B446=$B$6:$B$446)))</f>
+        <f aca="false">IF(J446="","",SUMPRODUCT((I446=$I$6:$I$1500)*(B446&lt;$B$6:$B$1500))+COUNTIFS($I$6:I446,I446,$B$6:B446,B446))</f>
         <v/>
       </c>
     </row>
@@ -21572,7 +21572,7 @@
         <v/>
       </c>
       <c r="K447" s="25" t="str">
-        <f aca="false">IF(J447="","",SUMPRODUCT((I447=$I$6:$I$1500)*(B447&lt;$B$6:$B$1500))+SUMPRODUCT((I447=$I$6:$I$447)*(B447=$B$6:$B$447)))</f>
+        <f aca="false">IF(J447="","",SUMPRODUCT((I447=$I$6:$I$1500)*(B447&lt;$B$6:$B$1500))+COUNTIFS($I$6:I447,I447,$B$6:B447,B447))</f>
         <v/>
       </c>
     </row>
@@ -21610,7 +21610,7 @@
         <v/>
       </c>
       <c r="K448" s="25" t="str">
-        <f aca="false">IF(J448="","",SUMPRODUCT((I448=$I$6:$I$1500)*(B448&lt;$B$6:$B$1500))+SUMPRODUCT((I448=$I$6:$I$448)*(B448=$B$6:$B$448)))</f>
+        <f aca="false">IF(J448="","",SUMPRODUCT((I448=$I$6:$I$1500)*(B448&lt;$B$6:$B$1500))+COUNTIFS($I$6:I448,I448,$B$6:B448,B448))</f>
         <v/>
       </c>
     </row>
@@ -21648,7 +21648,7 @@
         <v/>
       </c>
       <c r="K449" s="25" t="str">
-        <f aca="false">IF(J449="","",SUMPRODUCT((I449=$I$6:$I$1500)*(B449&lt;$B$6:$B$1500))+SUMPRODUCT((I449=$I$6:$I$449)*(B449=$B$6:$B$449)))</f>
+        <f aca="false">IF(J449="","",SUMPRODUCT((I449=$I$6:$I$1500)*(B449&lt;$B$6:$B$1500))+COUNTIFS($I$6:I449,I449,$B$6:B449,B449))</f>
         <v/>
       </c>
     </row>
@@ -21686,7 +21686,7 @@
         <v/>
       </c>
       <c r="K450" s="25" t="str">
-        <f aca="false">IF(J450="","",SUMPRODUCT((I450=$I$6:$I$1500)*(B450&lt;$B$6:$B$1500))+SUMPRODUCT((I450=$I$6:$I$450)*(B450=$B$6:$B$450)))</f>
+        <f aca="false">IF(J450="","",SUMPRODUCT((I450=$I$6:$I$1500)*(B450&lt;$B$6:$B$1500))+COUNTIFS($I$6:I450,I450,$B$6:B450,B450))</f>
         <v/>
       </c>
     </row>
@@ -21724,7 +21724,7 @@
         <v>23</v>
       </c>
       <c r="K451" s="25" t="n">
-        <f aca="false">IF(J451="","",SUMPRODUCT((I451=$I$6:$I$1500)*(B451&lt;$B$6:$B$1500))+SUMPRODUCT((I451=$I$6:$I$451)*(B451=$B$6:$B$451)))</f>
+        <f aca="false">IF(J451="","",SUMPRODUCT((I451=$I$6:$I$1500)*(B451&lt;$B$6:$B$1500))+COUNTIFS($I$6:I451,I451,$B$6:B451,B451))</f>
         <v>24</v>
       </c>
     </row>
@@ -21762,7 +21762,7 @@
         <v>4</v>
       </c>
       <c r="K452" s="25" t="n">
-        <f aca="false">IF(J452="","",SUMPRODUCT((I452=$I$6:$I$1500)*(B452&lt;$B$6:$B$1500))+SUMPRODUCT((I452=$I$6:$I$452)*(B452=$B$6:$B$452)))</f>
+        <f aca="false">IF(J452="","",SUMPRODUCT((I452=$I$6:$I$1500)*(B452&lt;$B$6:$B$1500))+COUNTIFS($I$6:I452,I452,$B$6:B452,B452))</f>
         <v>25</v>
       </c>
     </row>
@@ -21800,7 +21800,7 @@
         <v/>
       </c>
       <c r="K453" s="25" t="str">
-        <f aca="false">IF(J453="","",SUMPRODUCT((I453=$I$6:$I$1500)*(B453&lt;$B$6:$B$1500))+SUMPRODUCT((I453=$I$6:$I$453)*(B453=$B$6:$B$453)))</f>
+        <f aca="false">IF(J453="","",SUMPRODUCT((I453=$I$6:$I$1500)*(B453&lt;$B$6:$B$1500))+COUNTIFS($I$6:I453,I453,$B$6:B453,B453))</f>
         <v/>
       </c>
     </row>
@@ -21838,7 +21838,7 @@
         <v/>
       </c>
       <c r="K454" s="25" t="str">
-        <f aca="false">IF(J454="","",SUMPRODUCT((I454=$I$6:$I$1500)*(B454&lt;$B$6:$B$1500))+SUMPRODUCT((I454=$I$6:$I$454)*(B454=$B$6:$B$454)))</f>
+        <f aca="false">IF(J454="","",SUMPRODUCT((I454=$I$6:$I$1500)*(B454&lt;$B$6:$B$1500))+COUNTIFS($I$6:I454,I454,$B$6:B454,B454))</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +21876,7 @@
         <v/>
       </c>
       <c r="K455" s="25" t="str">
-        <f aca="false">IF(J455="","",SUMPRODUCT((I455=$I$6:$I$1500)*(B455&lt;$B$6:$B$1500))+SUMPRODUCT((I455=$I$6:$I$455)*(B455=$B$6:$B$455)))</f>
+        <f aca="false">IF(J455="","",SUMPRODUCT((I455=$I$6:$I$1500)*(B455&lt;$B$6:$B$1500))+COUNTIFS($I$6:I455,I455,$B$6:B455,B455))</f>
         <v/>
       </c>
     </row>
@@ -21914,7 +21914,7 @@
         <v/>
       </c>
       <c r="K456" s="25" t="str">
-        <f aca="false">IF(J456="","",SUMPRODUCT((I456=$I$6:$I$1500)*(B456&lt;$B$6:$B$1500))+SUMPRODUCT((I456=$I$6:$I$456)*(B456=$B$6:$B$456)))</f>
+        <f aca="false">IF(J456="","",SUMPRODUCT((I456=$I$6:$I$1500)*(B456&lt;$B$6:$B$1500))+COUNTIFS($I$6:I456,I456,$B$6:B456,B456))</f>
         <v/>
       </c>
     </row>
@@ -21952,7 +21952,7 @@
         <v/>
       </c>
       <c r="K457" s="25" t="str">
-        <f aca="false">IF(J457="","",SUMPRODUCT((I457=$I$6:$I$1500)*(B457&lt;$B$6:$B$1500))+SUMPRODUCT((I457=$I$6:$I$457)*(B457=$B$6:$B$457)))</f>
+        <f aca="false">IF(J457="","",SUMPRODUCT((I457=$I$6:$I$1500)*(B457&lt;$B$6:$B$1500))+COUNTIFS($I$6:I457,I457,$B$6:B457,B457))</f>
         <v/>
       </c>
     </row>
@@ -21990,7 +21990,7 @@
         <v/>
       </c>
       <c r="K458" s="25" t="str">
-        <f aca="false">IF(J458="","",SUMPRODUCT((I458=$I$6:$I$1500)*(B458&lt;$B$6:$B$1500))+SUMPRODUCT((I458=$I$6:$I$458)*(B458=$B$6:$B$458)))</f>
+        <f aca="false">IF(J458="","",SUMPRODUCT((I458=$I$6:$I$1500)*(B458&lt;$B$6:$B$1500))+COUNTIFS($I$6:I458,I458,$B$6:B458,B458))</f>
         <v/>
       </c>
     </row>
@@ -22028,7 +22028,7 @@
         <v/>
       </c>
       <c r="K459" s="25" t="str">
-        <f aca="false">IF(J459="","",SUMPRODUCT((I459=$I$6:$I$1500)*(B459&lt;$B$6:$B$1500))+SUMPRODUCT((I459=$I$6:$I$459)*(B459=$B$6:$B$459)))</f>
+        <f aca="false">IF(J459="","",SUMPRODUCT((I459=$I$6:$I$1500)*(B459&lt;$B$6:$B$1500))+COUNTIFS($I$6:I459,I459,$B$6:B459,B459))</f>
         <v/>
       </c>
     </row>
@@ -22066,7 +22066,7 @@
         <v/>
       </c>
       <c r="K460" s="25" t="str">
-        <f aca="false">IF(J460="","",SUMPRODUCT((I460=$I$6:$I$1500)*(B460&lt;$B$6:$B$1500))+SUMPRODUCT((I460=$I$6:$I$460)*(B460=$B$6:$B$460)))</f>
+        <f aca="false">IF(J460="","",SUMPRODUCT((I460=$I$6:$I$1500)*(B460&lt;$B$6:$B$1500))+COUNTIFS($I$6:I460,I460,$B$6:B460,B460))</f>
         <v/>
       </c>
     </row>
@@ -22104,7 +22104,7 @@
         <v/>
       </c>
       <c r="K461" s="25" t="str">
-        <f aca="false">IF(J461="","",SUMPRODUCT((I461=$I$6:$I$1500)*(B461&lt;$B$6:$B$1500))+SUMPRODUCT((I461=$I$6:$I$461)*(B461=$B$6:$B$461)))</f>
+        <f aca="false">IF(J461="","",SUMPRODUCT((I461=$I$6:$I$1500)*(B461&lt;$B$6:$B$1500))+COUNTIFS($I$6:I461,I461,$B$6:B461,B461))</f>
         <v/>
       </c>
     </row>
@@ -22142,7 +22142,7 @@
         <v/>
       </c>
       <c r="K462" s="25" t="str">
-        <f aca="false">IF(J462="","",SUMPRODUCT((I462=$I$6:$I$1500)*(B462&lt;$B$6:$B$1500))+SUMPRODUCT((I462=$I$6:$I$462)*(B462=$B$6:$B$462)))</f>
+        <f aca="false">IF(J462="","",SUMPRODUCT((I462=$I$6:$I$1500)*(B462&lt;$B$6:$B$1500))+COUNTIFS($I$6:I462,I462,$B$6:B462,B462))</f>
         <v/>
       </c>
     </row>
@@ -22180,7 +22180,7 @@
         <v/>
       </c>
       <c r="K463" s="25" t="str">
-        <f aca="false">IF(J463="","",SUMPRODUCT((I463=$I$6:$I$1500)*(B463&lt;$B$6:$B$1500))+SUMPRODUCT((I463=$I$6:$I$463)*(B463=$B$6:$B$463)))</f>
+        <f aca="false">IF(J463="","",SUMPRODUCT((I463=$I$6:$I$1500)*(B463&lt;$B$6:$B$1500))+COUNTIFS($I$6:I463,I463,$B$6:B463,B463))</f>
         <v/>
       </c>
     </row>
@@ -22218,7 +22218,7 @@
         <v/>
       </c>
       <c r="K464" s="25" t="str">
-        <f aca="false">IF(J464="","",SUMPRODUCT((I464=$I$6:$I$1500)*(B464&lt;$B$6:$B$1500))+SUMPRODUCT((I464=$I$6:$I$464)*(B464=$B$6:$B$464)))</f>
+        <f aca="false">IF(J464="","",SUMPRODUCT((I464=$I$6:$I$1500)*(B464&lt;$B$6:$B$1500))+COUNTIFS($I$6:I464,I464,$B$6:B464,B464))</f>
         <v/>
       </c>
     </row>
@@ -22256,7 +22256,7 @@
         <v/>
       </c>
       <c r="K465" s="25" t="str">
-        <f aca="false">IF(J465="","",SUMPRODUCT((I465=$I$6:$I$1500)*(B465&lt;$B$6:$B$1500))+SUMPRODUCT((I465=$I$6:$I$465)*(B465=$B$6:$B$465)))</f>
+        <f aca="false">IF(J465="","",SUMPRODUCT((I465=$I$6:$I$1500)*(B465&lt;$B$6:$B$1500))+COUNTIFS($I$6:I465,I465,$B$6:B465,B465))</f>
         <v/>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
         <v/>
       </c>
       <c r="K466" s="25" t="str">
-        <f aca="false">IF(J466="","",SUMPRODUCT((I466=$I$6:$I$1500)*(B466&lt;$B$6:$B$1500))+SUMPRODUCT((I466=$I$6:$I$466)*(B466=$B$6:$B$466)))</f>
+        <f aca="false">IF(J466="","",SUMPRODUCT((I466=$I$6:$I$1500)*(B466&lt;$B$6:$B$1500))+COUNTIFS($I$6:I466,I466,$B$6:B466,B466))</f>
         <v/>
       </c>
     </row>
@@ -22332,7 +22332,7 @@
         <v/>
       </c>
       <c r="K467" s="25" t="str">
-        <f aca="false">IF(J467="","",SUMPRODUCT((I467=$I$6:$I$1500)*(B467&lt;$B$6:$B$1500))+SUMPRODUCT((I467=$I$6:$I$467)*(B467=$B$6:$B$467)))</f>
+        <f aca="false">IF(J467="","",SUMPRODUCT((I467=$I$6:$I$1500)*(B467&lt;$B$6:$B$1500))+COUNTIFS($I$6:I467,I467,$B$6:B467,B467))</f>
         <v/>
       </c>
     </row>
@@ -22370,7 +22370,7 @@
         <v/>
       </c>
       <c r="K468" s="25" t="str">
-        <f aca="false">IF(J468="","",SUMPRODUCT((I468=$I$6:$I$1500)*(B468&lt;$B$6:$B$1500))+SUMPRODUCT((I468=$I$6:$I$468)*(B468=$B$6:$B$468)))</f>
+        <f aca="false">IF(J468="","",SUMPRODUCT((I468=$I$6:$I$1500)*(B468&lt;$B$6:$B$1500))+COUNTIFS($I$6:I468,I468,$B$6:B468,B468))</f>
         <v/>
       </c>
     </row>
@@ -22408,7 +22408,7 @@
         <v/>
       </c>
       <c r="K469" s="25" t="str">
-        <f aca="false">IF(J469="","",SUMPRODUCT((I469=$I$6:$I$1500)*(B469&lt;$B$6:$B$1500))+SUMPRODUCT((I469=$I$6:$I$469)*(B469=$B$6:$B$469)))</f>
+        <f aca="false">IF(J469="","",SUMPRODUCT((I469=$I$6:$I$1500)*(B469&lt;$B$6:$B$1500))+COUNTIFS($I$6:I469,I469,$B$6:B469,B469))</f>
         <v/>
       </c>
     </row>
@@ -22446,7 +22446,7 @@
         <v/>
       </c>
       <c r="K470" s="25" t="str">
-        <f aca="false">IF(J470="","",SUMPRODUCT((I470=$I$6:$I$1500)*(B470&lt;$B$6:$B$1500))+SUMPRODUCT((I470=$I$6:$I$470)*(B470=$B$6:$B$470)))</f>
+        <f aca="false">IF(J470="","",SUMPRODUCT((I470=$I$6:$I$1500)*(B470&lt;$B$6:$B$1500))+COUNTIFS($I$6:I470,I470,$B$6:B470,B470))</f>
         <v/>
       </c>
     </row>
@@ -22484,7 +22484,7 @@
         <v/>
       </c>
       <c r="K471" s="25" t="str">
-        <f aca="false">IF(J471="","",SUMPRODUCT((I471=$I$6:$I$1500)*(B471&lt;$B$6:$B$1500))+SUMPRODUCT((I471=$I$6:$I$471)*(B471=$B$6:$B$471)))</f>
+        <f aca="false">IF(J471="","",SUMPRODUCT((I471=$I$6:$I$1500)*(B471&lt;$B$6:$B$1500))+COUNTIFS($I$6:I471,I471,$B$6:B471,B471))</f>
         <v/>
       </c>
     </row>
@@ -22522,7 +22522,7 @@
         <v/>
       </c>
       <c r="K472" s="25" t="str">
-        <f aca="false">IF(J472="","",SUMPRODUCT((I472=$I$6:$I$1500)*(B472&lt;$B$6:$B$1500))+SUMPRODUCT((I472=$I$6:$I$472)*(B472=$B$6:$B$472)))</f>
+        <f aca="false">IF(J472="","",SUMPRODUCT((I472=$I$6:$I$1500)*(B472&lt;$B$6:$B$1500))+COUNTIFS($I$6:I472,I472,$B$6:B472,B472))</f>
         <v/>
       </c>
     </row>
@@ -22560,7 +22560,7 @@
         <v/>
       </c>
       <c r="K473" s="25" t="str">
-        <f aca="false">IF(J473="","",SUMPRODUCT((I473=$I$6:$I$1500)*(B473&lt;$B$6:$B$1500))+SUMPRODUCT((I473=$I$6:$I$473)*(B473=$B$6:$B$473)))</f>
+        <f aca="false">IF(J473="","",SUMPRODUCT((I473=$I$6:$I$1500)*(B473&lt;$B$6:$B$1500))+COUNTIFS($I$6:I473,I473,$B$6:B473,B473))</f>
         <v/>
       </c>
     </row>
@@ -22598,7 +22598,7 @@
         <v/>
       </c>
       <c r="K474" s="25" t="str">
-        <f aca="false">IF(J474="","",SUMPRODUCT((I474=$I$6:$I$1500)*(B474&lt;$B$6:$B$1500))+SUMPRODUCT((I474=$I$6:$I$474)*(B474=$B$6:$B$474)))</f>
+        <f aca="false">IF(J474="","",SUMPRODUCT((I474=$I$6:$I$1500)*(B474&lt;$B$6:$B$1500))+COUNTIFS($I$6:I474,I474,$B$6:B474,B474))</f>
         <v/>
       </c>
     </row>
@@ -22636,7 +22636,7 @@
         <v/>
       </c>
       <c r="K475" s="25" t="str">
-        <f aca="false">IF(J475="","",SUMPRODUCT((I475=$I$6:$I$1500)*(B475&lt;$B$6:$B$1500))+SUMPRODUCT((I475=$I$6:$I$475)*(B475=$B$6:$B$475)))</f>
+        <f aca="false">IF(J475="","",SUMPRODUCT((I475=$I$6:$I$1500)*(B475&lt;$B$6:$B$1500))+COUNTIFS($I$6:I475,I475,$B$6:B475,B475))</f>
         <v/>
       </c>
     </row>
@@ -22674,7 +22674,7 @@
         <v/>
       </c>
       <c r="K476" s="25" t="str">
-        <f aca="false">IF(J476="","",SUMPRODUCT((I476=$I$6:$I$1500)*(B476&lt;$B$6:$B$1500))+SUMPRODUCT((I476=$I$6:$I$476)*(B476=$B$6:$B$476)))</f>
+        <f aca="false">IF(J476="","",SUMPRODUCT((I476=$I$6:$I$1500)*(B476&lt;$B$6:$B$1500))+COUNTIFS($I$6:I476,I476,$B$6:B476,B476))</f>
         <v/>
       </c>
     </row>
@@ -22712,7 +22712,7 @@
         <v/>
       </c>
       <c r="K477" s="25" t="str">
-        <f aca="false">IF(J477="","",SUMPRODUCT((I477=$I$6:$I$1500)*(B477&lt;$B$6:$B$1500))+SUMPRODUCT((I477=$I$6:$I$477)*(B477=$B$6:$B$477)))</f>
+        <f aca="false">IF(J477="","",SUMPRODUCT((I477=$I$6:$I$1500)*(B477&lt;$B$6:$B$1500))+COUNTIFS($I$6:I477,I477,$B$6:B477,B477))</f>
         <v/>
       </c>
     </row>
@@ -22750,7 +22750,7 @@
         <v/>
       </c>
       <c r="K478" s="25" t="str">
-        <f aca="false">IF(J478="","",SUMPRODUCT((I478=$I$6:$I$1500)*(B478&lt;$B$6:$B$1500))+SUMPRODUCT((I478=$I$6:$I$478)*(B478=$B$6:$B$478)))</f>
+        <f aca="false">IF(J478="","",SUMPRODUCT((I478=$I$6:$I$1500)*(B478&lt;$B$6:$B$1500))+COUNTIFS($I$6:I478,I478,$B$6:B478,B478))</f>
         <v/>
       </c>
     </row>
@@ -22788,7 +22788,7 @@
         <v/>
       </c>
       <c r="K479" s="25" t="str">
-        <f aca="false">IF(J479="","",SUMPRODUCT((I479=$I$6:$I$1500)*(B479&lt;$B$6:$B$1500))+SUMPRODUCT((I479=$I$6:$I$479)*(B479=$B$6:$B$479)))</f>
+        <f aca="false">IF(J479="","",SUMPRODUCT((I479=$I$6:$I$1500)*(B479&lt;$B$6:$B$1500))+COUNTIFS($I$6:I479,I479,$B$6:B479,B479))</f>
         <v/>
       </c>
     </row>
@@ -22826,7 +22826,7 @@
         <v/>
       </c>
       <c r="K480" s="25" t="str">
-        <f aca="false">IF(J480="","",SUMPRODUCT((I480=$I$6:$I$1500)*(B480&lt;$B$6:$B$1500))+SUMPRODUCT((I480=$I$6:$I$480)*(B480=$B$6:$B$480)))</f>
+        <f aca="false">IF(J480="","",SUMPRODUCT((I480=$I$6:$I$1500)*(B480&lt;$B$6:$B$1500))+COUNTIFS($I$6:I480,I480,$B$6:B480,B480))</f>
         <v/>
       </c>
     </row>
@@ -22864,7 +22864,7 @@
         <v/>
       </c>
       <c r="K481" s="25" t="str">
-        <f aca="false">IF(J481="","",SUMPRODUCT((I481=$I$6:$I$1500)*(B481&lt;$B$6:$B$1500))+SUMPRODUCT((I481=$I$6:$I$481)*(B481=$B$6:$B$481)))</f>
+        <f aca="false">IF(J481="","",SUMPRODUCT((I481=$I$6:$I$1500)*(B481&lt;$B$6:$B$1500))+COUNTIFS($I$6:I481,I481,$B$6:B481,B481))</f>
         <v/>
       </c>
     </row>
@@ -22902,7 +22902,7 @@
         <v/>
       </c>
       <c r="K482" s="25" t="str">
-        <f aca="false">IF(J482="","",SUMPRODUCT((I482=$I$6:$I$1500)*(B482&lt;$B$6:$B$1500))+SUMPRODUCT((I482=$I$6:$I$482)*(B482=$B$6:$B$482)))</f>
+        <f aca="false">IF(J482="","",SUMPRODUCT((I482=$I$6:$I$1500)*(B482&lt;$B$6:$B$1500))+COUNTIFS($I$6:I482,I482,$B$6:B482,B482))</f>
         <v/>
       </c>
     </row>
@@ -22940,7 +22940,7 @@
         <v/>
       </c>
       <c r="K483" s="25" t="str">
-        <f aca="false">IF(J483="","",SUMPRODUCT((I483=$I$6:$I$1500)*(B483&lt;$B$6:$B$1500))+SUMPRODUCT((I483=$I$6:$I$483)*(B483=$B$6:$B$483)))</f>
+        <f aca="false">IF(J483="","",SUMPRODUCT((I483=$I$6:$I$1500)*(B483&lt;$B$6:$B$1500))+COUNTIFS($I$6:I483,I483,$B$6:B483,B483))</f>
         <v/>
       </c>
     </row>
@@ -22978,7 +22978,7 @@
         <v/>
       </c>
       <c r="K484" s="25" t="str">
-        <f aca="false">IF(J484="","",SUMPRODUCT((I484=$I$6:$I$1500)*(B484&lt;$B$6:$B$1500))+SUMPRODUCT((I484=$I$6:$I$484)*(B484=$B$6:$B$484)))</f>
+        <f aca="false">IF(J484="","",SUMPRODUCT((I484=$I$6:$I$1500)*(B484&lt;$B$6:$B$1500))+COUNTIFS($I$6:I484,I484,$B$6:B484,B484))</f>
         <v/>
       </c>
     </row>
@@ -23016,7 +23016,7 @@
         <v/>
       </c>
       <c r="K485" s="25" t="str">
-        <f aca="false">IF(J485="","",SUMPRODUCT((I485=$I$6:$I$1500)*(B485&lt;$B$6:$B$1500))+SUMPRODUCT((I485=$I$6:$I$485)*(B485=$B$6:$B$485)))</f>
+        <f aca="false">IF(J485="","",SUMPRODUCT((I485=$I$6:$I$1500)*(B485&lt;$B$6:$B$1500))+COUNTIFS($I$6:I485,I485,$B$6:B485,B485))</f>
         <v/>
       </c>
     </row>
@@ -23054,7 +23054,7 @@
         <v/>
       </c>
       <c r="K486" s="25" t="str">
-        <f aca="false">IF(J486="","",SUMPRODUCT((I486=$I$6:$I$1500)*(B486&lt;$B$6:$B$1500))+SUMPRODUCT((I486=$I$6:$I$486)*(B486=$B$6:$B$486)))</f>
+        <f aca="false">IF(J486="","",SUMPRODUCT((I486=$I$6:$I$1500)*(B486&lt;$B$6:$B$1500))+COUNTIFS($I$6:I486,I486,$B$6:B486,B486))</f>
         <v/>
       </c>
     </row>
@@ -23092,7 +23092,7 @@
         <v/>
       </c>
       <c r="K487" s="25" t="str">
-        <f aca="false">IF(J487="","",SUMPRODUCT((I487=$I$6:$I$1500)*(B487&lt;$B$6:$B$1500))+SUMPRODUCT((I487=$I$6:$I$487)*(B487=$B$6:$B$487)))</f>
+        <f aca="false">IF(J487="","",SUMPRODUCT((I487=$I$6:$I$1500)*(B487&lt;$B$6:$B$1500))+COUNTIFS($I$6:I487,I487,$B$6:B487,B487))</f>
         <v/>
       </c>
     </row>
@@ -23130,7 +23130,7 @@
         <v/>
       </c>
       <c r="K488" s="25" t="str">
-        <f aca="false">IF(J488="","",SUMPRODUCT((I488=$I$6:$I$1500)*(B488&lt;$B$6:$B$1500))+SUMPRODUCT((I488=$I$6:$I$488)*(B488=$B$6:$B$488)))</f>
+        <f aca="false">IF(J488="","",SUMPRODUCT((I488=$I$6:$I$1500)*(B488&lt;$B$6:$B$1500))+COUNTIFS($I$6:I488,I488,$B$6:B488,B488))</f>
         <v/>
       </c>
     </row>
@@ -23168,7 +23168,7 @@
         <v/>
       </c>
       <c r="K489" s="25" t="str">
-        <f aca="false">IF(J489="","",SUMPRODUCT((I489=$I$6:$I$1500)*(B489&lt;$B$6:$B$1500))+SUMPRODUCT((I489=$I$6:$I$489)*(B489=$B$6:$B$489)))</f>
+        <f aca="false">IF(J489="","",SUMPRODUCT((I489=$I$6:$I$1500)*(B489&lt;$B$6:$B$1500))+COUNTIFS($I$6:I489,I489,$B$6:B489,B489))</f>
         <v/>
       </c>
     </row>
@@ -23206,7 +23206,7 @@
         <v/>
       </c>
       <c r="K490" s="25" t="str">
-        <f aca="false">IF(J490="","",SUMPRODUCT((I490=$I$6:$I$1500)*(B490&lt;$B$6:$B$1500))+SUMPRODUCT((I490=$I$6:$I$490)*(B490=$B$6:$B$490)))</f>
+        <f aca="false">IF(J490="","",SUMPRODUCT((I490=$I$6:$I$1500)*(B490&lt;$B$6:$B$1500))+COUNTIFS($I$6:I490,I490,$B$6:B490,B490))</f>
         <v/>
       </c>
     </row>
@@ -23244,7 +23244,7 @@
         <v/>
       </c>
       <c r="K491" s="25" t="str">
-        <f aca="false">IF(J491="","",SUMPRODUCT((I491=$I$6:$I$1500)*(B491&lt;$B$6:$B$1500))+SUMPRODUCT((I491=$I$6:$I$491)*(B491=$B$6:$B$491)))</f>
+        <f aca="false">IF(J491="","",SUMPRODUCT((I491=$I$6:$I$1500)*(B491&lt;$B$6:$B$1500))+COUNTIFS($I$6:I491,I491,$B$6:B491,B491))</f>
         <v/>
       </c>
     </row>
@@ -23282,7 +23282,7 @@
         <v/>
       </c>
       <c r="K492" s="25" t="str">
-        <f aca="false">IF(J492="","",SUMPRODUCT((I492=$I$6:$I$1500)*(B492&lt;$B$6:$B$1500))+SUMPRODUCT((I492=$I$6:$I$492)*(B492=$B$6:$B$492)))</f>
+        <f aca="false">IF(J492="","",SUMPRODUCT((I492=$I$6:$I$1500)*(B492&lt;$B$6:$B$1500))+COUNTIFS($I$6:I492,I492,$B$6:B492,B492))</f>
         <v/>
       </c>
     </row>
@@ -23320,7 +23320,7 @@
         <v/>
       </c>
       <c r="K493" s="25" t="str">
-        <f aca="false">IF(J493="","",SUMPRODUCT((I493=$I$6:$I$1500)*(B493&lt;$B$6:$B$1500))+SUMPRODUCT((I493=$I$6:$I$493)*(B493=$B$6:$B$493)))</f>
+        <f aca="false">IF(J493="","",SUMPRODUCT((I493=$I$6:$I$1500)*(B493&lt;$B$6:$B$1500))+COUNTIFS($I$6:I493,I493,$B$6:B493,B493))</f>
         <v/>
       </c>
     </row>
@@ -23358,7 +23358,7 @@
         <v/>
       </c>
       <c r="K494" s="25" t="str">
-        <f aca="false">IF(J494="","",SUMPRODUCT((I494=$I$6:$I$1500)*(B494&lt;$B$6:$B$1500))+SUMPRODUCT((I494=$I$6:$I$494)*(B494=$B$6:$B$494)))</f>
+        <f aca="false">IF(J494="","",SUMPRODUCT((I494=$I$6:$I$1500)*(B494&lt;$B$6:$B$1500))+COUNTIFS($I$6:I494,I494,$B$6:B494,B494))</f>
         <v/>
       </c>
     </row>
@@ -23394,7 +23394,7 @@
         <v/>
       </c>
       <c r="K495" s="25" t="str">
-        <f aca="false">IF(J495="","",SUMPRODUCT((I495=$I$6:$I$1500)*(B495&lt;$B$6:$B$1500))+SUMPRODUCT((I495=$I$6:$I$495)*(B495=$B$6:$B$495)))</f>
+        <f aca="false">IF(J495="","",SUMPRODUCT((I495=$I$6:$I$1500)*(B495&lt;$B$6:$B$1500))+COUNTIFS($I$6:I495,I495,$B$6:B495,B495))</f>
         <v/>
       </c>
     </row>
@@ -23432,7 +23432,7 @@
         <v>44</v>
       </c>
       <c r="K496" s="25" t="n">
-        <f aca="false">IF(J496="","",SUMPRODUCT((I496=$I$6:$I$1500)*(B496&lt;$B$6:$B$1500))+SUMPRODUCT((I496=$I$6:$I$496)*(B496=$B$6:$B$496)))</f>
+        <f aca="false">IF(J496="","",SUMPRODUCT((I496=$I$6:$I$1500)*(B496&lt;$B$6:$B$1500))+COUNTIFS($I$6:I496,I496,$B$6:B496,B496))</f>
         <v>3</v>
       </c>
     </row>
@@ -23470,7 +23470,7 @@
         <v>40</v>
       </c>
       <c r="K497" s="25" t="n">
-        <f aca="false">IF(J497="","",SUMPRODUCT((I497=$I$6:$I$1500)*(B497&lt;$B$6:$B$1500))+SUMPRODUCT((I497=$I$6:$I$497)*(B497=$B$6:$B$497)))</f>
+        <f aca="false">IF(J497="","",SUMPRODUCT((I497=$I$6:$I$1500)*(B497&lt;$B$6:$B$1500))+COUNTIFS($I$6:I497,I497,$B$6:B497,B497))</f>
         <v>5</v>
       </c>
     </row>
@@ -23508,7 +23508,7 @@
         <v>7</v>
       </c>
       <c r="K498" s="25" t="n">
-        <f aca="false">IF(J498="","",SUMPRODUCT((I498=$I$6:$I$1500)*(B498&lt;$B$6:$B$1500))+SUMPRODUCT((I498=$I$6:$I$498)*(B498=$B$6:$B$498)))</f>
+        <f aca="false">IF(J498="","",SUMPRODUCT((I498=$I$6:$I$1500)*(B498&lt;$B$6:$B$1500))+COUNTIFS($I$6:I498,I498,$B$6:B498,B498))</f>
         <v>12</v>
       </c>
     </row>
@@ -23544,7 +23544,7 @@
         <v/>
       </c>
       <c r="K499" s="25" t="str">
-        <f aca="false">IF(J499="","",SUMPRODUCT((I499=$I$6:$I$1500)*(B499&lt;$B$6:$B$1500))+SUMPRODUCT((I499=$I$6:$I$499)*(B499=$B$6:$B$499)))</f>
+        <f aca="false">IF(J499="","",SUMPRODUCT((I499=$I$6:$I$1500)*(B499&lt;$B$6:$B$1500))+COUNTIFS($I$6:I499,I499,$B$6:B499,B499))</f>
         <v/>
       </c>
     </row>
@@ -23582,7 +23582,7 @@
         <v/>
       </c>
       <c r="K500" s="25" t="str">
-        <f aca="false">IF(J500="","",SUMPRODUCT((I500=$I$6:$I$1500)*(B500&lt;$B$6:$B$1500))+SUMPRODUCT((I500=$I$6:$I$500)*(B500=$B$6:$B$500)))</f>
+        <f aca="false">IF(J500="","",SUMPRODUCT((I500=$I$6:$I$1500)*(B500&lt;$B$6:$B$1500))+COUNTIFS($I$6:I500,I500,$B$6:B500,B500))</f>
         <v/>
       </c>
     </row>
@@ -23618,7 +23618,7 @@
         <v/>
       </c>
       <c r="K501" s="25" t="str">
-        <f aca="false">IF(J501="","",SUMPRODUCT((I501=$I$6:$I$1500)*(B501&lt;$B$6:$B$1500))+SUMPRODUCT((I501=$I$6:$I$501)*(B501=$B$6:$B$501)))</f>
+        <f aca="false">IF(J501="","",SUMPRODUCT((I501=$I$6:$I$1500)*(B501&lt;$B$6:$B$1500))+COUNTIFS($I$6:I501,I501,$B$6:B501,B501))</f>
         <v/>
       </c>
     </row>
@@ -23656,7 +23656,7 @@
         <v>5</v>
       </c>
       <c r="K502" s="25" t="n">
-        <f aca="false">IF(J502="","",SUMPRODUCT((I502=$I$6:$I$1500)*(B502&lt;$B$6:$B$1500))+SUMPRODUCT((I502=$I$6:$I$502)*(B502=$B$6:$B$502)))</f>
+        <f aca="false">IF(J502="","",SUMPRODUCT((I502=$I$6:$I$1500)*(B502&lt;$B$6:$B$1500))+COUNTIFS($I$6:I502,I502,$B$6:B502,B502))</f>
         <v>15</v>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
         <v>1</v>
       </c>
       <c r="K503" s="25" t="n">
-        <f aca="false">IF(J503="","",SUMPRODUCT((I503=$I$6:$I$1500)*(B503&lt;$B$6:$B$1500))+SUMPRODUCT((I503=$I$6:$I$503)*(B503=$B$6:$B$503)))</f>
+        <f aca="false">IF(J503="","",SUMPRODUCT((I503=$I$6:$I$1500)*(B503&lt;$B$6:$B$1500))+COUNTIFS($I$6:I503,I503,$B$6:B503,B503))</f>
         <v>18</v>
       </c>
     </row>
@@ -23732,7 +23732,7 @@
         <v>1</v>
       </c>
       <c r="K504" s="25" t="n">
-        <f aca="false">IF(J504="","",SUMPRODUCT((I504=$I$6:$I$1500)*(B504&lt;$B$6:$B$1500))+SUMPRODUCT((I504=$I$6:$I$504)*(B504=$B$6:$B$504)))</f>
+        <f aca="false">IF(J504="","",SUMPRODUCT((I504=$I$6:$I$1500)*(B504&lt;$B$6:$B$1500))+COUNTIFS($I$6:I504,I504,$B$6:B504,B504))</f>
         <v>19</v>
       </c>
     </row>
@@ -23770,7 +23770,7 @@
         <v>1</v>
       </c>
       <c r="K505" s="25" t="n">
-        <f aca="false">IF(J505="","",SUMPRODUCT((I505=$I$6:$I$1500)*(B505&lt;$B$6:$B$1500))+SUMPRODUCT((I505=$I$6:$I$505)*(B505=$B$6:$B$505)))</f>
+        <f aca="false">IF(J505="","",SUMPRODUCT((I505=$I$6:$I$1500)*(B505&lt;$B$6:$B$1500))+COUNTIFS($I$6:I505,I505,$B$6:B505,B505))</f>
         <v>20</v>
       </c>
     </row>
@@ -23806,7 +23806,7 @@
         <v/>
       </c>
       <c r="K506" s="25" t="str">
-        <f aca="false">IF(J506="","",SUMPRODUCT((I506=$I$6:$I$1500)*(B506&lt;$B$6:$B$1500))+SUMPRODUCT((I506=$I$6:$I$506)*(B506=$B$6:$B$506)))</f>
+        <f aca="false">IF(J506="","",SUMPRODUCT((I506=$I$6:$I$1500)*(B506&lt;$B$6:$B$1500))+COUNTIFS($I$6:I506,I506,$B$6:B506,B506))</f>
         <v/>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
         <v/>
       </c>
       <c r="K507" s="25" t="str">
-        <f aca="false">IF(J507="","",SUMPRODUCT((I507=$I$6:$I$1500)*(B507&lt;$B$6:$B$1500))+SUMPRODUCT((I507=$I$6:$I$507)*(B507=$B$6:$B$507)))</f>
+        <f aca="false">IF(J507="","",SUMPRODUCT((I507=$I$6:$I$1500)*(B507&lt;$B$6:$B$1500))+COUNTIFS($I$6:I507,I507,$B$6:B507,B507))</f>
         <v/>
       </c>
     </row>
@@ -23882,7 +23882,7 @@
         <v/>
       </c>
       <c r="K508" s="25" t="str">
-        <f aca="false">IF(J508="","",SUMPRODUCT((I508=$I$6:$I$1500)*(B508&lt;$B$6:$B$1500))+SUMPRODUCT((I508=$I$6:$I$508)*(B508=$B$6:$B$508)))</f>
+        <f aca="false">IF(J508="","",SUMPRODUCT((I508=$I$6:$I$1500)*(B508&lt;$B$6:$B$1500))+COUNTIFS($I$6:I508,I508,$B$6:B508,B508))</f>
         <v/>
       </c>
     </row>
@@ -23920,7 +23920,7 @@
         <v/>
       </c>
       <c r="K509" s="25" t="str">
-        <f aca="false">IF(J509="","",SUMPRODUCT((I509=$I$6:$I$1500)*(B509&lt;$B$6:$B$1500))+SUMPRODUCT((I509=$I$6:$I$509)*(B509=$B$6:$B$509)))</f>
+        <f aca="false">IF(J509="","",SUMPRODUCT((I509=$I$6:$I$1500)*(B509&lt;$B$6:$B$1500))+COUNTIFS($I$6:I509,I509,$B$6:B509,B509))</f>
         <v/>
       </c>
     </row>
@@ -23958,7 +23958,7 @@
         <v/>
       </c>
       <c r="K510" s="25" t="str">
-        <f aca="false">IF(J510="","",SUMPRODUCT((I510=$I$6:$I$1500)*(B510&lt;$B$6:$B$1500))+SUMPRODUCT((I510=$I$6:$I$510)*(B510=$B$6:$B$510)))</f>
+        <f aca="false">IF(J510="","",SUMPRODUCT((I510=$I$6:$I$1500)*(B510&lt;$B$6:$B$1500))+COUNTIFS($I$6:I510,I510,$B$6:B510,B510))</f>
         <v/>
       </c>
     </row>
@@ -23996,7 +23996,7 @@
         <v/>
       </c>
       <c r="K511" s="25" t="str">
-        <f aca="false">IF(J511="","",SUMPRODUCT((I511=$I$6:$I$1500)*(B511&lt;$B$6:$B$1500))+SUMPRODUCT((I511=$I$6:$I$511)*(B511=$B$6:$B$511)))</f>
+        <f aca="false">IF(J511="","",SUMPRODUCT((I511=$I$6:$I$1500)*(B511&lt;$B$6:$B$1500))+COUNTIFS($I$6:I511,I511,$B$6:B511,B511))</f>
         <v/>
       </c>
     </row>
@@ -24034,7 +24034,7 @@
         <v/>
       </c>
       <c r="K512" s="25" t="str">
-        <f aca="false">IF(J512="","",SUMPRODUCT((I512=$I$6:$I$1500)*(B512&lt;$B$6:$B$1500))+SUMPRODUCT((I512=$I$6:$I$512)*(B512=$B$6:$B$512)))</f>
+        <f aca="false">IF(J512="","",SUMPRODUCT((I512=$I$6:$I$1500)*(B512&lt;$B$6:$B$1500))+COUNTIFS($I$6:I512,I512,$B$6:B512,B512))</f>
         <v/>
       </c>
     </row>
@@ -24072,7 +24072,7 @@
         <v/>
       </c>
       <c r="K513" s="25" t="str">
-        <f aca="false">IF(J513="","",SUMPRODUCT((I513=$I$6:$I$1500)*(B513&lt;$B$6:$B$1500))+SUMPRODUCT((I513=$I$6:$I$513)*(B513=$B$6:$B$513)))</f>
+        <f aca="false">IF(J513="","",SUMPRODUCT((I513=$I$6:$I$1500)*(B513&lt;$B$6:$B$1500))+COUNTIFS($I$6:I513,I513,$B$6:B513,B513))</f>
         <v/>
       </c>
     </row>
@@ -24110,7 +24110,7 @@
         <v/>
       </c>
       <c r="K514" s="25" t="str">
-        <f aca="false">IF(J514="","",SUMPRODUCT((I514=$I$6:$I$1500)*(B514&lt;$B$6:$B$1500))+SUMPRODUCT((I514=$I$6:$I$514)*(B514=$B$6:$B$514)))</f>
+        <f aca="false">IF(J514="","",SUMPRODUCT((I514=$I$6:$I$1500)*(B514&lt;$B$6:$B$1500))+COUNTIFS($I$6:I514,I514,$B$6:B514,B514))</f>
         <v/>
       </c>
     </row>
@@ -24148,7 +24148,7 @@
         <v/>
       </c>
       <c r="K515" s="25" t="str">
-        <f aca="false">IF(J515="","",SUMPRODUCT((I515=$I$6:$I$1500)*(B515&lt;$B$6:$B$1500))+SUMPRODUCT((I515=$I$6:$I$515)*(B515=$B$6:$B$515)))</f>
+        <f aca="false">IF(J515="","",SUMPRODUCT((I515=$I$6:$I$1500)*(B515&lt;$B$6:$B$1500))+COUNTIFS($I$6:I515,I515,$B$6:B515,B515))</f>
         <v/>
       </c>
     </row>
@@ -24186,7 +24186,7 @@
         <v/>
       </c>
       <c r="K516" s="25" t="str">
-        <f aca="false">IF(J516="","",SUMPRODUCT((I516=$I$6:$I$1500)*(B516&lt;$B$6:$B$1500))+SUMPRODUCT((I516=$I$6:$I$516)*(B516=$B$6:$B$516)))</f>
+        <f aca="false">IF(J516="","",SUMPRODUCT((I516=$I$6:$I$1500)*(B516&lt;$B$6:$B$1500))+COUNTIFS($I$6:I516,I516,$B$6:B516,B516))</f>
         <v/>
       </c>
     </row>
@@ -24224,7 +24224,7 @@
         <v/>
       </c>
       <c r="K517" s="25" t="str">
-        <f aca="false">IF(J517="","",SUMPRODUCT((I517=$I$6:$I$1500)*(B517&lt;$B$6:$B$1500))+SUMPRODUCT((I517=$I$6:$I$517)*(B517=$B$6:$B$517)))</f>
+        <f aca="false">IF(J517="","",SUMPRODUCT((I517=$I$6:$I$1500)*(B517&lt;$B$6:$B$1500))+COUNTIFS($I$6:I517,I517,$B$6:B517,B517))</f>
         <v/>
       </c>
     </row>
@@ -24262,7 +24262,7 @@
         <v/>
       </c>
       <c r="K518" s="25" t="str">
-        <f aca="false">IF(J518="","",SUMPRODUCT((I518=$I$6:$I$1500)*(B518&lt;$B$6:$B$1500))+SUMPRODUCT((I518=$I$6:$I$518)*(B518=$B$6:$B$518)))</f>
+        <f aca="false">IF(J518="","",SUMPRODUCT((I518=$I$6:$I$1500)*(B518&lt;$B$6:$B$1500))+COUNTIFS($I$6:I518,I518,$B$6:B518,B518))</f>
         <v/>
       </c>
     </row>
@@ -24300,7 +24300,7 @@
         <v/>
       </c>
       <c r="K519" s="25" t="str">
-        <f aca="false">IF(J519="","",SUMPRODUCT((I519=$I$6:$I$1500)*(B519&lt;$B$6:$B$1500))+SUMPRODUCT((I519=$I$6:$I$519)*(B519=$B$6:$B$519)))</f>
+        <f aca="false">IF(J519="","",SUMPRODUCT((I519=$I$6:$I$1500)*(B519&lt;$B$6:$B$1500))+COUNTIFS($I$6:I519,I519,$B$6:B519,B519))</f>
         <v/>
       </c>
     </row>
@@ -24338,7 +24338,7 @@
         <v/>
       </c>
       <c r="K520" s="25" t="str">
-        <f aca="false">IF(J520="","",SUMPRODUCT((I520=$I$6:$I$1500)*(B520&lt;$B$6:$B$1500))+SUMPRODUCT((I520=$I$6:$I$520)*(B520=$B$6:$B$520)))</f>
+        <f aca="false">IF(J520="","",SUMPRODUCT((I520=$I$6:$I$1500)*(B520&lt;$B$6:$B$1500))+COUNTIFS($I$6:I520,I520,$B$6:B520,B520))</f>
         <v/>
       </c>
     </row>
@@ -24376,7 +24376,7 @@
         <v/>
       </c>
       <c r="K521" s="25" t="str">
-        <f aca="false">IF(J521="","",SUMPRODUCT((I521=$I$6:$I$1500)*(B521&lt;$B$6:$B$1500))+SUMPRODUCT((I521=$I$6:$I$521)*(B521=$B$6:$B$521)))</f>
+        <f aca="false">IF(J521="","",SUMPRODUCT((I521=$I$6:$I$1500)*(B521&lt;$B$6:$B$1500))+COUNTIFS($I$6:I521,I521,$B$6:B521,B521))</f>
         <v/>
       </c>
     </row>
@@ -24414,7 +24414,7 @@
         <v/>
       </c>
       <c r="K522" s="25" t="str">
-        <f aca="false">IF(J522="","",SUMPRODUCT((I522=$I$6:$I$1500)*(B522&lt;$B$6:$B$1500))+SUMPRODUCT((I522=$I$6:$I$522)*(B522=$B$6:$B$522)))</f>
+        <f aca="false">IF(J522="","",SUMPRODUCT((I522=$I$6:$I$1500)*(B522&lt;$B$6:$B$1500))+COUNTIFS($I$6:I522,I522,$B$6:B522,B522))</f>
         <v/>
       </c>
     </row>
@@ -24452,7 +24452,7 @@
         <v/>
       </c>
       <c r="K523" s="25" t="str">
-        <f aca="false">IF(J523="","",SUMPRODUCT((I523=$I$6:$I$1500)*(B523&lt;$B$6:$B$1500))+SUMPRODUCT((I523=$I$6:$I$523)*(B523=$B$6:$B$523)))</f>
+        <f aca="false">IF(J523="","",SUMPRODUCT((I523=$I$6:$I$1500)*(B523&lt;$B$6:$B$1500))+COUNTIFS($I$6:I523,I523,$B$6:B523,B523))</f>
         <v/>
       </c>
     </row>
@@ -24490,7 +24490,7 @@
         <v/>
       </c>
       <c r="K524" s="25" t="str">
-        <f aca="false">IF(J524="","",SUMPRODUCT((I524=$I$6:$I$1500)*(B524&lt;$B$6:$B$1500))+SUMPRODUCT((I524=$I$6:$I$524)*(B524=$B$6:$B$524)))</f>
+        <f aca="false">IF(J524="","",SUMPRODUCT((I524=$I$6:$I$1500)*(B524&lt;$B$6:$B$1500))+COUNTIFS($I$6:I524,I524,$B$6:B524,B524))</f>
         <v/>
       </c>
     </row>
@@ -24528,7 +24528,7 @@
         <v/>
       </c>
       <c r="K525" s="25" t="str">
-        <f aca="false">IF(J525="","",SUMPRODUCT((I525=$I$6:$I$1500)*(B525&lt;$B$6:$B$1500))+SUMPRODUCT((I525=$I$6:$I$525)*(B525=$B$6:$B$525)))</f>
+        <f aca="false">IF(J525="","",SUMPRODUCT((I525=$I$6:$I$1500)*(B525&lt;$B$6:$B$1500))+COUNTIFS($I$6:I525,I525,$B$6:B525,B525))</f>
         <v/>
       </c>
     </row>
@@ -24566,7 +24566,7 @@
         <v/>
       </c>
       <c r="K526" s="25" t="str">
-        <f aca="false">IF(J526="","",SUMPRODUCT((I526=$I$6:$I$1500)*(B526&lt;$B$6:$B$1500))+SUMPRODUCT((I526=$I$6:$I$526)*(B526=$B$6:$B$526)))</f>
+        <f aca="false">IF(J526="","",SUMPRODUCT((I526=$I$6:$I$1500)*(B526&lt;$B$6:$B$1500))+COUNTIFS($I$6:I526,I526,$B$6:B526,B526))</f>
         <v/>
       </c>
     </row>
@@ -24604,7 +24604,7 @@
         <v/>
       </c>
       <c r="K527" s="25" t="str">
-        <f aca="false">IF(J527="","",SUMPRODUCT((I527=$I$6:$I$1500)*(B527&lt;$B$6:$B$1500))+SUMPRODUCT((I527=$I$6:$I$527)*(B527=$B$6:$B$527)))</f>
+        <f aca="false">IF(J527="","",SUMPRODUCT((I527=$I$6:$I$1500)*(B527&lt;$B$6:$B$1500))+COUNTIFS($I$6:I527,I527,$B$6:B527,B527))</f>
         <v/>
       </c>
     </row>
@@ -24642,7 +24642,7 @@
         <v/>
       </c>
       <c r="K528" s="25" t="str">
-        <f aca="false">IF(J528="","",SUMPRODUCT((I528=$I$6:$I$1500)*(B528&lt;$B$6:$B$1500))+SUMPRODUCT((I528=$I$6:$I$528)*(B528=$B$6:$B$528)))</f>
+        <f aca="false">IF(J528="","",SUMPRODUCT((I528=$I$6:$I$1500)*(B528&lt;$B$6:$B$1500))+COUNTIFS($I$6:I528,I528,$B$6:B528,B528))</f>
         <v/>
       </c>
     </row>
@@ -24680,7 +24680,7 @@
         <v/>
       </c>
       <c r="K529" s="25" t="str">
-        <f aca="false">IF(J529="","",SUMPRODUCT((I529=$I$6:$I$1500)*(B529&lt;$B$6:$B$1500))+SUMPRODUCT((I529=$I$6:$I$529)*(B529=$B$6:$B$529)))</f>
+        <f aca="false">IF(J529="","",SUMPRODUCT((I529=$I$6:$I$1500)*(B529&lt;$B$6:$B$1500))+COUNTIFS($I$6:I529,I529,$B$6:B529,B529))</f>
         <v/>
       </c>
     </row>
@@ -24718,7 +24718,7 @@
         <v/>
       </c>
       <c r="K530" s="25" t="str">
-        <f aca="false">IF(J530="","",SUMPRODUCT((I530=$I$6:$I$1500)*(B530&lt;$B$6:$B$1500))+SUMPRODUCT((I530=$I$6:$I$530)*(B530=$B$6:$B$530)))</f>
+        <f aca="false">IF(J530="","",SUMPRODUCT((I530=$I$6:$I$1500)*(B530&lt;$B$6:$B$1500))+COUNTIFS($I$6:I530,I530,$B$6:B530,B530))</f>
         <v/>
       </c>
     </row>
@@ -24756,7 +24756,7 @@
         <v/>
       </c>
       <c r="K531" s="25" t="str">
-        <f aca="false">IF(J531="","",SUMPRODUCT((I531=$I$6:$I$1500)*(B531&lt;$B$6:$B$1500))+SUMPRODUCT((I531=$I$6:$I$531)*(B531=$B$6:$B$531)))</f>
+        <f aca="false">IF(J531="","",SUMPRODUCT((I531=$I$6:$I$1500)*(B531&lt;$B$6:$B$1500))+COUNTIFS($I$6:I531,I531,$B$6:B531,B531))</f>
         <v/>
       </c>
     </row>
@@ -24794,7 +24794,7 @@
         <v/>
       </c>
       <c r="K532" s="25" t="str">
-        <f aca="false">IF(J532="","",SUMPRODUCT((I532=$I$6:$I$1500)*(B532&lt;$B$6:$B$1500))+SUMPRODUCT((I532=$I$6:$I$532)*(B532=$B$6:$B$532)))</f>
+        <f aca="false">IF(J532="","",SUMPRODUCT((I532=$I$6:$I$1500)*(B532&lt;$B$6:$B$1500))+COUNTIFS($I$6:I532,I532,$B$6:B532,B532))</f>
         <v/>
       </c>
     </row>
@@ -24832,7 +24832,7 @@
         <v/>
       </c>
       <c r="K533" s="25" t="str">
-        <f aca="false">IF(J533="","",SUMPRODUCT((I533=$I$6:$I$1500)*(B533&lt;$B$6:$B$1500))+SUMPRODUCT((I533=$I$6:$I$533)*(B533=$B$6:$B$533)))</f>
+        <f aca="false">IF(J533="","",SUMPRODUCT((I533=$I$6:$I$1500)*(B533&lt;$B$6:$B$1500))+COUNTIFS($I$6:I533,I533,$B$6:B533,B533))</f>
         <v/>
       </c>
     </row>
@@ -24870,7 +24870,7 @@
         <v/>
       </c>
       <c r="K534" s="25" t="str">
-        <f aca="false">IF(J534="","",SUMPRODUCT((I534=$I$6:$I$1500)*(B534&lt;$B$6:$B$1500))+SUMPRODUCT((I534=$I$6:$I$534)*(B534=$B$6:$B$534)))</f>
+        <f aca="false">IF(J534="","",SUMPRODUCT((I534=$I$6:$I$1500)*(B534&lt;$B$6:$B$1500))+COUNTIFS($I$6:I534,I534,$B$6:B534,B534))</f>
         <v/>
       </c>
     </row>
@@ -24908,7 +24908,7 @@
         <v/>
       </c>
       <c r="K535" s="25" t="str">
-        <f aca="false">IF(J535="","",SUMPRODUCT((I535=$I$6:$I$1500)*(B535&lt;$B$6:$B$1500))+SUMPRODUCT((I535=$I$6:$I$535)*(B535=$B$6:$B$535)))</f>
+        <f aca="false">IF(J535="","",SUMPRODUCT((I535=$I$6:$I$1500)*(B535&lt;$B$6:$B$1500))+COUNTIFS($I$6:I535,I535,$B$6:B535,B535))</f>
         <v/>
       </c>
     </row>
@@ -24946,7 +24946,7 @@
         <v/>
       </c>
       <c r="K536" s="25" t="str">
-        <f aca="false">IF(J536="","",SUMPRODUCT((I536=$I$6:$I$1500)*(B536&lt;$B$6:$B$1500))+SUMPRODUCT((I536=$I$6:$I$536)*(B536=$B$6:$B$536)))</f>
+        <f aca="false">IF(J536="","",SUMPRODUCT((I536=$I$6:$I$1500)*(B536&lt;$B$6:$B$1500))+COUNTIFS($I$6:I536,I536,$B$6:B536,B536))</f>
         <v/>
       </c>
     </row>
@@ -24984,7 +24984,7 @@
         <v/>
       </c>
       <c r="K537" s="25" t="str">
-        <f aca="false">IF(J537="","",SUMPRODUCT((I537=$I$6:$I$1500)*(B537&lt;$B$6:$B$1500))+SUMPRODUCT((I537=$I$6:$I$537)*(B537=$B$6:$B$537)))</f>
+        <f aca="false">IF(J537="","",SUMPRODUCT((I537=$I$6:$I$1500)*(B537&lt;$B$6:$B$1500))+COUNTIFS($I$6:I537,I537,$B$6:B537,B537))</f>
         <v/>
       </c>
     </row>
@@ -25022,7 +25022,7 @@
         <v/>
       </c>
       <c r="K538" s="25" t="str">
-        <f aca="false">IF(J538="","",SUMPRODUCT((I538=$I$6:$I$1500)*(B538&lt;$B$6:$B$1500))+SUMPRODUCT((I538=$I$6:$I$538)*(B538=$B$6:$B$538)))</f>
+        <f aca="false">IF(J538="","",SUMPRODUCT((I538=$I$6:$I$1500)*(B538&lt;$B$6:$B$1500))+COUNTIFS($I$6:I538,I538,$B$6:B538,B538))</f>
         <v/>
       </c>
     </row>
@@ -25060,7 +25060,7 @@
         <v/>
       </c>
       <c r="K539" s="25" t="str">
-        <f aca="false">IF(J539="","",SUMPRODUCT((I539=$I$6:$I$1500)*(B539&lt;$B$6:$B$1500))+SUMPRODUCT((I539=$I$6:$I$539)*(B539=$B$6:$B$539)))</f>
+        <f aca="false">IF(J539="","",SUMPRODUCT((I539=$I$6:$I$1500)*(B539&lt;$B$6:$B$1500))+COUNTIFS($I$6:I539,I539,$B$6:B539,B539))</f>
         <v/>
       </c>
     </row>
@@ -25098,7 +25098,7 @@
         <v/>
       </c>
       <c r="K540" s="25" t="str">
-        <f aca="false">IF(J540="","",SUMPRODUCT((I540=$I$6:$I$1500)*(B540&lt;$B$6:$B$1500))+SUMPRODUCT((I540=$I$6:$I$540)*(B540=$B$6:$B$540)))</f>
+        <f aca="false">IF(J540="","",SUMPRODUCT((I540=$I$6:$I$1500)*(B540&lt;$B$6:$B$1500))+COUNTIFS($I$6:I540,I540,$B$6:B540,B540))</f>
         <v/>
       </c>
     </row>
@@ -25136,7 +25136,7 @@
         <v/>
       </c>
       <c r="K541" s="25" t="str">
-        <f aca="false">IF(J541="","",SUMPRODUCT((I541=$I$6:$I$1500)*(B541&lt;$B$6:$B$1500))+SUMPRODUCT((I541=$I$6:$I$541)*(B541=$B$6:$B$541)))</f>
+        <f aca="false">IF(J541="","",SUMPRODUCT((I541=$I$6:$I$1500)*(B541&lt;$B$6:$B$1500))+COUNTIFS($I$6:I541,I541,$B$6:B541,B541))</f>
         <v/>
       </c>
     </row>
@@ -25174,7 +25174,7 @@
         <v/>
       </c>
       <c r="K542" s="25" t="str">
-        <f aca="false">IF(J542="","",SUMPRODUCT((I542=$I$6:$I$1500)*(B542&lt;$B$6:$B$1500))+SUMPRODUCT((I542=$I$6:$I$542)*(B542=$B$6:$B$542)))</f>
+        <f aca="false">IF(J542="","",SUMPRODUCT((I542=$I$6:$I$1500)*(B542&lt;$B$6:$B$1500))+COUNTIFS($I$6:I542,I542,$B$6:B542,B542))</f>
         <v/>
       </c>
     </row>
@@ -25212,7 +25212,7 @@
         <v/>
       </c>
       <c r="K543" s="25" t="str">
-        <f aca="false">IF(J543="","",SUMPRODUCT((I543=$I$6:$I$1500)*(B543&lt;$B$6:$B$1500))+SUMPRODUCT((I543=$I$6:$I$543)*(B543=$B$6:$B$543)))</f>
+        <f aca="false">IF(J543="","",SUMPRODUCT((I543=$I$6:$I$1500)*(B543&lt;$B$6:$B$1500))+COUNTIFS($I$6:I543,I543,$B$6:B543,B543))</f>
         <v/>
       </c>
     </row>
@@ -25250,7 +25250,7 @@
         <v/>
       </c>
       <c r="K544" s="25" t="str">
-        <f aca="false">IF(J544="","",SUMPRODUCT((I544=$I$6:$I$1500)*(B544&lt;$B$6:$B$1500))+SUMPRODUCT((I544=$I$6:$I$544)*(B544=$B$6:$B$544)))</f>
+        <f aca="false">IF(J544="","",SUMPRODUCT((I544=$I$6:$I$1500)*(B544&lt;$B$6:$B$1500))+COUNTIFS($I$6:I544,I544,$B$6:B544,B544))</f>
         <v/>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
         <v/>
       </c>
       <c r="K545" s="25" t="str">
-        <f aca="false">IF(J545="","",SUMPRODUCT((I545=$I$6:$I$1500)*(B545&lt;$B$6:$B$1500))+SUMPRODUCT((I545=$I$6:$I$545)*(B545=$B$6:$B$545)))</f>
+        <f aca="false">IF(J545="","",SUMPRODUCT((I545=$I$6:$I$1500)*(B545&lt;$B$6:$B$1500))+COUNTIFS($I$6:I545,I545,$B$6:B545,B545))</f>
         <v/>
       </c>
     </row>
@@ -25326,7 +25326,7 @@
         <v/>
       </c>
       <c r="K546" s="25" t="str">
-        <f aca="false">IF(J546="","",SUMPRODUCT((I546=$I$6:$I$1500)*(B546&lt;$B$6:$B$1500))+SUMPRODUCT((I546=$I$6:$I$546)*(B546=$B$6:$B$546)))</f>
+        <f aca="false">IF(J546="","",SUMPRODUCT((I546=$I$6:$I$1500)*(B546&lt;$B$6:$B$1500))+COUNTIFS($I$6:I546,I546,$B$6:B546,B546))</f>
         <v/>
       </c>
     </row>
@@ -25364,7 +25364,7 @@
         <v/>
       </c>
       <c r="K547" s="25" t="str">
-        <f aca="false">IF(J547="","",SUMPRODUCT((I547=$I$6:$I$1500)*(B547&lt;$B$6:$B$1500))+SUMPRODUCT((I547=$I$6:$I$547)*(B547=$B$6:$B$547)))</f>
+        <f aca="false">IF(J547="","",SUMPRODUCT((I547=$I$6:$I$1500)*(B547&lt;$B$6:$B$1500))+COUNTIFS($I$6:I547,I547,$B$6:B547,B547))</f>
         <v/>
       </c>
     </row>
@@ -25402,7 +25402,7 @@
         <v/>
       </c>
       <c r="K548" s="25" t="str">
-        <f aca="false">IF(J548="","",SUMPRODUCT((I548=$I$6:$I$1500)*(B548&lt;$B$6:$B$1500))+SUMPRODUCT((I548=$I$6:$I$548)*(B548=$B$6:$B$548)))</f>
+        <f aca="false">IF(J548="","",SUMPRODUCT((I548=$I$6:$I$1500)*(B548&lt;$B$6:$B$1500))+COUNTIFS($I$6:I548,I548,$B$6:B548,B548))</f>
         <v/>
       </c>
     </row>
@@ -25440,7 +25440,7 @@
         <v/>
       </c>
       <c r="K549" s="25" t="str">
-        <f aca="false">IF(J549="","",SUMPRODUCT((I549=$I$6:$I$1500)*(B549&lt;$B$6:$B$1500))+SUMPRODUCT((I549=$I$6:$I$549)*(B549=$B$6:$B$549)))</f>
+        <f aca="false">IF(J549="","",SUMPRODUCT((I549=$I$6:$I$1500)*(B549&lt;$B$6:$B$1500))+COUNTIFS($I$6:I549,I549,$B$6:B549,B549))</f>
         <v/>
       </c>
     </row>
@@ -25478,7 +25478,7 @@
         <v/>
       </c>
       <c r="K550" s="25" t="str">
-        <f aca="false">IF(J550="","",SUMPRODUCT((I550=$I$6:$I$1500)*(B550&lt;$B$6:$B$1500))+SUMPRODUCT((I550=$I$6:$I$550)*(B550=$B$6:$B$550)))</f>
+        <f aca="false">IF(J550="","",SUMPRODUCT((I550=$I$6:$I$1500)*(B550&lt;$B$6:$B$1500))+COUNTIFS($I$6:I550,I550,$B$6:B550,B550))</f>
         <v/>
       </c>
     </row>
@@ -25516,7 +25516,7 @@
         <v/>
       </c>
       <c r="K551" s="25" t="str">
-        <f aca="false">IF(J551="","",SUMPRODUCT((I551=$I$6:$I$1500)*(B551&lt;$B$6:$B$1500))+SUMPRODUCT((I551=$I$6:$I$551)*(B551=$B$6:$B$551)))</f>
+        <f aca="false">IF(J551="","",SUMPRODUCT((I551=$I$6:$I$1500)*(B551&lt;$B$6:$B$1500))+COUNTIFS($I$6:I551,I551,$B$6:B551,B551))</f>
         <v/>
       </c>
     </row>
@@ -25554,7 +25554,7 @@
         <v/>
       </c>
       <c r="K552" s="25" t="str">
-        <f aca="false">IF(J552="","",SUMPRODUCT((I552=$I$6:$I$1500)*(B552&lt;$B$6:$B$1500))+SUMPRODUCT((I552=$I$6:$I$552)*(B552=$B$6:$B$552)))</f>
+        <f aca="false">IF(J552="","",SUMPRODUCT((I552=$I$6:$I$1500)*(B552&lt;$B$6:$B$1500))+COUNTIFS($I$6:I552,I552,$B$6:B552,B552))</f>
         <v/>
       </c>
     </row>
@@ -25592,7 +25592,7 @@
         <v/>
       </c>
       <c r="K553" s="25" t="str">
-        <f aca="false">IF(J553="","",SUMPRODUCT((I553=$I$6:$I$1500)*(B553&lt;$B$6:$B$1500))+SUMPRODUCT((I553=$I$6:$I$553)*(B553=$B$6:$B$553)))</f>
+        <f aca="false">IF(J553="","",SUMPRODUCT((I553=$I$6:$I$1500)*(B553&lt;$B$6:$B$1500))+COUNTIFS($I$6:I553,I553,$B$6:B553,B553))</f>
         <v/>
       </c>
     </row>
@@ -25630,7 +25630,7 @@
         <v/>
       </c>
       <c r="K554" s="25" t="str">
-        <f aca="false">IF(J554="","",SUMPRODUCT((I554=$I$6:$I$1500)*(B554&lt;$B$6:$B$1500))+SUMPRODUCT((I554=$I$6:$I$554)*(B554=$B$6:$B$554)))</f>
+        <f aca="false">IF(J554="","",SUMPRODUCT((I554=$I$6:$I$1500)*(B554&lt;$B$6:$B$1500))+COUNTIFS($I$6:I554,I554,$B$6:B554,B554))</f>
         <v/>
       </c>
     </row>
@@ -25668,7 +25668,7 @@
         <v/>
       </c>
       <c r="K555" s="25" t="str">
-        <f aca="false">IF(J555="","",SUMPRODUCT((I555=$I$6:$I$1500)*(B555&lt;$B$6:$B$1500))+SUMPRODUCT((I555=$I$6:$I$555)*(B555=$B$6:$B$555)))</f>
+        <f aca="false">IF(J555="","",SUMPRODUCT((I555=$I$6:$I$1500)*(B555&lt;$B$6:$B$1500))+COUNTIFS($I$6:I555,I555,$B$6:B555,B555))</f>
         <v/>
       </c>
     </row>
@@ -25706,7 +25706,7 @@
         <v/>
       </c>
       <c r="K556" s="25" t="str">
-        <f aca="false">IF(J556="","",SUMPRODUCT((I556=$I$6:$I$1500)*(B556&lt;$B$6:$B$1500))+SUMPRODUCT((I556=$I$6:$I$556)*(B556=$B$6:$B$556)))</f>
+        <f aca="false">IF(J556="","",SUMPRODUCT((I556=$I$6:$I$1500)*(B556&lt;$B$6:$B$1500))+COUNTIFS($I$6:I556,I556,$B$6:B556,B556))</f>
         <v/>
       </c>
     </row>
@@ -25744,7 +25744,7 @@
         <v/>
       </c>
       <c r="K557" s="25" t="str">
-        <f aca="false">IF(J557="","",SUMPRODUCT((I557=$I$6:$I$1500)*(B557&lt;$B$6:$B$1500))+SUMPRODUCT((I557=$I$6:$I$557)*(B557=$B$6:$B$557)))</f>
+        <f aca="false">IF(J557="","",SUMPRODUCT((I557=$I$6:$I$1500)*(B557&lt;$B$6:$B$1500))+COUNTIFS($I$6:I557,I557,$B$6:B557,B557))</f>
         <v/>
       </c>
     </row>
@@ -25782,7 +25782,7 @@
         <v/>
       </c>
       <c r="K558" s="25" t="str">
-        <f aca="false">IF(J558="","",SUMPRODUCT((I558=$I$6:$I$1500)*(B558&lt;$B$6:$B$1500))+SUMPRODUCT((I558=$I$6:$I$558)*(B558=$B$6:$B$558)))</f>
+        <f aca="false">IF(J558="","",SUMPRODUCT((I558=$I$6:$I$1500)*(B558&lt;$B$6:$B$1500))+COUNTIFS($I$6:I558,I558,$B$6:B558,B558))</f>
         <v/>
       </c>
     </row>
@@ -25820,7 +25820,7 @@
         <v/>
       </c>
       <c r="K559" s="25" t="str">
-        <f aca="false">IF(J559="","",SUMPRODUCT((I559=$I$6:$I$1500)*(B559&lt;$B$6:$B$1500))+SUMPRODUCT((I559=$I$6:$I$559)*(B559=$B$6:$B$559)))</f>
+        <f aca="false">IF(J559="","",SUMPRODUCT((I559=$I$6:$I$1500)*(B559&lt;$B$6:$B$1500))+COUNTIFS($I$6:I559,I559,$B$6:B559,B559))</f>
         <v/>
       </c>
     </row>
@@ -25858,7 +25858,7 @@
         <v/>
       </c>
       <c r="K560" s="25" t="str">
-        <f aca="false">IF(J560="","",SUMPRODUCT((I560=$I$6:$I$1500)*(B560&lt;$B$6:$B$1500))+SUMPRODUCT((I560=$I$6:$I$560)*(B560=$B$6:$B$560)))</f>
+        <f aca="false">IF(J560="","",SUMPRODUCT((I560=$I$6:$I$1500)*(B560&lt;$B$6:$B$1500))+COUNTIFS($I$6:I560,I560,$B$6:B560,B560))</f>
         <v/>
       </c>
     </row>
@@ -25896,7 +25896,7 @@
         <v/>
       </c>
       <c r="K561" s="25" t="str">
-        <f aca="false">IF(J561="","",SUMPRODUCT((I561=$I$6:$I$1500)*(B561&lt;$B$6:$B$1500))+SUMPRODUCT((I561=$I$6:$I$561)*(B561=$B$6:$B$561)))</f>
+        <f aca="false">IF(J561="","",SUMPRODUCT((I561=$I$6:$I$1500)*(B561&lt;$B$6:$B$1500))+COUNTIFS($I$6:I561,I561,$B$6:B561,B561))</f>
         <v/>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
         <v/>
       </c>
       <c r="K562" s="25" t="str">
-        <f aca="false">IF(J562="","",SUMPRODUCT((I562=$I$6:$I$1500)*(B562&lt;$B$6:$B$1500))+SUMPRODUCT((I562=$I$6:$I$562)*(B562=$B$6:$B$562)))</f>
+        <f aca="false">IF(J562="","",SUMPRODUCT((I562=$I$6:$I$1500)*(B562&lt;$B$6:$B$1500))+COUNTIFS($I$6:I562,I562,$B$6:B562,B562))</f>
         <v/>
       </c>
     </row>
@@ -25972,7 +25972,7 @@
         <v/>
       </c>
       <c r="K563" s="25" t="str">
-        <f aca="false">IF(J563="","",SUMPRODUCT((I563=$I$6:$I$1500)*(B563&lt;$B$6:$B$1500))+SUMPRODUCT((I563=$I$6:$I$563)*(B563=$B$6:$B$563)))</f>
+        <f aca="false">IF(J563="","",SUMPRODUCT((I563=$I$6:$I$1500)*(B563&lt;$B$6:$B$1500))+COUNTIFS($I$6:I563,I563,$B$6:B563,B563))</f>
         <v/>
       </c>
     </row>
@@ -26010,7 +26010,7 @@
         <v/>
       </c>
       <c r="K564" s="25" t="str">
-        <f aca="false">IF(J564="","",SUMPRODUCT((I564=$I$6:$I$1500)*(B564&lt;$B$6:$B$1500))+SUMPRODUCT((I564=$I$6:$I$564)*(B564=$B$6:$B$564)))</f>
+        <f aca="false">IF(J564="","",SUMPRODUCT((I564=$I$6:$I$1500)*(B564&lt;$B$6:$B$1500))+COUNTIFS($I$6:I564,I564,$B$6:B564,B564))</f>
         <v/>
       </c>
     </row>
@@ -26048,7 +26048,7 @@
         <v/>
       </c>
       <c r="K565" s="25" t="str">
-        <f aca="false">IF(J565="","",SUMPRODUCT((I565=$I$6:$I$1500)*(B565&lt;$B$6:$B$1500))+SUMPRODUCT((I565=$I$6:$I$565)*(B565=$B$6:$B$565)))</f>
+        <f aca="false">IF(J565="","",SUMPRODUCT((I565=$I$6:$I$1500)*(B565&lt;$B$6:$B$1500))+COUNTIFS($I$6:I565,I565,$B$6:B565,B565))</f>
         <v/>
       </c>
     </row>
@@ -26086,7 +26086,7 @@
         <v/>
       </c>
       <c r="K566" s="25" t="str">
-        <f aca="false">IF(J566="","",SUMPRODUCT((I566=$I$6:$I$1500)*(B566&lt;$B$6:$B$1500))+SUMPRODUCT((I566=$I$6:$I$566)*(B566=$B$6:$B$566)))</f>
+        <f aca="false">IF(J566="","",SUMPRODUCT((I566=$I$6:$I$1500)*(B566&lt;$B$6:$B$1500))+COUNTIFS($I$6:I566,I566,$B$6:B566,B566))</f>
         <v/>
       </c>
     </row>
@@ -26124,7 +26124,7 @@
         <v/>
       </c>
       <c r="K567" s="25" t="str">
-        <f aca="false">IF(J567="","",SUMPRODUCT((I567=$I$6:$I$1500)*(B567&lt;$B$6:$B$1500))+SUMPRODUCT((I567=$I$6:$I$567)*(B567=$B$6:$B$567)))</f>
+        <f aca="false">IF(J567="","",SUMPRODUCT((I567=$I$6:$I$1500)*(B567&lt;$B$6:$B$1500))+COUNTIFS($I$6:I567,I567,$B$6:B567,B567))</f>
         <v/>
       </c>
     </row>
@@ -26162,7 +26162,7 @@
         <v/>
       </c>
       <c r="K568" s="25" t="str">
-        <f aca="false">IF(J568="","",SUMPRODUCT((I568=$I$6:$I$1500)*(B568&lt;$B$6:$B$1500))+SUMPRODUCT((I568=$I$6:$I$568)*(B568=$B$6:$B$568)))</f>
+        <f aca="false">IF(J568="","",SUMPRODUCT((I568=$I$6:$I$1500)*(B568&lt;$B$6:$B$1500))+COUNTIFS($I$6:I568,I568,$B$6:B568,B568))</f>
         <v/>
       </c>
     </row>
@@ -26200,7 +26200,7 @@
         <v/>
       </c>
       <c r="K569" s="25" t="str">
-        <f aca="false">IF(J569="","",SUMPRODUCT((I569=$I$6:$I$1500)*(B569&lt;$B$6:$B$1500))+SUMPRODUCT((I569=$I$6:$I$569)*(B569=$B$6:$B$569)))</f>
+        <f aca="false">IF(J569="","",SUMPRODUCT((I569=$I$6:$I$1500)*(B569&lt;$B$6:$B$1500))+COUNTIFS($I$6:I569,I569,$B$6:B569,B569))</f>
         <v/>
       </c>
     </row>
@@ -26238,7 +26238,7 @@
         <v/>
       </c>
       <c r="K570" s="25" t="str">
-        <f aca="false">IF(J570="","",SUMPRODUCT((I570=$I$6:$I$1500)*(B570&lt;$B$6:$B$1500))+SUMPRODUCT((I570=$I$6:$I$570)*(B570=$B$6:$B$570)))</f>
+        <f aca="false">IF(J570="","",SUMPRODUCT((I570=$I$6:$I$1500)*(B570&lt;$B$6:$B$1500))+COUNTIFS($I$6:I570,I570,$B$6:B570,B570))</f>
         <v/>
       </c>
     </row>
@@ -26276,7 +26276,7 @@
         <v/>
       </c>
       <c r="K571" s="25" t="str">
-        <f aca="false">IF(J571="","",SUMPRODUCT((I571=$I$6:$I$1500)*(B571&lt;$B$6:$B$1500))+SUMPRODUCT((I571=$I$6:$I$571)*(B571=$B$6:$B$571)))</f>
+        <f aca="false">IF(J571="","",SUMPRODUCT((I571=$I$6:$I$1500)*(B571&lt;$B$6:$B$1500))+COUNTIFS($I$6:I571,I571,$B$6:B571,B571))</f>
         <v/>
       </c>
     </row>
@@ -26314,7 +26314,7 @@
         <v/>
       </c>
       <c r="K572" s="25" t="str">
-        <f aca="false">IF(J572="","",SUMPRODUCT((I572=$I$6:$I$1500)*(B572&lt;$B$6:$B$1500))+SUMPRODUCT((I572=$I$6:$I$572)*(B572=$B$6:$B$572)))</f>
+        <f aca="false">IF(J572="","",SUMPRODUCT((I572=$I$6:$I$1500)*(B572&lt;$B$6:$B$1500))+COUNTIFS($I$6:I572,I572,$B$6:B572,B572))</f>
         <v/>
       </c>
     </row>
@@ -26352,7 +26352,7 @@
         <v/>
       </c>
       <c r="K573" s="25" t="str">
-        <f aca="false">IF(J573="","",SUMPRODUCT((I573=$I$6:$I$1500)*(B573&lt;$B$6:$B$1500))+SUMPRODUCT((I573=$I$6:$I$573)*(B573=$B$6:$B$573)))</f>
+        <f aca="false">IF(J573="","",SUMPRODUCT((I573=$I$6:$I$1500)*(B573&lt;$B$6:$B$1500))+COUNTIFS($I$6:I573,I573,$B$6:B573,B573))</f>
         <v/>
       </c>
     </row>
@@ -26390,7 +26390,7 @@
         <v/>
       </c>
       <c r="K574" s="25" t="str">
-        <f aca="false">IF(J574="","",SUMPRODUCT((I574=$I$6:$I$1500)*(B574&lt;$B$6:$B$1500))+SUMPRODUCT((I574=$I$6:$I$574)*(B574=$B$6:$B$574)))</f>
+        <f aca="false">IF(J574="","",SUMPRODUCT((I574=$I$6:$I$1500)*(B574&lt;$B$6:$B$1500))+COUNTIFS($I$6:I574,I574,$B$6:B574,B574))</f>
         <v/>
       </c>
     </row>
@@ -26428,7 +26428,7 @@
         <v/>
       </c>
       <c r="K575" s="25" t="str">
-        <f aca="false">IF(J575="","",SUMPRODUCT((I575=$I$6:$I$1500)*(B575&lt;$B$6:$B$1500))+SUMPRODUCT((I575=$I$6:$I$575)*(B575=$B$6:$B$575)))</f>
+        <f aca="false">IF(J575="","",SUMPRODUCT((I575=$I$6:$I$1500)*(B575&lt;$B$6:$B$1500))+COUNTIFS($I$6:I575,I575,$B$6:B575,B575))</f>
         <v/>
       </c>
     </row>
@@ -26466,7 +26466,7 @@
         <v/>
       </c>
       <c r="K576" s="25" t="str">
-        <f aca="false">IF(J576="","",SUMPRODUCT((I576=$I$6:$I$1500)*(B576&lt;$B$6:$B$1500))+SUMPRODUCT((I576=$I$6:$I$576)*(B576=$B$6:$B$576)))</f>
+        <f aca="false">IF(J576="","",SUMPRODUCT((I576=$I$6:$I$1500)*(B576&lt;$B$6:$B$1500))+COUNTIFS($I$6:I576,I576,$B$6:B576,B576))</f>
         <v/>
       </c>
     </row>
@@ -26504,7 +26504,7 @@
         <v/>
       </c>
       <c r="K577" s="25" t="str">
-        <f aca="false">IF(J577="","",SUMPRODUCT((I577=$I$6:$I$1500)*(B577&lt;$B$6:$B$1500))+SUMPRODUCT((I577=$I$6:$I$577)*(B577=$B$6:$B$577)))</f>
+        <f aca="false">IF(J577="","",SUMPRODUCT((I577=$I$6:$I$1500)*(B577&lt;$B$6:$B$1500))+COUNTIFS($I$6:I577,I577,$B$6:B577,B577))</f>
         <v/>
       </c>
     </row>
@@ -26542,7 +26542,7 @@
         <v/>
       </c>
       <c r="K578" s="25" t="str">
-        <f aca="false">IF(J578="","",SUMPRODUCT((I578=$I$6:$I$1500)*(B578&lt;$B$6:$B$1500))+SUMPRODUCT((I578=$I$6:$I$578)*(B578=$B$6:$B$578)))</f>
+        <f aca="false">IF(J578="","",SUMPRODUCT((I578=$I$6:$I$1500)*(B578&lt;$B$6:$B$1500))+COUNTIFS($I$6:I578,I578,$B$6:B578,B578))</f>
         <v/>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
         <v/>
       </c>
       <c r="K579" s="25" t="str">
-        <f aca="false">IF(J579="","",SUMPRODUCT((I579=$I$6:$I$1500)*(B579&lt;$B$6:$B$1500))+SUMPRODUCT((I579=$I$6:$I$579)*(B579=$B$6:$B$579)))</f>
+        <f aca="false">IF(J579="","",SUMPRODUCT((I579=$I$6:$I$1500)*(B579&lt;$B$6:$B$1500))+COUNTIFS($I$6:I579,I579,$B$6:B579,B579))</f>
         <v/>
       </c>
     </row>
@@ -26618,7 +26618,7 @@
         <v/>
       </c>
       <c r="K580" s="25" t="str">
-        <f aca="false">IF(J580="","",SUMPRODUCT((I580=$I$6:$I$1500)*(B580&lt;$B$6:$B$1500))+SUMPRODUCT((I580=$I$6:$I$580)*(B580=$B$6:$B$580)))</f>
+        <f aca="false">IF(J580="","",SUMPRODUCT((I580=$I$6:$I$1500)*(B580&lt;$B$6:$B$1500))+COUNTIFS($I$6:I580,I580,$B$6:B580,B580))</f>
         <v/>
       </c>
     </row>
@@ -26656,7 +26656,7 @@
         <v/>
       </c>
       <c r="K581" s="25" t="str">
-        <f aca="false">IF(J581="","",SUMPRODUCT((I581=$I$6:$I$1500)*(B581&lt;$B$6:$B$1500))+SUMPRODUCT((I581=$I$6:$I$581)*(B581=$B$6:$B$581)))</f>
+        <f aca="false">IF(J581="","",SUMPRODUCT((I581=$I$6:$I$1500)*(B581&lt;$B$6:$B$1500))+COUNTIFS($I$6:I581,I581,$B$6:B581,B581))</f>
         <v/>
       </c>
     </row>
@@ -26692,7 +26692,7 @@
         <v/>
       </c>
       <c r="K582" s="25" t="str">
-        <f aca="false">IF(J582="","",SUMPRODUCT((I582=$I$6:$I$1500)*(B582&lt;$B$6:$B$1500))+SUMPRODUCT((I582=$I$6:$I$582)*(B582=$B$6:$B$582)))</f>
+        <f aca="false">IF(J582="","",SUMPRODUCT((I582=$I$6:$I$1500)*(B582&lt;$B$6:$B$1500))+COUNTIFS($I$6:I582,I582,$B$6:B582,B582))</f>
         <v/>
       </c>
     </row>
@@ -26730,7 +26730,7 @@
         <v/>
       </c>
       <c r="K583" s="25" t="str">
-        <f aca="false">IF(J583="","",SUMPRODUCT((I583=$I$6:$I$1500)*(B583&lt;$B$6:$B$1500))+SUMPRODUCT((I583=$I$6:$I$583)*(B583=$B$6:$B$583)))</f>
+        <f aca="false">IF(J583="","",SUMPRODUCT((I583=$I$6:$I$1500)*(B583&lt;$B$6:$B$1500))+COUNTIFS($I$6:I583,I583,$B$6:B583,B583))</f>
         <v/>
       </c>
     </row>
@@ -26766,7 +26766,7 @@
         <v/>
       </c>
       <c r="K584" s="25" t="str">
-        <f aca="false">IF(J584="","",SUMPRODUCT((I584=$I$6:$I$1500)*(B584&lt;$B$6:$B$1500))+SUMPRODUCT((I584=$I$6:$I$584)*(B584=$B$6:$B$584)))</f>
+        <f aca="false">IF(J584="","",SUMPRODUCT((I584=$I$6:$I$1500)*(B584&lt;$B$6:$B$1500))+COUNTIFS($I$6:I584,I584,$B$6:B584,B584))</f>
         <v/>
       </c>
     </row>
@@ -26804,7 +26804,7 @@
         <v/>
       </c>
       <c r="K585" s="25" t="str">
-        <f aca="false">IF(J585="","",SUMPRODUCT((I585=$I$6:$I$1500)*(B585&lt;$B$6:$B$1500))+SUMPRODUCT((I585=$I$6:$I$585)*(B585=$B$6:$B$585)))</f>
+        <f aca="false">IF(J585="","",SUMPRODUCT((I585=$I$6:$I$1500)*(B585&lt;$B$6:$B$1500))+COUNTIFS($I$6:I585,I585,$B$6:B585,B585))</f>
         <v/>
       </c>
     </row>
@@ -26842,7 +26842,7 @@
         <v/>
       </c>
       <c r="K586" s="25" t="str">
-        <f aca="false">IF(J586="","",SUMPRODUCT((I586=$I$6:$I$1500)*(B586&lt;$B$6:$B$1500))+SUMPRODUCT((I586=$I$6:$I$586)*(B586=$B$6:$B$586)))</f>
+        <f aca="false">IF(J586="","",SUMPRODUCT((I586=$I$6:$I$1500)*(B586&lt;$B$6:$B$1500))+COUNTIFS($I$6:I586,I586,$B$6:B586,B586))</f>
         <v/>
       </c>
     </row>
@@ -26859,7 +26859,7 @@
         <v/>
       </c>
       <c r="K587" s="25" t="str">
-        <f aca="false">IF(J587="","",SUMPRODUCT((I587=$I$6:$I$1500)*(B587&lt;$B$6:$B$1500))+SUMPRODUCT((I587=$I$6:$I$587)*(B587=$B$6:$B$587)))</f>
+        <f aca="false">IF(J587="","",SUMPRODUCT((I587=$I$6:$I$1500)*(B587&lt;$B$6:$B$1500))+COUNTIFS($I$6:I587,I587,$B$6:B587,B587))</f>
         <v/>
       </c>
     </row>
@@ -26897,7 +26897,7 @@
         <v/>
       </c>
       <c r="K588" s="25" t="str">
-        <f aca="false">IF(J588="","",SUMPRODUCT((I588=$I$6:$I$1500)*(B588&lt;$B$6:$B$1500))+SUMPRODUCT((I588=$I$6:$I$588)*(B588=$B$6:$B$588)))</f>
+        <f aca="false">IF(J588="","",SUMPRODUCT((I588=$I$6:$I$1500)*(B588&lt;$B$6:$B$1500))+COUNTIFS($I$6:I588,I588,$B$6:B588,B588))</f>
         <v/>
       </c>
     </row>
@@ -26935,7 +26935,7 @@
         <v/>
       </c>
       <c r="K589" s="25" t="str">
-        <f aca="false">IF(J589="","",SUMPRODUCT((I589=$I$6:$I$1500)*(B589&lt;$B$6:$B$1500))+SUMPRODUCT((I589=$I$6:$I$589)*(B589=$B$6:$B$589)))</f>
+        <f aca="false">IF(J589="","",SUMPRODUCT((I589=$I$6:$I$1500)*(B589&lt;$B$6:$B$1500))+COUNTIFS($I$6:I589,I589,$B$6:B589,B589))</f>
         <v/>
       </c>
     </row>
@@ -26973,7 +26973,7 @@
         <v/>
       </c>
       <c r="K590" s="25" t="str">
-        <f aca="false">IF(J590="","",SUMPRODUCT((I590=$I$6:$I$1500)*(B590&lt;$B$6:$B$1500))+SUMPRODUCT((I590=$I$6:$I$590)*(B590=$B$6:$B$590)))</f>
+        <f aca="false">IF(J590="","",SUMPRODUCT((I590=$I$6:$I$1500)*(B590&lt;$B$6:$B$1500))+COUNTIFS($I$6:I590,I590,$B$6:B590,B590))</f>
         <v/>
       </c>
     </row>
@@ -27011,7 +27011,7 @@
         <v/>
       </c>
       <c r="K591" s="25" t="str">
-        <f aca="false">IF(J591="","",SUMPRODUCT((I591=$I$6:$I$1500)*(B591&lt;$B$6:$B$1500))+SUMPRODUCT((I591=$I$6:$I$591)*(B591=$B$6:$B$591)))</f>
+        <f aca="false">IF(J591="","",SUMPRODUCT((I591=$I$6:$I$1500)*(B591&lt;$B$6:$B$1500))+COUNTIFS($I$6:I591,I591,$B$6:B591,B591))</f>
         <v/>
       </c>
     </row>
@@ -27049,7 +27049,7 @@
         <v/>
       </c>
       <c r="K592" s="25" t="str">
-        <f aca="false">IF(J592="","",SUMPRODUCT((I592=$I$6:$I$1500)*(B592&lt;$B$6:$B$1500))+SUMPRODUCT((I592=$I$6:$I$592)*(B592=$B$6:$B$592)))</f>
+        <f aca="false">IF(J592="","",SUMPRODUCT((I592=$I$6:$I$1500)*(B592&lt;$B$6:$B$1500))+COUNTIFS($I$6:I592,I592,$B$6:B592,B592))</f>
         <v/>
       </c>
     </row>
@@ -27087,7 +27087,7 @@
         <v/>
       </c>
       <c r="K593" s="25" t="str">
-        <f aca="false">IF(J593="","",SUMPRODUCT((I593=$I$6:$I$1500)*(B593&lt;$B$6:$B$1500))+SUMPRODUCT((I593=$I$6:$I$593)*(B593=$B$6:$B$593)))</f>
+        <f aca="false">IF(J593="","",SUMPRODUCT((I593=$I$6:$I$1500)*(B593&lt;$B$6:$B$1500))+COUNTIFS($I$6:I593,I593,$B$6:B593,B593))</f>
         <v/>
       </c>
     </row>
@@ -27125,7 +27125,7 @@
         <v/>
       </c>
       <c r="K594" s="25" t="str">
-        <f aca="false">IF(J594="","",SUMPRODUCT((I594=$I$6:$I$1500)*(B594&lt;$B$6:$B$1500))+SUMPRODUCT((I594=$I$6:$I$594)*(B594=$B$6:$B$594)))</f>
+        <f aca="false">IF(J594="","",SUMPRODUCT((I594=$I$6:$I$1500)*(B594&lt;$B$6:$B$1500))+COUNTIFS($I$6:I594,I594,$B$6:B594,B594))</f>
         <v/>
       </c>
     </row>
@@ -27163,7 +27163,7 @@
         <v/>
       </c>
       <c r="K595" s="25" t="str">
-        <f aca="false">IF(J595="","",SUMPRODUCT((I595=$I$6:$I$1500)*(B595&lt;$B$6:$B$1500))+SUMPRODUCT((I595=$I$6:$I$595)*(B595=$B$6:$B$595)))</f>
+        <f aca="false">IF(J595="","",SUMPRODUCT((I595=$I$6:$I$1500)*(B595&lt;$B$6:$B$1500))+COUNTIFS($I$6:I595,I595,$B$6:B595,B595))</f>
         <v/>
       </c>
     </row>
@@ -27201,7 +27201,7 @@
         <v/>
       </c>
       <c r="K596" s="25" t="str">
-        <f aca="false">IF(J596="","",SUMPRODUCT((I596=$I$6:$I$1500)*(B596&lt;$B$6:$B$1500))+SUMPRODUCT((I596=$I$6:$I$596)*(B596=$B$6:$B$596)))</f>
+        <f aca="false">IF(J596="","",SUMPRODUCT((I596=$I$6:$I$1500)*(B596&lt;$B$6:$B$1500))+COUNTIFS($I$6:I596,I596,$B$6:B596,B596))</f>
         <v/>
       </c>
     </row>
@@ -27239,7 +27239,7 @@
         <v/>
       </c>
       <c r="K597" s="25" t="str">
-        <f aca="false">IF(J597="","",SUMPRODUCT((I597=$I$6:$I$1500)*(B597&lt;$B$6:$B$1500))+SUMPRODUCT((I597=$I$6:$I$597)*(B597=$B$6:$B$597)))</f>
+        <f aca="false">IF(J597="","",SUMPRODUCT((I597=$I$6:$I$1500)*(B597&lt;$B$6:$B$1500))+COUNTIFS($I$6:I597,I597,$B$6:B597,B597))</f>
         <v/>
       </c>
     </row>
@@ -27277,7 +27277,7 @@
         <v/>
       </c>
       <c r="K598" s="25" t="str">
-        <f aca="false">IF(J598="","",SUMPRODUCT((I598=$I$6:$I$1500)*(B598&lt;$B$6:$B$1500))+SUMPRODUCT((I598=$I$6:$I$598)*(B598=$B$6:$B$598)))</f>
+        <f aca="false">IF(J598="","",SUMPRODUCT((I598=$I$6:$I$1500)*(B598&lt;$B$6:$B$1500))+COUNTIFS($I$6:I598,I598,$B$6:B598,B598))</f>
         <v/>
       </c>
     </row>
@@ -27315,7 +27315,7 @@
         <v/>
       </c>
       <c r="K599" s="25" t="str">
-        <f aca="false">IF(J599="","",SUMPRODUCT((I599=$I$6:$I$1500)*(B599&lt;$B$6:$B$1500))+SUMPRODUCT((I599=$I$6:$I$599)*(B599=$B$6:$B$599)))</f>
+        <f aca="false">IF(J599="","",SUMPRODUCT((I599=$I$6:$I$1500)*(B599&lt;$B$6:$B$1500))+COUNTIFS($I$6:I599,I599,$B$6:B599,B599))</f>
         <v/>
       </c>
     </row>
@@ -27353,7 +27353,7 @@
         <v/>
       </c>
       <c r="K600" s="25" t="str">
-        <f aca="false">IF(J600="","",SUMPRODUCT((I600=$I$6:$I$1500)*(B600&lt;$B$6:$B$1500))+SUMPRODUCT((I600=$I$6:$I$600)*(B600=$B$6:$B$600)))</f>
+        <f aca="false">IF(J600="","",SUMPRODUCT((I600=$I$6:$I$1500)*(B600&lt;$B$6:$B$1500))+COUNTIFS($I$6:I600,I600,$B$6:B600,B600))</f>
         <v/>
       </c>
     </row>
@@ -27391,7 +27391,7 @@
         <v/>
       </c>
       <c r="K601" s="25" t="str">
-        <f aca="false">IF(J601="","",SUMPRODUCT((I601=$I$6:$I$1500)*(B601&lt;$B$6:$B$1500))+SUMPRODUCT((I601=$I$6:$I$601)*(B601=$B$6:$B$601)))</f>
+        <f aca="false">IF(J601="","",SUMPRODUCT((I601=$I$6:$I$1500)*(B601&lt;$B$6:$B$1500))+COUNTIFS($I$6:I601,I601,$B$6:B601,B601))</f>
         <v/>
       </c>
     </row>
@@ -27429,7 +27429,7 @@
         <v/>
       </c>
       <c r="K602" s="25" t="str">
-        <f aca="false">IF(J602="","",SUMPRODUCT((I602=$I$6:$I$1500)*(B602&lt;$B$6:$B$1500))+SUMPRODUCT((I602=$I$6:$I$602)*(B602=$B$6:$B$602)))</f>
+        <f aca="false">IF(J602="","",SUMPRODUCT((I602=$I$6:$I$1500)*(B602&lt;$B$6:$B$1500))+COUNTIFS($I$6:I602,I602,$B$6:B602,B602))</f>
         <v/>
       </c>
     </row>
@@ -27467,7 +27467,7 @@
         <v/>
       </c>
       <c r="K603" s="25" t="str">
-        <f aca="false">IF(J603="","",SUMPRODUCT((I603=$I$6:$I$1500)*(B603&lt;$B$6:$B$1500))+SUMPRODUCT((I603=$I$6:$I$603)*(B603=$B$6:$B$603)))</f>
+        <f aca="false">IF(J603="","",SUMPRODUCT((I603=$I$6:$I$1500)*(B603&lt;$B$6:$B$1500))+COUNTIFS($I$6:I603,I603,$B$6:B603,B603))</f>
         <v/>
       </c>
     </row>
@@ -27503,7 +27503,7 @@
         <v/>
       </c>
       <c r="K604" s="25" t="str">
-        <f aca="false">IF(J604="","",SUMPRODUCT((I604=$I$6:$I$1500)*(B604&lt;$B$6:$B$1500))+SUMPRODUCT((I604=$I$6:$I$604)*(B604=$B$6:$B$604)))</f>
+        <f aca="false">IF(J604="","",SUMPRODUCT((I604=$I$6:$I$1500)*(B604&lt;$B$6:$B$1500))+COUNTIFS($I$6:I604,I604,$B$6:B604,B604))</f>
         <v/>
       </c>
     </row>
@@ -27541,7 +27541,7 @@
         <v/>
       </c>
       <c r="K605" s="25" t="str">
-        <f aca="false">IF(J605="","",SUMPRODUCT((I605=$I$6:$I$1500)*(B605&lt;$B$6:$B$1500))+SUMPRODUCT((I605=$I$6:$I$605)*(B605=$B$6:$B$605)))</f>
+        <f aca="false">IF(J605="","",SUMPRODUCT((I605=$I$6:$I$1500)*(B605&lt;$B$6:$B$1500))+COUNTIFS($I$6:I605,I605,$B$6:B605,B605))</f>
         <v/>
       </c>
     </row>
@@ -27579,7 +27579,7 @@
         <v/>
       </c>
       <c r="K606" s="25" t="str">
-        <f aca="false">IF(J606="","",SUMPRODUCT((I606=$I$6:$I$1500)*(B606&lt;$B$6:$B$1500))+SUMPRODUCT((I606=$I$6:$I$606)*(B606=$B$6:$B$606)))</f>
+        <f aca="false">IF(J606="","",SUMPRODUCT((I606=$I$6:$I$1500)*(B606&lt;$B$6:$B$1500))+COUNTIFS($I$6:I606,I606,$B$6:B606,B606))</f>
         <v/>
       </c>
     </row>
@@ -27596,7 +27596,7 @@
         <v/>
       </c>
       <c r="K607" s="25" t="str">
-        <f aca="false">IF(J607="","",SUMPRODUCT((I607=$I$6:$I$1500)*(B607&lt;$B$6:$B$1500))+SUMPRODUCT((I607=$I$6:$I$607)*(B607=$B$6:$B$607)))</f>
+        <f aca="false">IF(J607="","",SUMPRODUCT((I607=$I$6:$I$1500)*(B607&lt;$B$6:$B$1500))+COUNTIFS($I$6:I607,I607,$B$6:B607,B607))</f>
         <v/>
       </c>
     </row>
